--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -30,6 +30,12 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Valor Despesa Empenhada</t>
+  </si>
+  <si>
+    <t>Valor Despesa Liquidada</t>
+  </si>
+  <si>
     <t>Valor Pago Financeiro</t>
   </si>
   <si>
@@ -207,6 +213,12 @@
     <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
   </si>
   <si>
+    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
     <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
   </si>
   <si>
@@ -231,9 +243,6 @@
     <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
   </si>
   <si>
-    <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
-  </si>
-  <si>
     <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
   </si>
   <si>
@@ -247,9 +256,6 @@
   </si>
   <si>
     <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
   </si>
   <si>
     <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
@@ -278,7 +284,6 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -631,20 +636,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="4" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -657,17 +662,23 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>2025</v>
       </c>
@@ -675,22 +686,28 @@
         <v>1071</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="6">
+        <v>55898902.780000001</v>
+      </c>
+      <c r="E2" s="6">
+        <v>34921981.439999998</v>
+      </c>
+      <c r="F2" s="6">
         <v>32307667.050000001</v>
       </c>
-      <c r="E2" s="6">
+      <c r="G2" s="6">
         <v>0</v>
       </c>
-      <c r="F2" s="6">
+      <c r="H2" s="6">
         <v>4293686.1900000004</v>
       </c>
-      <c r="G2" s="7">
+      <c r="I2" s="7">
         <v>4293686.1900000004</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2025</v>
       </c>
@@ -698,22 +715,28 @@
         <v>1081</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6">
+        <v>1023743951.58</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1014541849.87</v>
+      </c>
+      <c r="F3" s="6">
         <v>759567117.26999998</v>
       </c>
-      <c r="E3" s="6">
+      <c r="G3" s="6">
         <v>11357399.470000001</v>
       </c>
-      <c r="F3" s="6">
+      <c r="H3" s="6">
         <v>2680004.75</v>
       </c>
-      <c r="G3" s="7">
+      <c r="I3" s="7">
         <v>14037404.220000001</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>2025</v>
       </c>
@@ -721,22 +744,28 @@
         <v>1101</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6">
+        <v>18048368.199999999</v>
+      </c>
+      <c r="E4" s="6">
+        <v>17928588.510000002</v>
+      </c>
+      <c r="F4" s="6">
         <v>17774694.27</v>
       </c>
-      <c r="E4" s="6">
+      <c r="G4" s="6">
         <v>0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="H4" s="6">
         <v>57114.59</v>
       </c>
-      <c r="G4" s="7">
+      <c r="I4" s="7">
         <v>57114.59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2025</v>
       </c>
@@ -744,22 +773,28 @@
         <v>1191</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6">
+        <v>1886784188.8099999</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1792612515.5899999</v>
+      </c>
+      <c r="F5" s="6">
         <v>1767643635.4300001</v>
       </c>
-      <c r="E5" s="6">
+      <c r="G5" s="6">
         <v>5956448.8899999997</v>
       </c>
-      <c r="F5" s="6">
+      <c r="H5" s="6">
         <v>38130787.079999998</v>
       </c>
-      <c r="G5" s="7">
+      <c r="I5" s="7">
         <v>44087235.969999999</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2025</v>
       </c>
@@ -767,22 +802,28 @@
         <v>1221</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6">
+        <v>425928118.32999998</v>
+      </c>
+      <c r="E6" s="6">
+        <v>106813200.90000001</v>
+      </c>
+      <c r="F6" s="6">
         <v>104972627.41</v>
       </c>
-      <c r="E6" s="6">
+      <c r="G6" s="6">
         <v>3819.55</v>
       </c>
-      <c r="F6" s="6">
+      <c r="H6" s="6">
         <v>10240167.34</v>
       </c>
-      <c r="G6" s="7">
+      <c r="I6" s="7">
         <v>10243986.890000001</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>2025</v>
       </c>
@@ -790,22 +831,28 @@
         <v>1231</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="6">
+        <v>319941879.06999999</v>
+      </c>
+      <c r="E7" s="6">
+        <v>286029024.67000002</v>
+      </c>
+      <c r="F7" s="6">
         <v>275453889.56</v>
       </c>
-      <c r="E7" s="6">
+      <c r="G7" s="6">
         <v>4468309.21</v>
       </c>
-      <c r="F7" s="6">
+      <c r="H7" s="6">
         <v>18499399.920000002</v>
       </c>
-      <c r="G7" s="7">
+      <c r="I7" s="7">
         <v>22967709.129999999</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2025</v>
       </c>
@@ -813,22 +860,28 @@
         <v>1251</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6">
+        <v>17184629357.540001</v>
+      </c>
+      <c r="E8" s="6">
+        <v>16913388822.07</v>
+      </c>
+      <c r="F8" s="6">
         <v>16881355805.92</v>
       </c>
-      <c r="E8" s="6">
+      <c r="G8" s="6">
         <v>22568008.23</v>
       </c>
-      <c r="F8" s="6">
+      <c r="H8" s="6">
         <v>179457677.69</v>
       </c>
-      <c r="G8" s="7">
+      <c r="I8" s="7">
         <v>202025685.91999999</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2025</v>
       </c>
@@ -836,22 +889,28 @@
         <v>1261</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6">
+        <v>20024070516.279999</v>
+      </c>
+      <c r="E9" s="6">
+        <v>19817333122</v>
+      </c>
+      <c r="F9" s="6">
         <v>19583419698.990002</v>
       </c>
-      <c r="E9" s="6">
+      <c r="G9" s="6">
         <v>102690852.14</v>
       </c>
-      <c r="F9" s="6">
+      <c r="H9" s="6">
         <v>437921985.25</v>
       </c>
-      <c r="G9" s="7">
+      <c r="I9" s="7">
         <v>540612837.38999999</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>2025</v>
       </c>
@@ -859,22 +918,28 @@
         <v>1271</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6">
+        <v>261449910.33000001</v>
+      </c>
+      <c r="E10" s="6">
+        <v>260070135.18000001</v>
+      </c>
+      <c r="F10" s="6">
         <v>257629551.13</v>
       </c>
-      <c r="E10" s="6">
+      <c r="G10" s="6">
         <v>2520</v>
       </c>
-      <c r="F10" s="6">
+      <c r="H10" s="6">
         <v>2485549.7200000002</v>
       </c>
-      <c r="G10" s="7">
+      <c r="I10" s="7">
         <v>2488069.7200000002</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>2025</v>
       </c>
@@ -882,22 +947,28 @@
         <v>1301</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="6">
+        <v>480636059.57999998</v>
+      </c>
+      <c r="E11" s="6">
+        <v>393222333.81</v>
+      </c>
+      <c r="F11" s="6">
         <v>363896390.25999999</v>
       </c>
-      <c r="E11" s="6">
+      <c r="G11" s="6">
         <v>11727528.060000001</v>
       </c>
-      <c r="F11" s="6">
+      <c r="H11" s="6">
         <v>201174882.84999999</v>
       </c>
-      <c r="G11" s="7">
+      <c r="I11" s="7">
         <v>212902410.91</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>2025</v>
       </c>
@@ -905,22 +976,28 @@
         <v>1371</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6">
+        <v>185286819.99000001</v>
+      </c>
+      <c r="E12" s="6">
+        <v>178437283.68000001</v>
+      </c>
+      <c r="F12" s="6">
         <v>172648640.16</v>
       </c>
-      <c r="E12" s="6">
+      <c r="G12" s="6">
         <v>271467.65000000002</v>
       </c>
-      <c r="F12" s="6">
+      <c r="H12" s="6">
         <v>5465504.5800000001</v>
       </c>
-      <c r="G12" s="7">
+      <c r="I12" s="7">
         <v>5736972.2300000004</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>2025</v>
       </c>
@@ -928,22 +1005,28 @@
         <v>1401</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6">
+        <v>2074027252.0699999</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1999073232.1300001</v>
+      </c>
+      <c r="F13" s="6">
         <v>1988491760.28</v>
       </c>
-      <c r="E13" s="6">
+      <c r="G13" s="6">
         <v>4678551.78</v>
       </c>
-      <c r="F13" s="6">
+      <c r="H13" s="6">
         <v>71714800.709999993</v>
       </c>
-      <c r="G13" s="7">
+      <c r="I13" s="7">
         <v>76393352.489999995</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>2025</v>
       </c>
@@ -951,22 +1034,28 @@
         <v>1451</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14" s="6">
+        <v>4556477829.6899996</v>
+      </c>
+      <c r="E14" s="6">
+        <v>4357599952.2399998</v>
+      </c>
+      <c r="F14" s="6">
         <v>4322020545.1700001</v>
       </c>
-      <c r="E14" s="6">
+      <c r="G14" s="6">
         <v>4833097.2</v>
       </c>
-      <c r="F14" s="6">
+      <c r="H14" s="6">
         <v>108147895.72</v>
       </c>
-      <c r="G14" s="7">
+      <c r="I14" s="7">
         <v>112980992.92</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>2025</v>
       </c>
@@ -974,22 +1063,28 @@
         <v>1481</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" s="6">
+        <v>338412512.00999999</v>
+      </c>
+      <c r="E15" s="6">
+        <v>284330922.13999999</v>
+      </c>
+      <c r="F15" s="6">
         <v>273376533.99000001</v>
       </c>
-      <c r="E15" s="6">
+      <c r="G15" s="6">
         <v>6492833.4299999997</v>
       </c>
-      <c r="F15" s="6">
+      <c r="H15" s="6">
         <v>13954481.02</v>
       </c>
-      <c r="G15" s="7">
+      <c r="I15" s="7">
         <v>20447314.449999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>2025</v>
       </c>
@@ -997,22 +1092,28 @@
         <v>1491</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="6">
+        <v>971196665.48000002</v>
+      </c>
+      <c r="E16" s="6">
+        <v>965761230.42999995</v>
+      </c>
+      <c r="F16" s="6">
         <v>950181400.99000001</v>
       </c>
-      <c r="E16" s="6">
+      <c r="G16" s="6">
         <v>1028658.15</v>
       </c>
-      <c r="F16" s="6">
+      <c r="H16" s="6">
         <v>17535020.600000001</v>
       </c>
-      <c r="G16" s="7">
+      <c r="I16" s="7">
         <v>18563678.75</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>2025</v>
       </c>
@@ -1020,22 +1121,28 @@
         <v>1501</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6">
+        <v>940771355.50999999</v>
+      </c>
+      <c r="E17" s="6">
+        <v>840171011.04999995</v>
+      </c>
+      <c r="F17" s="6">
         <v>779489331.71000004</v>
       </c>
-      <c r="E17" s="6">
+      <c r="G17" s="6">
         <v>9145522.5999999996</v>
       </c>
-      <c r="F17" s="6">
+      <c r="H17" s="6">
         <v>62616118.700000003</v>
       </c>
-      <c r="G17" s="7">
+      <c r="I17" s="7">
         <v>71761641.299999997</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>2025</v>
       </c>
@@ -1043,22 +1150,28 @@
         <v>1511</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6">
+        <v>3138279917.0599999</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3076106533.5700002</v>
+      </c>
+      <c r="F18" s="6">
         <v>3055981056.6799998</v>
       </c>
-      <c r="E18" s="6">
+      <c r="G18" s="6">
         <v>18355346.550000001</v>
       </c>
-      <c r="F18" s="6">
+      <c r="H18" s="6">
         <v>41103215.43</v>
       </c>
-      <c r="G18" s="7">
+      <c r="I18" s="7">
         <v>59458561.979999997</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>2025</v>
       </c>
@@ -1066,22 +1179,28 @@
         <v>1521</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="6">
+        <v>70667226.109999999</v>
+      </c>
+      <c r="E19" s="6">
+        <v>69307261.739999995</v>
+      </c>
+      <c r="F19" s="6">
         <v>69083242.060000002</v>
       </c>
-      <c r="E19" s="6">
+      <c r="G19" s="6">
         <v>39281.15</v>
       </c>
-      <c r="F19" s="6">
+      <c r="H19" s="6">
         <v>907780.5</v>
       </c>
-      <c r="G19" s="7">
+      <c r="I19" s="7">
         <v>947061.65</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>2025</v>
       </c>
@@ -1089,22 +1208,28 @@
         <v>1541</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="6">
+        <v>25352006.23</v>
+      </c>
+      <c r="E20" s="6">
+        <v>23581392.719999999</v>
+      </c>
+      <c r="F20" s="6">
         <v>22865578.489999998</v>
       </c>
-      <c r="E20" s="6">
+      <c r="G20" s="6">
         <v>0</v>
       </c>
-      <c r="F20" s="6">
+      <c r="H20" s="6">
         <v>351886.66</v>
       </c>
-      <c r="G20" s="7">
+      <c r="I20" s="7">
         <v>351886.66</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>2025</v>
       </c>
@@ -1112,22 +1237,28 @@
         <v>1631</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21" s="6">
+        <v>12493555.880000001</v>
+      </c>
+      <c r="E21" s="6">
+        <v>12400512.789999999</v>
+      </c>
+      <c r="F21" s="6">
         <v>12257285.880000001</v>
       </c>
-      <c r="E21" s="6">
+      <c r="G21" s="6">
         <v>0</v>
       </c>
-      <c r="F21" s="6">
+      <c r="H21" s="6">
         <v>138983.67999999999</v>
       </c>
-      <c r="G21" s="7">
+      <c r="I21" s="7">
         <v>138983.67999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>2025</v>
       </c>
@@ -1135,22 +1266,28 @@
         <v>1711</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="6">
+        <v>181181663.88</v>
+      </c>
+      <c r="E22" s="6">
+        <v>101620737.73999999</v>
+      </c>
+      <c r="F22" s="6">
         <v>97019401.540000007</v>
       </c>
-      <c r="E22" s="6">
+      <c r="G22" s="6">
         <v>0</v>
       </c>
-      <c r="F22" s="6">
+      <c r="H22" s="6">
         <v>76618911.299999997</v>
       </c>
-      <c r="G22" s="7">
+      <c r="I22" s="7">
         <v>76618911.299999997</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>2025</v>
       </c>
@@ -1158,22 +1295,28 @@
         <v>1721</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" s="6">
+        <v>10652572.939999999</v>
+      </c>
+      <c r="E23" s="6">
+        <v>10295525.119999999</v>
+      </c>
+      <c r="F23" s="6">
         <v>9939287.6500000004</v>
       </c>
-      <c r="E23" s="6">
+      <c r="G23" s="6">
         <v>10152.64</v>
       </c>
-      <c r="F23" s="6">
+      <c r="H23" s="6">
         <v>276281.69</v>
       </c>
-      <c r="G23" s="7">
+      <c r="I23" s="7">
         <v>286434.33</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>2025</v>
       </c>
@@ -1181,22 +1324,28 @@
         <v>1911</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="6">
+        <v>1211264345.4300001</v>
+      </c>
+      <c r="E24" s="6">
         <v>1127569424.8</v>
       </c>
-      <c r="E24" s="6">
+      <c r="F24" s="6">
+        <v>1127569424.8</v>
+      </c>
+      <c r="G24" s="6">
         <v>0</v>
       </c>
-      <c r="F24" s="6">
+      <c r="H24" s="6">
         <v>70456474.189999998</v>
       </c>
-      <c r="G24" s="7">
+      <c r="I24" s="7">
         <v>70456474.189999998</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>2025</v>
       </c>
@@ -1204,22 +1353,28 @@
         <v>1915</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" s="6">
         <v>20043002.559999999</v>
       </c>
       <c r="E25" s="6">
+        <v>20043002.559999999</v>
+      </c>
+      <c r="F25" s="6">
+        <v>20043002.559999999</v>
+      </c>
+      <c r="G25" s="6">
         <v>0</v>
       </c>
-      <c r="F25" s="6">
+      <c r="H25" s="6">
         <v>46.77</v>
       </c>
-      <c r="G25" s="7">
+      <c r="I25" s="7">
         <v>46.77</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>2025</v>
       </c>
@@ -1227,22 +1382,28 @@
         <v>1916</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" s="6">
+        <v>6570721631.0600004</v>
+      </c>
+      <c r="E26" s="6">
+        <v>6570721631.0600004</v>
+      </c>
+      <c r="F26" s="6">
         <v>6497797081.6999998</v>
       </c>
-      <c r="E26" s="6">
+      <c r="G26" s="6">
         <v>260833467.16</v>
       </c>
-      <c r="F26" s="6">
+      <c r="H26" s="6">
         <v>0</v>
       </c>
-      <c r="G26" s="7">
+      <c r="I26" s="7">
         <v>260833467.16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>2025</v>
       </c>
@@ -1250,22 +1411,28 @@
         <v>1941</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D27" s="6">
+        <v>194535650.21000001</v>
+      </c>
+      <c r="E27" s="6">
+        <v>193268761.55000001</v>
+      </c>
+      <c r="F27" s="6">
         <v>193178812.25</v>
       </c>
-      <c r="E27" s="6">
+      <c r="G27" s="6">
         <v>27888.27</v>
       </c>
-      <c r="F27" s="6">
+      <c r="H27" s="6">
         <v>1669467.18</v>
       </c>
-      <c r="G27" s="7">
+      <c r="I27" s="7">
         <v>1697355.45</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>2025</v>
       </c>
@@ -1273,22 +1440,28 @@
         <v>2011</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D28" s="6">
+        <v>2066687330.24</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1811898139.4000001</v>
+      </c>
+      <c r="F28" s="6">
         <v>1767628149.6600001</v>
       </c>
-      <c r="E28" s="6">
+      <c r="G28" s="6">
         <v>1062515.58</v>
       </c>
-      <c r="F28" s="6">
+      <c r="H28" s="6">
         <v>92904525.540000007</v>
       </c>
-      <c r="G28" s="7">
+      <c r="I28" s="7">
         <v>93967041.120000005</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>2025</v>
       </c>
@@ -1296,22 +1469,28 @@
         <v>2041</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" s="6">
+        <v>2901561.62</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2865088.76</v>
+      </c>
+      <c r="F29" s="6">
         <v>2860275.95</v>
       </c>
-      <c r="E29" s="6">
+      <c r="G29" s="6">
         <v>3394.97</v>
       </c>
-      <c r="F29" s="6">
+      <c r="H29" s="6">
         <v>24471.67</v>
       </c>
-      <c r="G29" s="7">
+      <c r="I29" s="7">
         <v>27866.639999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>2025</v>
       </c>
@@ -1319,22 +1498,28 @@
         <v>2061</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" s="6">
+        <v>70806633.620000005</v>
+      </c>
+      <c r="E30" s="6">
+        <v>68325905.25</v>
+      </c>
+      <c r="F30" s="6">
         <v>67044604.869999997</v>
       </c>
-      <c r="E30" s="6">
+      <c r="G30" s="6">
         <v>11590.87</v>
       </c>
-      <c r="F30" s="6">
+      <c r="H30" s="6">
         <v>1026935.64</v>
       </c>
-      <c r="G30" s="7">
+      <c r="I30" s="7">
         <v>1038526.51</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>2025</v>
       </c>
@@ -1342,22 +1527,28 @@
         <v>2071</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" s="6">
+        <v>585603048.33000004</v>
+      </c>
+      <c r="E31" s="6">
+        <v>580710591.19000006</v>
+      </c>
+      <c r="F31" s="6">
         <v>574854711.53999996</v>
       </c>
-      <c r="E31" s="6">
+      <c r="G31" s="6">
         <v>1239266.23</v>
       </c>
-      <c r="F31" s="6">
+      <c r="H31" s="6">
         <v>8506819.6199999992</v>
       </c>
-      <c r="G31" s="7">
+      <c r="I31" s="7">
         <v>9746085.8499999996</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>2025</v>
       </c>
@@ -1365,22 +1556,28 @@
         <v>2091</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D32" s="6">
+        <v>75621728.879999995</v>
+      </c>
+      <c r="E32" s="6">
+        <v>74134505.909999996</v>
+      </c>
+      <c r="F32" s="6">
         <v>72540998.400000006</v>
       </c>
-      <c r="E32" s="6">
+      <c r="G32" s="6">
         <v>24329.43</v>
       </c>
-      <c r="F32" s="6">
+      <c r="H32" s="6">
         <v>2347292.71</v>
       </c>
-      <c r="G32" s="7">
+      <c r="I32" s="7">
         <v>2371622.14</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>2025</v>
       </c>
@@ -1388,22 +1585,28 @@
         <v>2101</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D33" s="6">
+        <v>217212201.81999999</v>
+      </c>
+      <c r="E33" s="6">
+        <v>204765475.80000001</v>
+      </c>
+      <c r="F33" s="6">
         <v>196759897.63</v>
       </c>
-      <c r="E33" s="6">
+      <c r="G33" s="6">
         <v>1333045.2</v>
       </c>
-      <c r="F33" s="6">
+      <c r="H33" s="6">
         <v>7655898.75</v>
       </c>
-      <c r="G33" s="7">
+      <c r="I33" s="7">
         <v>8988943.9499999993</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>2025</v>
       </c>
@@ -1411,22 +1614,28 @@
         <v>2121</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D34" s="6">
+        <v>3302390465.79</v>
+      </c>
+      <c r="E34" s="6">
+        <v>3251209178.8699999</v>
+      </c>
+      <c r="F34" s="6">
         <v>3202602086.9200001</v>
       </c>
-      <c r="E34" s="6">
+      <c r="G34" s="6">
         <v>294911.07</v>
       </c>
-      <c r="F34" s="6">
+      <c r="H34" s="6">
         <v>15606900.02</v>
       </c>
-      <c r="G34" s="7">
+      <c r="I34" s="7">
         <v>15901811.09</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>2025</v>
       </c>
@@ -1434,22 +1643,28 @@
         <v>2151</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" s="6">
+        <v>81750398.859999999</v>
+      </c>
+      <c r="E35" s="6">
+        <v>76284993.930000007</v>
+      </c>
+      <c r="F35" s="6">
         <v>75483300.689999998</v>
       </c>
-      <c r="E35" s="6">
+      <c r="G35" s="6">
         <v>24887.1</v>
       </c>
-      <c r="F35" s="6">
+      <c r="H35" s="6">
         <v>1770214.54</v>
       </c>
-      <c r="G35" s="7">
+      <c r="I35" s="7">
         <v>1795101.64</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>2025</v>
       </c>
@@ -1457,22 +1672,28 @@
         <v>2161</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D36" s="6">
+        <v>6356895.04</v>
+      </c>
+      <c r="E36" s="6">
+        <v>5950697.5800000001</v>
+      </c>
+      <c r="F36" s="6">
         <v>5865105.7800000003</v>
       </c>
-      <c r="E36" s="6">
+      <c r="G36" s="6">
         <v>0</v>
       </c>
-      <c r="F36" s="6">
+      <c r="H36" s="6">
         <v>416373.16</v>
       </c>
-      <c r="G36" s="7">
+      <c r="I36" s="7">
         <v>416373.16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>2025</v>
       </c>
@@ -1480,22 +1701,28 @@
         <v>2171</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D37" s="6">
+        <v>9439748.6199999992</v>
+      </c>
+      <c r="E37" s="6">
+        <v>9225890.4000000004</v>
+      </c>
+      <c r="F37" s="6">
         <v>8465439.7200000007</v>
       </c>
-      <c r="E37" s="6">
+      <c r="G37" s="6">
         <v>480546.01</v>
       </c>
-      <c r="F37" s="6">
+      <c r="H37" s="6">
         <v>177676.07</v>
       </c>
-      <c r="G37" s="7">
+      <c r="I37" s="7">
         <v>658222.07999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>2025</v>
       </c>
@@ -1503,22 +1730,28 @@
         <v>2181</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D38" s="6">
+        <v>63217552.93</v>
+      </c>
+      <c r="E38" s="6">
+        <v>60940567.950000003</v>
+      </c>
+      <c r="F38" s="6">
         <v>56959723.43</v>
       </c>
-      <c r="E38" s="6">
+      <c r="G38" s="6">
         <v>119258.05</v>
       </c>
-      <c r="F38" s="6">
+      <c r="H38" s="6">
         <v>2222004.25</v>
       </c>
-      <c r="G38" s="7">
+      <c r="I38" s="7">
         <v>2341262.2999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>2025</v>
       </c>
@@ -1526,22 +1759,28 @@
         <v>2201</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D39" s="6">
+        <v>28359171.850000001</v>
+      </c>
+      <c r="E39" s="6">
+        <v>27321777.399999999</v>
+      </c>
+      <c r="F39" s="6">
         <v>25220175.309999999</v>
       </c>
-      <c r="E39" s="6">
+      <c r="G39" s="6">
         <v>6473.82</v>
       </c>
-      <c r="F39" s="6">
+      <c r="H39" s="6">
         <v>1262449.1299999999</v>
       </c>
-      <c r="G39" s="7">
+      <c r="I39" s="7">
         <v>1268922.95</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>2025</v>
       </c>
@@ -1549,22 +1788,28 @@
         <v>2211</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D40" s="6">
+        <v>16376327.77</v>
+      </c>
+      <c r="E40" s="6">
+        <v>15665660.91</v>
+      </c>
+      <c r="F40" s="6">
         <v>14963532.880000001</v>
       </c>
-      <c r="E40" s="6">
+      <c r="G40" s="6">
         <v>84375.35</v>
       </c>
-      <c r="F40" s="6">
+      <c r="H40" s="6">
         <v>903154.46</v>
       </c>
-      <c r="G40" s="7">
+      <c r="I40" s="7">
         <v>987529.81</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>2025</v>
       </c>
@@ -1572,22 +1817,28 @@
         <v>2241</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D41" s="6">
+        <v>195257062.84999999</v>
+      </c>
+      <c r="E41" s="6">
+        <v>182522813.41</v>
+      </c>
+      <c r="F41" s="6">
         <v>181974009.41</v>
       </c>
-      <c r="E41" s="6">
+      <c r="G41" s="6">
         <v>10483113.83</v>
       </c>
-      <c r="F41" s="6">
+      <c r="H41" s="6">
         <v>1680822.65</v>
       </c>
-      <c r="G41" s="7">
+      <c r="I41" s="7">
         <v>12163936.48</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>2025</v>
       </c>
@@ -1595,22 +1846,28 @@
         <v>2251</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D42" s="6">
+        <v>41105200.07</v>
+      </c>
+      <c r="E42" s="6">
+        <v>38759738.469999999</v>
+      </c>
+      <c r="F42" s="6">
         <v>36259002.32</v>
       </c>
-      <c r="E42" s="6">
+      <c r="G42" s="6">
         <v>0</v>
       </c>
-      <c r="F42" s="6">
+      <c r="H42" s="6">
         <v>1415037.52</v>
       </c>
-      <c r="G42" s="7">
+      <c r="I42" s="7">
         <v>1415037.52</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>2025</v>
       </c>
@@ -1618,22 +1875,28 @@
         <v>2261</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6">
+        <v>553211607.35000002</v>
+      </c>
+      <c r="E43" s="6">
+        <v>369463545.18000001</v>
+      </c>
+      <c r="F43" s="6">
         <v>355249323.07999998</v>
       </c>
-      <c r="E43" s="6">
+      <c r="G43" s="6">
         <v>38687418.560000002</v>
       </c>
-      <c r="F43" s="6">
+      <c r="H43" s="6">
         <v>130773841.95</v>
       </c>
-      <c r="G43" s="7">
+      <c r="I43" s="7">
         <v>169461260.50999999</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>2025</v>
       </c>
@@ -1641,22 +1904,28 @@
         <v>2271</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D44" s="6">
+        <v>2478485587.5</v>
+      </c>
+      <c r="E44" s="6">
+        <v>2347428600.4299998</v>
+      </c>
+      <c r="F44" s="6">
         <v>2300004443.9499998</v>
       </c>
-      <c r="E44" s="6">
+      <c r="G44" s="6">
         <v>18122531.300000001</v>
       </c>
-      <c r="F44" s="6">
+      <c r="H44" s="6">
         <v>63228349.740000002</v>
       </c>
-      <c r="G44" s="7">
+      <c r="I44" s="7">
         <v>81350881.040000007</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>2025</v>
       </c>
@@ -1664,22 +1933,28 @@
         <v>2281</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D45" s="6">
+        <v>7417117.2199999997</v>
+      </c>
+      <c r="E45" s="6">
+        <v>6859782.46</v>
+      </c>
+      <c r="F45" s="6">
         <v>6435691.9100000001</v>
       </c>
-      <c r="E45" s="6">
+      <c r="G45" s="6">
         <v>0</v>
       </c>
-      <c r="F45" s="6">
+      <c r="H45" s="6">
         <v>231057.02</v>
       </c>
-      <c r="G45" s="7">
+      <c r="I45" s="7">
         <v>231057.02</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>2025</v>
       </c>
@@ -1687,22 +1962,28 @@
         <v>2301</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D46" s="6">
+        <v>2143327357.7</v>
+      </c>
+      <c r="E46" s="6">
+        <v>1655881609.23</v>
+      </c>
+      <c r="F46" s="6">
         <v>1611441301.3699999</v>
       </c>
-      <c r="E46" s="6">
+      <c r="G46" s="6">
         <v>14178677.35</v>
       </c>
-      <c r="F46" s="6">
+      <c r="H46" s="6">
         <v>411934193.73000002</v>
       </c>
-      <c r="G46" s="7">
+      <c r="I46" s="7">
         <v>426112871.07999998</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>2025</v>
       </c>
@@ -1710,22 +1991,28 @@
         <v>2311</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D47" s="6">
+        <v>533150763.61000001</v>
+      </c>
+      <c r="E47" s="6">
+        <v>503448723.24000001</v>
+      </c>
+      <c r="F47" s="6">
         <v>492058770.58999997</v>
       </c>
-      <c r="E47" s="6">
+      <c r="G47" s="6">
         <v>274974.01</v>
       </c>
-      <c r="F47" s="6">
+      <c r="H47" s="6">
         <v>39010212.219999999</v>
       </c>
-      <c r="G47" s="7">
+      <c r="I47" s="7">
         <v>39285186.229999997</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>2025</v>
       </c>
@@ -1733,22 +2020,28 @@
         <v>2321</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D48" s="6">
+        <v>394549598.81</v>
+      </c>
+      <c r="E48" s="6">
+        <v>359596023.43000001</v>
+      </c>
+      <c r="F48" s="6">
         <v>346696259.17000002</v>
       </c>
-      <c r="E48" s="6">
+      <c r="G48" s="6">
         <v>1425788.73</v>
       </c>
-      <c r="F48" s="6">
+      <c r="H48" s="6">
         <v>30573782.129999999</v>
       </c>
-      <c r="G48" s="7">
+      <c r="I48" s="7">
         <v>31999570.859999999</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>2025</v>
       </c>
@@ -1756,22 +2049,28 @@
         <v>2331</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D49" s="6">
+        <v>35739703.740000002</v>
+      </c>
+      <c r="E49" s="6">
+        <v>34318152.899999999</v>
+      </c>
+      <c r="F49" s="6">
         <v>33074380.829999998</v>
       </c>
-      <c r="E49" s="6">
+      <c r="G49" s="6">
         <v>420781.11</v>
       </c>
-      <c r="F49" s="6">
+      <c r="H49" s="6">
         <v>436480.49</v>
       </c>
-      <c r="G49" s="7">
+      <c r="I49" s="7">
         <v>857261.6</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>2025</v>
       </c>
@@ -1779,22 +2078,28 @@
         <v>2351</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D50" s="6">
+        <v>431560939.48000002</v>
+      </c>
+      <c r="E50" s="6">
+        <v>399364373.02999997</v>
+      </c>
+      <c r="F50" s="6">
         <v>391027226.75999999</v>
       </c>
-      <c r="E50" s="6">
+      <c r="G50" s="6">
         <v>1690845.8</v>
       </c>
-      <c r="F50" s="6">
+      <c r="H50" s="6">
         <v>7591910.9699999997</v>
       </c>
-      <c r="G50" s="7">
+      <c r="I50" s="7">
         <v>9282756.7699999996</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>2025</v>
       </c>
@@ -1802,22 +2107,28 @@
         <v>2371</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D51" s="6">
+        <v>290312222.92000002</v>
+      </c>
+      <c r="E51" s="6">
+        <v>283815022.33999997</v>
+      </c>
+      <c r="F51" s="6">
         <v>282551558.48000002</v>
       </c>
-      <c r="E51" s="6">
+      <c r="G51" s="6">
         <v>654297.56999999995</v>
       </c>
-      <c r="F51" s="6">
+      <c r="H51" s="6">
         <v>7082912.7699999996</v>
       </c>
-      <c r="G51" s="7">
+      <c r="I51" s="7">
         <v>7737210.3399999999</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>2025</v>
       </c>
@@ -1825,22 +2136,28 @@
         <v>2421</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D52" s="6">
+        <v>61510642.640000001</v>
+      </c>
+      <c r="E52" s="6">
+        <v>43124254.630000003</v>
+      </c>
+      <c r="F52" s="6">
         <v>41282826.789999999</v>
       </c>
-      <c r="E52" s="6">
+      <c r="G52" s="6">
         <v>713315.27</v>
       </c>
-      <c r="F52" s="6">
+      <c r="H52" s="6">
         <v>7206237.1500000004</v>
       </c>
-      <c r="G52" s="7">
+      <c r="I52" s="7">
         <v>7919552.4199999999</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>2025</v>
       </c>
@@ -1848,22 +2165,28 @@
         <v>2431</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D53" s="6">
+        <v>7932027.7699999996</v>
+      </c>
+      <c r="E53" s="6">
+        <v>7756446.6299999999</v>
+      </c>
+      <c r="F53" s="6">
         <v>7297654.8799999999</v>
       </c>
-      <c r="E53" s="6">
+      <c r="G53" s="6">
         <v>45611.95</v>
       </c>
-      <c r="F53" s="6">
+      <c r="H53" s="6">
         <v>40582.82</v>
       </c>
-      <c r="G53" s="7">
+      <c r="I53" s="7">
         <v>86194.77</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>2025</v>
       </c>
@@ -1871,22 +2194,28 @@
         <v>2441</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D54" s="6">
+        <v>19031476.379999999</v>
+      </c>
+      <c r="E54" s="6">
+        <v>18693505.57</v>
+      </c>
+      <c r="F54" s="6">
         <v>18533956.489999998</v>
       </c>
-      <c r="E54" s="6">
+      <c r="G54" s="6">
         <v>87975.15</v>
       </c>
-      <c r="F54" s="6">
+      <c r="H54" s="6">
         <v>226885.18</v>
       </c>
-      <c r="G54" s="7">
+      <c r="I54" s="7">
         <v>314860.33</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>2025</v>
       </c>
@@ -1894,22 +2223,28 @@
         <v>2461</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D55" s="6">
+        <v>4789292.1100000003</v>
+      </c>
+      <c r="E55" s="6">
+        <v>3903632.02</v>
+      </c>
+      <c r="F55" s="6">
         <v>3547153</v>
       </c>
-      <c r="E55" s="6">
+      <c r="G55" s="6">
         <v>13266.26</v>
       </c>
-      <c r="F55" s="6">
+      <c r="H55" s="6">
         <v>175463.15</v>
       </c>
-      <c r="G55" s="7">
+      <c r="I55" s="7">
         <v>188729.41</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>2025</v>
       </c>
@@ -1917,361 +2252,445 @@
         <v>2471</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D56" s="6">
+        <v>12995181.74</v>
+      </c>
+      <c r="E56" s="6">
+        <v>9545227.8000000007</v>
+      </c>
+      <c r="F56" s="6">
         <v>9172117.3000000007</v>
       </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="7"/>
-    </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>2025</v>
       </c>
       <c r="B57" s="4">
+        <v>3041</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="6">
+        <v>411646902.57999998</v>
+      </c>
+      <c r="E57" s="6">
+        <v>411646902.57999998</v>
+      </c>
+      <c r="F57" s="6">
+        <v>411646902.57999998</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B58" s="4">
+        <v>3051</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="6">
+        <v>150702794.75999999</v>
+      </c>
+      <c r="E58" s="6">
+        <v>150702794.75999999</v>
+      </c>
+      <c r="F58" s="6">
+        <v>150702794.75999999</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B59" s="4">
         <v>4091</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="C59" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="6">
+        <v>610536.65</v>
+      </c>
+      <c r="E59" s="6">
         <v>323136.65999999997</v>
       </c>
-      <c r="E57" s="6">
+      <c r="F59" s="6">
+        <v>323136.65999999997</v>
+      </c>
+      <c r="G59" s="6">
         <v>0</v>
       </c>
-      <c r="F57" s="6">
+      <c r="H59" s="6">
         <v>2867068.53</v>
       </c>
-      <c r="G57" s="7">
+      <c r="I59" s="7">
         <v>2867068.53</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B58" s="4">
+    <row r="60" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B60" s="4">
         <v>4101</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="C60" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="6">
+        <v>16870000</v>
+      </c>
+      <c r="E60" s="6">
+        <v>16870000</v>
+      </c>
+      <c r="F60" s="6">
         <v>15570000</v>
       </c>
-      <c r="E58" s="6">
+      <c r="G60" s="6">
         <v>0</v>
       </c>
-      <c r="F58" s="6">
+      <c r="H60" s="6">
         <v>0</v>
       </c>
-      <c r="G58" s="7">
+      <c r="I60" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B59" s="4">
+    <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B61" s="4">
         <v>4141</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="C61" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" s="6">
+        <v>10407251.17</v>
+      </c>
+      <c r="E61" s="6">
+        <v>6488589.5</v>
+      </c>
+      <c r="F61" s="6">
         <v>6364731.3399999999</v>
       </c>
-      <c r="E59" s="6">
+      <c r="G61" s="6">
         <v>747392.63</v>
       </c>
-      <c r="F59" s="6">
+      <c r="H61" s="6">
         <v>8034402.6799999997</v>
       </c>
-      <c r="G59" s="7">
+      <c r="I61" s="7">
         <v>8781795.3100000005</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B60" s="4">
+    <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B62" s="4">
         <v>4251</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="6">
+      <c r="C62" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="6">
+        <v>172407716.30000001</v>
+      </c>
+      <c r="E62" s="6">
+        <v>169951293.66999999</v>
+      </c>
+      <c r="F62" s="6">
         <v>168474678.25999999</v>
       </c>
-      <c r="E60" s="6">
+      <c r="G62" s="6">
         <v>1112168.8899999999</v>
       </c>
-      <c r="F60" s="6">
+      <c r="H62" s="6">
         <v>5271380.07</v>
       </c>
-      <c r="G60" s="7">
+      <c r="I62" s="7">
         <v>6383548.96</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B61" s="4">
+    <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B63" s="4">
         <v>4291</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="6">
+      <c r="C63" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="6">
+        <v>12684000278.799999</v>
+      </c>
+      <c r="E63" s="6">
+        <v>12066473764.49</v>
+      </c>
+      <c r="F63" s="6">
         <v>11940374576.379999</v>
       </c>
-      <c r="E61" s="6">
+      <c r="G63" s="6">
         <v>622978466.21000004</v>
       </c>
-      <c r="F61" s="6">
+      <c r="H63" s="6">
         <v>547393802.41999996</v>
       </c>
-      <c r="G61" s="7">
+      <c r="I63" s="7">
         <v>1170372268.6300001</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B62" s="4">
+    <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B64" s="4">
         <v>4331</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C64" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="6">
+        <v>3035441.45</v>
+      </c>
+      <c r="E64" s="6">
+        <v>97428.45</v>
+      </c>
+      <c r="F64" s="6">
         <v>93102.96</v>
       </c>
-      <c r="E62" s="6">
+      <c r="G64" s="6">
         <v>0</v>
       </c>
-      <c r="F62" s="6">
+      <c r="H64" s="6">
         <v>206186.42</v>
       </c>
-      <c r="G62" s="7">
+      <c r="I64" s="7">
         <v>206186.42</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B63" s="4">
+    <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B65" s="4">
         <v>4341</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C65" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="6">
+        <v>2288740.7400000002</v>
+      </c>
+      <c r="E65" s="6">
+        <v>1318579.3999999999</v>
+      </c>
+      <c r="F65" s="6">
         <v>1060943.48</v>
       </c>
-      <c r="E63" s="6">
+      <c r="G65" s="6">
         <v>223487.09</v>
       </c>
-      <c r="F63" s="6">
+      <c r="H65" s="6">
         <v>548165.38</v>
       </c>
-      <c r="G63" s="7">
+      <c r="I65" s="7">
         <v>771652.47</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B64" s="4">
+    <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B66" s="4">
         <v>4381</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" s="6">
+      <c r="C66" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="6">
+        <v>127170575.95</v>
+      </c>
+      <c r="E66" s="6">
+        <v>102885370.45</v>
+      </c>
+      <c r="F66" s="6">
         <v>98080707.200000003</v>
       </c>
-      <c r="E64" s="6">
+      <c r="G66" s="6">
         <v>0</v>
       </c>
-      <c r="F64" s="6">
+      <c r="H66" s="6">
         <v>21378670.300000001</v>
       </c>
-      <c r="G64" s="7">
+      <c r="I66" s="7">
         <v>21378670.300000001</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B65" s="4">
-        <v>4421</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="6">
-        <v>3658.62</v>
-      </c>
-      <c r="E65" s="6">
-        <v>895.13</v>
-      </c>
-      <c r="F65" s="6">
+    <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B67" s="4">
+        <v>4451</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" s="6">
+        <v>48631312.579999998</v>
+      </c>
+      <c r="E67" s="6">
+        <v>11932319.970000001</v>
+      </c>
+      <c r="F67" s="6">
+        <v>11013107.33</v>
+      </c>
+      <c r="G67" s="6">
+        <v>679.54</v>
+      </c>
+      <c r="H67" s="6">
+        <v>8080205.7800000003</v>
+      </c>
+      <c r="I67" s="7">
+        <v>8080885.3200000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B68" s="4">
+        <v>4491</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="6">
+        <v>2634653.3199999998</v>
+      </c>
+      <c r="E68" s="6">
+        <v>2500037.94</v>
+      </c>
+      <c r="F68" s="6">
+        <v>1882700.63</v>
+      </c>
+      <c r="G68" s="6">
         <v>0</v>
       </c>
-      <c r="G65" s="7">
-        <v>895.13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B66" s="4">
-        <v>4451</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" s="6">
-        <v>11013107.33</v>
-      </c>
-      <c r="E66" s="6">
-        <v>679.54</v>
-      </c>
-      <c r="F66" s="6">
-        <v>8080205.7800000003</v>
-      </c>
-      <c r="G66" s="7">
-        <v>8080885.3200000003</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B67" s="4">
-        <v>4491</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="6">
-        <v>1882700.63</v>
-      </c>
-      <c r="E67" s="6">
+      <c r="H68" s="6">
+        <v>15394</v>
+      </c>
+      <c r="I68" s="7">
+        <v>15394</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B69" s="4">
+        <v>4541</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="6">
+        <v>350405</v>
+      </c>
+      <c r="E69" s="6">
+        <v>318593.90999999997</v>
+      </c>
+      <c r="F69" s="6">
+        <v>300914.63</v>
+      </c>
+      <c r="G69" s="6">
         <v>0</v>
       </c>
-      <c r="F67" s="6">
-        <v>15394</v>
-      </c>
-      <c r="G67" s="7">
-        <v>15394</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B68" s="4">
-        <v>4541</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D68" s="6">
-        <v>300914.63</v>
-      </c>
-      <c r="E68" s="6">
+      <c r="H69" s="6">
+        <v>26392.47</v>
+      </c>
+      <c r="I69" s="7">
+        <v>26392.47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B70" s="4">
+        <v>4551</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" s="6">
+        <v>148883049.19999999</v>
+      </c>
+      <c r="E70" s="6">
+        <v>148355490.34</v>
+      </c>
+      <c r="F70" s="6">
+        <v>148348943.52000001</v>
+      </c>
+      <c r="G70" s="6">
         <v>0</v>
       </c>
-      <c r="F68" s="6">
-        <v>26392.47</v>
-      </c>
-      <c r="G68" s="7">
-        <v>26392.47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B69" s="4">
-        <v>4551</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" s="6">
-        <v>148348943.52000001</v>
-      </c>
-      <c r="E69" s="6">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6">
+      <c r="H70" s="6">
         <v>620005.26</v>
       </c>
-      <c r="G69" s="7">
+      <c r="I70" s="7">
         <v>620005.26</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B70" s="4">
+    <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B71" s="4">
         <v>4601</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D70" s="6">
+      <c r="C71" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" s="6">
+        <v>1473191.28</v>
+      </c>
+      <c r="E71" s="6">
+        <v>1033455.88</v>
+      </c>
+      <c r="F71" s="6">
         <v>987548.81</v>
       </c>
-      <c r="E70" s="6">
+      <c r="G71" s="6">
         <v>2887433.54</v>
       </c>
-      <c r="F70" s="6">
+      <c r="H71" s="6">
         <v>3042047.61</v>
       </c>
-      <c r="G70" s="7">
+      <c r="I71" s="7">
         <v>5929481.1500000004</v>
       </c>
     </row>
-    <row r="71" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B71" s="4">
-        <v>4631</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" s="6">
-        <v>535779525.63</v>
-      </c>
-      <c r="E71" s="6">
-        <v>0</v>
-      </c>
-      <c r="F71" s="6">
-        <v>35286533.509999998</v>
-      </c>
-      <c r="G71" s="7">
-        <v>35286533.509999998</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>2025</v>
       </c>
@@ -2279,22 +2698,28 @@
         <v>4691</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D72" s="6">
+        <v>64705464.399999999</v>
+      </c>
+      <c r="E72" s="6">
+        <v>14436749.82</v>
+      </c>
+      <c r="F72" s="6">
         <v>9663966.0199999996</v>
       </c>
-      <c r="E72" s="6">
+      <c r="G72" s="6">
         <v>2093885.86</v>
       </c>
-      <c r="F72" s="6">
+      <c r="H72" s="6">
         <v>31330993.84</v>
       </c>
-      <c r="G72" s="7">
+      <c r="I72" s="7">
         <v>33424879.699999999</v>
       </c>
     </row>
-    <row r="73" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>2025</v>
       </c>
@@ -2302,22 +2727,28 @@
         <v>4701</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D73" s="6">
+        <v>2107186.39</v>
+      </c>
+      <c r="E73" s="6">
+        <v>781389.39</v>
+      </c>
+      <c r="F73" s="6">
         <v>754127.26</v>
       </c>
-      <c r="E73" s="6">
+      <c r="G73" s="6">
         <v>0</v>
       </c>
-      <c r="F73" s="6">
+      <c r="H73" s="6">
         <v>86523.72</v>
       </c>
-      <c r="G73" s="7">
+      <c r="I73" s="7">
         <v>86523.72</v>
       </c>
     </row>
-    <row r="74" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>2025</v>
       </c>
@@ -2325,22 +2756,28 @@
         <v>4711</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D74" s="6">
+        <v>18258352481.540001</v>
+      </c>
+      <c r="E74" s="6">
+        <v>18256651559.23</v>
+      </c>
+      <c r="F74" s="6">
         <v>18259071357.130001</v>
       </c>
-      <c r="E74" s="6">
+      <c r="G74" s="6">
         <v>46065.66</v>
       </c>
-      <c r="F74" s="6">
+      <c r="H74" s="6">
         <v>2149146.04</v>
       </c>
-      <c r="G74" s="7">
+      <c r="I74" s="7">
         <v>2195211.7000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:7" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="82">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -210,61 +210,61 @@
     <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
   </si>
   <si>
+    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DE HABITACAO</t>
+  </si>
+  <si>
+    <t>FUNDO PENITENCIARIO ESTADUAL</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DE SAUDE</t>
+  </si>
+  <si>
+    <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+  </si>
+  <si>
+    <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DE CULTURA</t>
+  </si>
+  <si>
+    <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
     <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE HABITACAO</t>
-  </si>
-  <si>
-    <t>FUNDO PENITENCIARIO ESTADUAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SAUDE</t>
-  </si>
-  <si>
-    <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
-  </si>
-  <si>
-    <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE CULTURA</t>
-  </si>
-  <si>
-    <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
   </si>
 </sst>
 </file>
@@ -636,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -680,7 +680,7 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B2" s="4">
         <v>1071</v>
@@ -689,27 +689,21 @@
         <v>9</v>
       </c>
       <c r="D2" s="6">
-        <v>55898902.780000001</v>
+        <v>39892772.32</v>
       </c>
       <c r="E2" s="6">
-        <v>34921981.439999998</v>
+        <v>35166360.520000003</v>
       </c>
       <c r="F2" s="6">
-        <v>32307667.050000001</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>4293686.1900000004</v>
-      </c>
-      <c r="I2" s="7">
-        <v>4293686.1900000004</v>
-      </c>
+        <v>34432753.310000002</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B3" s="4">
         <v>1081</v>
@@ -718,27 +712,21 @@
         <v>10</v>
       </c>
       <c r="D3" s="6">
-        <v>1023743951.58</v>
+        <v>1176383140.29</v>
       </c>
       <c r="E3" s="6">
-        <v>1014541849.87</v>
+        <v>1169049193.7</v>
       </c>
       <c r="F3" s="6">
-        <v>759567117.26999998</v>
-      </c>
-      <c r="G3" s="6">
-        <v>11357399.470000001</v>
-      </c>
-      <c r="H3" s="6">
-        <v>2680004.75</v>
-      </c>
-      <c r="I3" s="7">
-        <v>14037404.220000001</v>
-      </c>
+        <v>1101390201.9200001</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B4" s="4">
         <v>1101</v>
@@ -747,27 +735,21 @@
         <v>11</v>
       </c>
       <c r="D4" s="6">
-        <v>18048368.199999999</v>
+        <v>16775084.75</v>
       </c>
       <c r="E4" s="6">
-        <v>17928588.510000002</v>
+        <v>16686029.560000001</v>
       </c>
       <c r="F4" s="6">
-        <v>17774694.27</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
-        <v>57114.59</v>
-      </c>
-      <c r="I4" s="7">
-        <v>57114.59</v>
-      </c>
+        <v>16501107.08</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B5" s="4">
         <v>1191</v>
@@ -776,27 +758,21 @@
         <v>12</v>
       </c>
       <c r="D5" s="6">
-        <v>1886784188.8099999</v>
+        <v>1774005537.77</v>
       </c>
       <c r="E5" s="6">
-        <v>1792612515.5899999</v>
+        <v>1675743095.8699999</v>
       </c>
       <c r="F5" s="6">
-        <v>1767643635.4300001</v>
-      </c>
-      <c r="G5" s="6">
-        <v>5956448.8899999997</v>
-      </c>
-      <c r="H5" s="6">
-        <v>38130787.079999998</v>
-      </c>
-      <c r="I5" s="7">
-        <v>44087235.969999999</v>
-      </c>
+        <v>1655219211.46</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B6" s="4">
         <v>1221</v>
@@ -805,27 +781,21 @@
         <v>13</v>
       </c>
       <c r="D6" s="6">
-        <v>425928118.32999998</v>
+        <v>73450042.359999999</v>
       </c>
       <c r="E6" s="6">
-        <v>106813200.90000001</v>
+        <v>68755382.680000007</v>
       </c>
       <c r="F6" s="6">
-        <v>104972627.41</v>
-      </c>
-      <c r="G6" s="6">
-        <v>3819.55</v>
-      </c>
-      <c r="H6" s="6">
-        <v>10240167.34</v>
-      </c>
-      <c r="I6" s="7">
-        <v>10243986.890000001</v>
-      </c>
+        <v>67360741.430000007</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B7" s="4">
         <v>1231</v>
@@ -834,27 +804,21 @@
         <v>14</v>
       </c>
       <c r="D7" s="6">
-        <v>319941879.06999999</v>
+        <v>144310208.36000001</v>
       </c>
       <c r="E7" s="6">
-        <v>286029024.67000002</v>
+        <v>121768607.78</v>
       </c>
       <c r="F7" s="6">
-        <v>275453889.56</v>
-      </c>
-      <c r="G7" s="6">
-        <v>4468309.21</v>
-      </c>
-      <c r="H7" s="6">
-        <v>18499399.920000002</v>
-      </c>
-      <c r="I7" s="7">
-        <v>22967709.129999999</v>
-      </c>
+        <v>115667927.76000001</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B8" s="4">
         <v>1251</v>
@@ -863,27 +827,21 @@
         <v>15</v>
       </c>
       <c r="D8" s="6">
-        <v>17184629357.540001</v>
+        <v>14358949915.030001</v>
       </c>
       <c r="E8" s="6">
-        <v>16913388822.07</v>
+        <v>14172994593.1</v>
       </c>
       <c r="F8" s="6">
-        <v>16881355805.92</v>
-      </c>
-      <c r="G8" s="6">
-        <v>22568008.23</v>
-      </c>
-      <c r="H8" s="6">
-        <v>179457677.69</v>
-      </c>
-      <c r="I8" s="7">
-        <v>202025685.91999999</v>
-      </c>
+        <v>14136708514.629999</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="4">
         <v>1261</v>
@@ -892,27 +850,21 @@
         <v>16</v>
       </c>
       <c r="D9" s="6">
-        <v>20024070516.279999</v>
+        <v>19265871510.98</v>
       </c>
       <c r="E9" s="6">
-        <v>19817333122</v>
+        <v>18803285393.110001</v>
       </c>
       <c r="F9" s="6">
-        <v>19583419698.990002</v>
-      </c>
-      <c r="G9" s="6">
-        <v>102690852.14</v>
-      </c>
-      <c r="H9" s="6">
-        <v>437921985.25</v>
-      </c>
-      <c r="I9" s="7">
-        <v>540612837.38999999</v>
-      </c>
+        <v>18714498875.099998</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B10" s="4">
         <v>1271</v>
@@ -921,27 +873,21 @@
         <v>17</v>
       </c>
       <c r="D10" s="6">
-        <v>261449910.33000001</v>
+        <v>278574229.64999998</v>
       </c>
       <c r="E10" s="6">
-        <v>260070135.18000001</v>
+        <v>275244209.69</v>
       </c>
       <c r="F10" s="6">
-        <v>257629551.13</v>
-      </c>
-      <c r="G10" s="6">
-        <v>2520</v>
-      </c>
-      <c r="H10" s="6">
-        <v>2485549.7200000002</v>
-      </c>
-      <c r="I10" s="7">
-        <v>2488069.7200000002</v>
-      </c>
+        <v>272306597.25999999</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B11" s="4">
         <v>1301</v>
@@ -950,27 +896,21 @@
         <v>18</v>
       </c>
       <c r="D11" s="6">
-        <v>480636059.57999998</v>
+        <v>739415330.30999994</v>
       </c>
       <c r="E11" s="6">
-        <v>393222333.81</v>
+        <v>535038118.5</v>
       </c>
       <c r="F11" s="6">
-        <v>363896390.25999999</v>
-      </c>
-      <c r="G11" s="6">
-        <v>11727528.060000001</v>
-      </c>
-      <c r="H11" s="6">
-        <v>201174882.84999999</v>
-      </c>
-      <c r="I11" s="7">
-        <v>212902410.91</v>
-      </c>
+        <v>520804921.24000001</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B12" s="4">
         <v>1371</v>
@@ -979,27 +919,21 @@
         <v>19</v>
       </c>
       <c r="D12" s="6">
-        <v>185286819.99000001</v>
+        <v>184730264.22999999</v>
       </c>
       <c r="E12" s="6">
-        <v>178437283.68000001</v>
+        <v>174620059.84999999</v>
       </c>
       <c r="F12" s="6">
-        <v>172648640.16</v>
-      </c>
-      <c r="G12" s="6">
-        <v>271467.65000000002</v>
-      </c>
-      <c r="H12" s="6">
-        <v>5465504.5800000001</v>
-      </c>
-      <c r="I12" s="7">
-        <v>5736972.2300000004</v>
-      </c>
+        <v>171768182.38999999</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B13" s="4">
         <v>1401</v>
@@ -1008,27 +942,21 @@
         <v>20</v>
       </c>
       <c r="D13" s="6">
-        <v>2074027252.0699999</v>
+        <v>1689247203.3900001</v>
       </c>
       <c r="E13" s="6">
-        <v>1999073232.1300001</v>
+        <v>1633624349.8599999</v>
       </c>
       <c r="F13" s="6">
-        <v>1988491760.28</v>
-      </c>
-      <c r="G13" s="6">
-        <v>4678551.78</v>
-      </c>
-      <c r="H13" s="6">
-        <v>71714800.709999993</v>
-      </c>
-      <c r="I13" s="7">
-        <v>76393352.489999995</v>
-      </c>
+        <v>1628884534.1500001</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B14" s="4">
         <v>1451</v>
@@ -1037,27 +965,21 @@
         <v>21</v>
       </c>
       <c r="D14" s="6">
-        <v>4556477829.6899996</v>
+        <v>4151305223.1199999</v>
       </c>
       <c r="E14" s="6">
-        <v>4357599952.2399998</v>
+        <v>4013226715.0500002</v>
       </c>
       <c r="F14" s="6">
-        <v>4322020545.1700001</v>
-      </c>
-      <c r="G14" s="6">
-        <v>4833097.2</v>
-      </c>
-      <c r="H14" s="6">
-        <v>108147895.72</v>
-      </c>
-      <c r="I14" s="7">
-        <v>112980992.92</v>
-      </c>
+        <v>3984233963.5300002</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B15" s="4">
         <v>1481</v>
@@ -1066,27 +988,21 @@
         <v>22</v>
       </c>
       <c r="D15" s="6">
-        <v>338412512.00999999</v>
+        <v>192351891.56999999</v>
       </c>
       <c r="E15" s="6">
-        <v>284330922.13999999</v>
+        <v>161820266.28</v>
       </c>
       <c r="F15" s="6">
-        <v>273376533.99000001</v>
-      </c>
-      <c r="G15" s="6">
-        <v>6492833.4299999997</v>
-      </c>
-      <c r="H15" s="6">
-        <v>13954481.02</v>
-      </c>
-      <c r="I15" s="7">
-        <v>20447314.449999999</v>
-      </c>
+        <v>151442671.16</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B16" s="4">
         <v>1491</v>
@@ -1095,27 +1011,21 @@
         <v>23</v>
       </c>
       <c r="D16" s="6">
-        <v>971196665.48000002</v>
+        <v>936918721.66999996</v>
       </c>
       <c r="E16" s="6">
-        <v>965761230.42999995</v>
+        <v>903588865.71000004</v>
       </c>
       <c r="F16" s="6">
-        <v>950181400.99000001</v>
-      </c>
-      <c r="G16" s="6">
-        <v>1028658.15</v>
-      </c>
-      <c r="H16" s="6">
-        <v>17535020.600000001</v>
-      </c>
-      <c r="I16" s="7">
-        <v>18563678.75</v>
-      </c>
+        <v>899254287.63999999</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B17" s="4">
         <v>1501</v>
@@ -1124,27 +1034,21 @@
         <v>24</v>
       </c>
       <c r="D17" s="6">
-        <v>940771355.50999999</v>
+        <v>855546794.05999994</v>
       </c>
       <c r="E17" s="6">
-        <v>840171011.04999995</v>
+        <v>760671962.16999996</v>
       </c>
       <c r="F17" s="6">
-        <v>779489331.71000004</v>
-      </c>
-      <c r="G17" s="6">
-        <v>9145522.5999999996</v>
-      </c>
-      <c r="H17" s="6">
-        <v>62616118.700000003</v>
-      </c>
-      <c r="I17" s="7">
-        <v>71761641.299999997</v>
-      </c>
+        <v>719982759.67999995</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B18" s="4">
         <v>1511</v>
@@ -1153,27 +1057,21 @@
         <v>25</v>
       </c>
       <c r="D18" s="6">
-        <v>3138279917.0599999</v>
+        <v>2971107807.8499999</v>
       </c>
       <c r="E18" s="6">
-        <v>3076106533.5700002</v>
+        <v>2911787285.4699998</v>
       </c>
       <c r="F18" s="6">
-        <v>3055981056.6799998</v>
-      </c>
-      <c r="G18" s="6">
-        <v>18355346.550000001</v>
-      </c>
-      <c r="H18" s="6">
-        <v>41103215.43</v>
-      </c>
-      <c r="I18" s="7">
-        <v>59458561.979999997</v>
-      </c>
+        <v>2882948197.5799999</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B19" s="4">
         <v>1521</v>
@@ -1182,27 +1080,21 @@
         <v>26</v>
       </c>
       <c r="D19" s="6">
-        <v>70667226.109999999</v>
+        <v>67525357.700000003</v>
       </c>
       <c r="E19" s="6">
-        <v>69307261.739999995</v>
+        <v>66249891.549999997</v>
       </c>
       <c r="F19" s="6">
-        <v>69083242.060000002</v>
-      </c>
-      <c r="G19" s="6">
-        <v>39281.15</v>
-      </c>
-      <c r="H19" s="6">
-        <v>907780.5</v>
-      </c>
-      <c r="I19" s="7">
-        <v>947061.65</v>
-      </c>
+        <v>66020996.240000002</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B20" s="4">
         <v>1541</v>
@@ -1211,27 +1103,21 @@
         <v>27</v>
       </c>
       <c r="D20" s="6">
-        <v>25352006.23</v>
+        <v>21259443.359999999</v>
       </c>
       <c r="E20" s="6">
-        <v>23581392.719999999</v>
+        <v>20594781.940000001</v>
       </c>
       <c r="F20" s="6">
-        <v>22865578.489999998</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
-        <v>351886.66</v>
-      </c>
-      <c r="I20" s="7">
-        <v>351886.66</v>
-      </c>
+        <v>20198969.09</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B21" s="4">
         <v>1631</v>
@@ -1240,27 +1126,21 @@
         <v>28</v>
       </c>
       <c r="D21" s="6">
-        <v>12493555.880000001</v>
+        <v>9422516.7100000009</v>
       </c>
       <c r="E21" s="6">
-        <v>12400512.789999999</v>
+        <v>9269804.5999999996</v>
       </c>
       <c r="F21" s="6">
-        <v>12257285.880000001</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
-        <v>138983.67999999999</v>
-      </c>
-      <c r="I21" s="7">
-        <v>138983.67999999999</v>
-      </c>
+        <v>9157892.9600000009</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B22" s="4">
         <v>1711</v>
@@ -1269,27 +1149,21 @@
         <v>29</v>
       </c>
       <c r="D22" s="6">
-        <v>181181663.88</v>
+        <v>145415971.84</v>
       </c>
       <c r="E22" s="6">
-        <v>101620737.73999999</v>
+        <v>57212986.340000004</v>
       </c>
       <c r="F22" s="6">
-        <v>97019401.540000007</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6">
-        <v>76618911.299999997</v>
-      </c>
-      <c r="I22" s="7">
-        <v>76618911.299999997</v>
-      </c>
+        <v>54811118.270000003</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B23" s="4">
         <v>1721</v>
@@ -1298,27 +1172,21 @@
         <v>30</v>
       </c>
       <c r="D23" s="6">
-        <v>10652572.939999999</v>
+        <v>11376822.58</v>
       </c>
       <c r="E23" s="6">
-        <v>10295525.119999999</v>
+        <v>10825343.529999999</v>
       </c>
       <c r="F23" s="6">
-        <v>9939287.6500000004</v>
-      </c>
-      <c r="G23" s="6">
-        <v>10152.64</v>
-      </c>
-      <c r="H23" s="6">
-        <v>276281.69</v>
-      </c>
-      <c r="I23" s="7">
-        <v>286434.33</v>
-      </c>
+        <v>10646102.960000001</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B24" s="4">
         <v>1911</v>
@@ -1327,27 +1195,21 @@
         <v>31</v>
       </c>
       <c r="D24" s="6">
-        <v>1211264345.4300001</v>
+        <v>1542024334.1800001</v>
       </c>
       <c r="E24" s="6">
-        <v>1127569424.8</v>
+        <v>1424388867.28</v>
       </c>
       <c r="F24" s="6">
-        <v>1127569424.8</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
-        <v>70456474.189999998</v>
-      </c>
-      <c r="I24" s="7">
-        <v>70456474.189999998</v>
-      </c>
+        <v>1424388867.28</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B25" s="4">
         <v>1915</v>
@@ -1356,27 +1218,21 @@
         <v>32</v>
       </c>
       <c r="D25" s="6">
-        <v>20043002.559999999</v>
+        <v>77370454.079999998</v>
       </c>
       <c r="E25" s="6">
-        <v>20043002.559999999</v>
+        <v>77346508.569999993</v>
       </c>
       <c r="F25" s="6">
-        <v>20043002.559999999</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <v>46.77</v>
-      </c>
-      <c r="I25" s="7">
-        <v>46.77</v>
-      </c>
+        <v>77346508.569999993</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B26" s="4">
         <v>1916</v>
@@ -1385,27 +1241,21 @@
         <v>33</v>
       </c>
       <c r="D26" s="6">
-        <v>6570721631.0600004</v>
+        <v>3797673691.6900001</v>
       </c>
       <c r="E26" s="6">
-        <v>6570721631.0600004</v>
+        <v>3797673691.6900001</v>
       </c>
       <c r="F26" s="6">
-        <v>6497797081.6999998</v>
-      </c>
-      <c r="G26" s="6">
-        <v>260833467.16</v>
-      </c>
-      <c r="H26" s="6">
-        <v>0</v>
-      </c>
-      <c r="I26" s="7">
-        <v>260833467.16</v>
-      </c>
+        <v>3525271258.0100002</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B27" s="4">
         <v>1941</v>
@@ -1414,27 +1264,21 @@
         <v>34</v>
       </c>
       <c r="D27" s="6">
-        <v>194535650.21000001</v>
+        <v>198068287.50999999</v>
       </c>
       <c r="E27" s="6">
-        <v>193268761.55000001</v>
+        <v>195102654.49000001</v>
       </c>
       <c r="F27" s="6">
-        <v>193178812.25</v>
-      </c>
-      <c r="G27" s="6">
-        <v>27888.27</v>
-      </c>
-      <c r="H27" s="6">
-        <v>1669467.18</v>
-      </c>
-      <c r="I27" s="7">
-        <v>1697355.45</v>
-      </c>
+        <v>195045661.81</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B28" s="4">
         <v>2011</v>
@@ -1443,27 +1287,21 @@
         <v>35</v>
       </c>
       <c r="D28" s="6">
-        <v>2066687330.24</v>
+        <v>1725474955.8</v>
       </c>
       <c r="E28" s="6">
-        <v>1811898139.4000001</v>
+        <v>1598962422.8800001</v>
       </c>
       <c r="F28" s="6">
-        <v>1767628149.6600001</v>
-      </c>
-      <c r="G28" s="6">
-        <v>1062515.58</v>
-      </c>
-      <c r="H28" s="6">
-        <v>92904525.540000007</v>
-      </c>
-      <c r="I28" s="7">
-        <v>93967041.120000005</v>
-      </c>
+        <v>1555299505.74</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B29" s="4">
         <v>2041</v>
@@ -1472,27 +1310,21 @@
         <v>36</v>
       </c>
       <c r="D29" s="6">
-        <v>2901561.62</v>
+        <v>2753285.11</v>
       </c>
       <c r="E29" s="6">
-        <v>2865088.76</v>
+        <v>2718960.43</v>
       </c>
       <c r="F29" s="6">
-        <v>2860275.95</v>
-      </c>
-      <c r="G29" s="6">
-        <v>3394.97</v>
-      </c>
-      <c r="H29" s="6">
-        <v>24471.67</v>
-      </c>
-      <c r="I29" s="7">
-        <v>27866.639999999999</v>
-      </c>
+        <v>2712294.25</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B30" s="4">
         <v>2061</v>
@@ -1501,27 +1333,21 @@
         <v>37</v>
       </c>
       <c r="D30" s="6">
-        <v>70806633.620000005</v>
+        <v>69147295.900000006</v>
       </c>
       <c r="E30" s="6">
-        <v>68325905.25</v>
+        <v>66097932.409999996</v>
       </c>
       <c r="F30" s="6">
-        <v>67044604.869999997</v>
-      </c>
-      <c r="G30" s="6">
-        <v>11590.87</v>
-      </c>
-      <c r="H30" s="6">
-        <v>1026935.64</v>
-      </c>
-      <c r="I30" s="7">
-        <v>1038526.51</v>
-      </c>
+        <v>64809217.450000003</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B31" s="4">
         <v>2071</v>
@@ -1530,27 +1356,21 @@
         <v>38</v>
       </c>
       <c r="D31" s="6">
-        <v>585603048.33000004</v>
+        <v>533594583.23000002</v>
       </c>
       <c r="E31" s="6">
-        <v>580710591.19000006</v>
+        <v>523602791.54000002</v>
       </c>
       <c r="F31" s="6">
-        <v>574854711.53999996</v>
-      </c>
-      <c r="G31" s="6">
-        <v>1239266.23</v>
-      </c>
-      <c r="H31" s="6">
-        <v>8506819.6199999992</v>
-      </c>
-      <c r="I31" s="7">
-        <v>9746085.8499999996</v>
-      </c>
+        <v>524266165.17000002</v>
+      </c>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B32" s="4">
         <v>2091</v>
@@ -1559,27 +1379,21 @@
         <v>39</v>
       </c>
       <c r="D32" s="6">
-        <v>75621728.879999995</v>
+        <v>63780232.719999999</v>
       </c>
       <c r="E32" s="6">
-        <v>74134505.909999996</v>
+        <v>61454087.810000002</v>
       </c>
       <c r="F32" s="6">
-        <v>72540998.400000006</v>
-      </c>
-      <c r="G32" s="6">
-        <v>24329.43</v>
-      </c>
-      <c r="H32" s="6">
-        <v>2347292.71</v>
-      </c>
-      <c r="I32" s="7">
-        <v>2371622.14</v>
-      </c>
+        <v>60658393.880000003</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B33" s="4">
         <v>2101</v>
@@ -1588,27 +1402,21 @@
         <v>40</v>
       </c>
       <c r="D33" s="6">
-        <v>217212201.81999999</v>
+        <v>217344980.62</v>
       </c>
       <c r="E33" s="6">
-        <v>204765475.80000001</v>
+        <v>207079100.46000001</v>
       </c>
       <c r="F33" s="6">
-        <v>196759897.63</v>
-      </c>
-      <c r="G33" s="6">
-        <v>1333045.2</v>
-      </c>
-      <c r="H33" s="6">
-        <v>7655898.75</v>
-      </c>
-      <c r="I33" s="7">
-        <v>8988943.9499999993</v>
-      </c>
+        <v>198091936.58000001</v>
+      </c>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B34" s="4">
         <v>2121</v>
@@ -1617,27 +1425,21 @@
         <v>41</v>
       </c>
       <c r="D34" s="6">
-        <v>3302390465.79</v>
+        <v>3010650321.5900002</v>
       </c>
       <c r="E34" s="6">
-        <v>3251209178.8699999</v>
+        <v>2990182081.1199999</v>
       </c>
       <c r="F34" s="6">
-        <v>3202602086.9200001</v>
-      </c>
-      <c r="G34" s="6">
-        <v>294911.07</v>
-      </c>
-      <c r="H34" s="6">
-        <v>15606900.02</v>
-      </c>
-      <c r="I34" s="7">
-        <v>15901811.09</v>
-      </c>
+        <v>2961013745.75</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B35" s="4">
         <v>2151</v>
@@ -1646,27 +1448,21 @@
         <v>42</v>
       </c>
       <c r="D35" s="6">
-        <v>81750398.859999999</v>
+        <v>88180552.390000001</v>
       </c>
       <c r="E35" s="6">
-        <v>76284993.930000007</v>
+        <v>80251235.980000004</v>
       </c>
       <c r="F35" s="6">
-        <v>75483300.689999998</v>
-      </c>
-      <c r="G35" s="6">
-        <v>24887.1</v>
-      </c>
-      <c r="H35" s="6">
-        <v>1770214.54</v>
-      </c>
-      <c r="I35" s="7">
-        <v>1795101.64</v>
-      </c>
+        <v>78333556.760000005</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B36" s="4">
         <v>2161</v>
@@ -1675,27 +1471,21 @@
         <v>43</v>
       </c>
       <c r="D36" s="6">
-        <v>6356895.04</v>
+        <v>8462182.1600000001</v>
       </c>
       <c r="E36" s="6">
-        <v>5950697.5800000001</v>
+        <v>7716382.4500000002</v>
       </c>
       <c r="F36" s="6">
-        <v>5865105.7800000003</v>
-      </c>
-      <c r="G36" s="6">
-        <v>0</v>
-      </c>
-      <c r="H36" s="6">
-        <v>416373.16</v>
-      </c>
-      <c r="I36" s="7">
-        <v>416373.16</v>
-      </c>
+        <v>7622126.71</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B37" s="4">
         <v>2171</v>
@@ -1704,27 +1494,21 @@
         <v>44</v>
       </c>
       <c r="D37" s="6">
-        <v>9439748.6199999992</v>
+        <v>7941833.3700000001</v>
       </c>
       <c r="E37" s="6">
-        <v>9225890.4000000004</v>
+        <v>7516887.29</v>
       </c>
       <c r="F37" s="6">
-        <v>8465439.7200000007</v>
-      </c>
-      <c r="G37" s="6">
-        <v>480546.01</v>
-      </c>
-      <c r="H37" s="6">
-        <v>177676.07</v>
-      </c>
-      <c r="I37" s="7">
-        <v>658222.07999999996</v>
-      </c>
+        <v>6813631.04</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B38" s="4">
         <v>2181</v>
@@ -1733,27 +1517,21 @@
         <v>45</v>
       </c>
       <c r="D38" s="6">
-        <v>63217552.93</v>
+        <v>61200638.609999999</v>
       </c>
       <c r="E38" s="6">
-        <v>60940567.950000003</v>
+        <v>58218035.710000001</v>
       </c>
       <c r="F38" s="6">
-        <v>56959723.43</v>
-      </c>
-      <c r="G38" s="6">
-        <v>119258.05</v>
-      </c>
-      <c r="H38" s="6">
-        <v>2222004.25</v>
-      </c>
-      <c r="I38" s="7">
-        <v>2341262.2999999998</v>
-      </c>
+        <v>55031527.640000001</v>
+      </c>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B39" s="4">
         <v>2201</v>
@@ -1762,27 +1540,21 @@
         <v>46</v>
       </c>
       <c r="D39" s="6">
-        <v>28359171.850000001</v>
+        <v>32151361.800000001</v>
       </c>
       <c r="E39" s="6">
-        <v>27321777.399999999</v>
+        <v>29851278.469999999</v>
       </c>
       <c r="F39" s="6">
-        <v>25220175.309999999</v>
-      </c>
-      <c r="G39" s="6">
-        <v>6473.82</v>
-      </c>
-      <c r="H39" s="6">
-        <v>1262449.1299999999</v>
-      </c>
-      <c r="I39" s="7">
-        <v>1268922.95</v>
-      </c>
+        <v>27723914.949999999</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B40" s="4">
         <v>2211</v>
@@ -1791,27 +1563,21 @@
         <v>47</v>
       </c>
       <c r="D40" s="6">
-        <v>16376327.77</v>
+        <v>18099484.140000001</v>
       </c>
       <c r="E40" s="6">
-        <v>15665660.91</v>
+        <v>16714066.1</v>
       </c>
       <c r="F40" s="6">
-        <v>14963532.880000001</v>
-      </c>
-      <c r="G40" s="6">
-        <v>84375.35</v>
-      </c>
-      <c r="H40" s="6">
-        <v>903154.46</v>
-      </c>
-      <c r="I40" s="7">
-        <v>987529.81</v>
-      </c>
+        <v>15905442.439999999</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B41" s="4">
         <v>2241</v>
@@ -1820,27 +1586,21 @@
         <v>48</v>
       </c>
       <c r="D41" s="6">
-        <v>195257062.84999999</v>
+        <v>163783014.55000001</v>
       </c>
       <c r="E41" s="6">
-        <v>182522813.41</v>
+        <v>159345489.81</v>
       </c>
       <c r="F41" s="6">
-        <v>181974009.41</v>
-      </c>
-      <c r="G41" s="6">
-        <v>10483113.83</v>
-      </c>
-      <c r="H41" s="6">
-        <v>1680822.65</v>
-      </c>
-      <c r="I41" s="7">
-        <v>12163936.48</v>
-      </c>
+        <v>158705842.44</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B42" s="4">
         <v>2251</v>
@@ -1849,27 +1609,21 @@
         <v>49</v>
       </c>
       <c r="D42" s="6">
-        <v>41105200.07</v>
+        <v>34101030</v>
       </c>
       <c r="E42" s="6">
-        <v>38759738.469999999</v>
+        <v>32049801.809999999</v>
       </c>
       <c r="F42" s="6">
-        <v>36259002.32</v>
-      </c>
-      <c r="G42" s="6">
-        <v>0</v>
-      </c>
-      <c r="H42" s="6">
-        <v>1415037.52</v>
-      </c>
-      <c r="I42" s="7">
-        <v>1415037.52</v>
-      </c>
+        <v>31364550.07</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B43" s="4">
         <v>2261</v>
@@ -1878,27 +1632,21 @@
         <v>50</v>
       </c>
       <c r="D43" s="6">
-        <v>553211607.35000002</v>
+        <v>617079458.69000006</v>
       </c>
       <c r="E43" s="6">
-        <v>369463545.18000001</v>
+        <v>457880133.86000001</v>
       </c>
       <c r="F43" s="6">
-        <v>355249323.07999998</v>
-      </c>
-      <c r="G43" s="6">
-        <v>38687418.560000002</v>
-      </c>
-      <c r="H43" s="6">
-        <v>130773841.95</v>
-      </c>
-      <c r="I43" s="7">
-        <v>169461260.50999999</v>
-      </c>
+        <v>414275548.19</v>
+      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B44" s="4">
         <v>2271</v>
@@ -1907,27 +1655,21 @@
         <v>51</v>
       </c>
       <c r="D44" s="6">
-        <v>2478485587.5</v>
+        <v>2332862602.7199998</v>
       </c>
       <c r="E44" s="6">
-        <v>2347428600.4299998</v>
+        <v>2250096399.4099998</v>
       </c>
       <c r="F44" s="6">
-        <v>2300004443.9499998</v>
-      </c>
-      <c r="G44" s="6">
-        <v>18122531.300000001</v>
-      </c>
-      <c r="H44" s="6">
-        <v>63228349.740000002</v>
-      </c>
-      <c r="I44" s="7">
-        <v>81350881.040000007</v>
-      </c>
+        <v>2191298111.2800002</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B45" s="4">
         <v>2281</v>
@@ -1936,27 +1678,21 @@
         <v>52</v>
       </c>
       <c r="D45" s="6">
-        <v>7417117.2199999997</v>
+        <v>6571067.71</v>
       </c>
       <c r="E45" s="6">
-        <v>6859782.46</v>
+        <v>6006116.6900000004</v>
       </c>
       <c r="F45" s="6">
-        <v>6435691.9100000001</v>
-      </c>
-      <c r="G45" s="6">
-        <v>0</v>
-      </c>
-      <c r="H45" s="6">
-        <v>231057.02</v>
-      </c>
-      <c r="I45" s="7">
-        <v>231057.02</v>
-      </c>
+        <v>5621531.5899999999</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B46" s="4">
         <v>2301</v>
@@ -1965,27 +1701,21 @@
         <v>53</v>
       </c>
       <c r="D46" s="6">
-        <v>2143327357.7</v>
+        <v>2166907648.9699998</v>
       </c>
       <c r="E46" s="6">
-        <v>1655881609.23</v>
+        <v>1614406418.0699999</v>
       </c>
       <c r="F46" s="6">
-        <v>1611441301.3699999</v>
-      </c>
-      <c r="G46" s="6">
-        <v>14178677.35</v>
-      </c>
-      <c r="H46" s="6">
-        <v>411934193.73000002</v>
-      </c>
-      <c r="I46" s="7">
-        <v>426112871.07999998</v>
-      </c>
+        <v>1579074300.1199999</v>
+      </c>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B47" s="4">
         <v>2311</v>
@@ -1994,27 +1724,21 @@
         <v>54</v>
       </c>
       <c r="D47" s="6">
-        <v>533150763.61000001</v>
+        <v>499332522.39999998</v>
       </c>
       <c r="E47" s="6">
-        <v>503448723.24000001</v>
+        <v>462442399.38</v>
       </c>
       <c r="F47" s="6">
-        <v>492058770.58999997</v>
-      </c>
-      <c r="G47" s="6">
-        <v>274974.01</v>
-      </c>
-      <c r="H47" s="6">
-        <v>39010212.219999999</v>
-      </c>
-      <c r="I47" s="7">
-        <v>39285186.229999997</v>
-      </c>
+        <v>452206130.54000002</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B48" s="4">
         <v>2321</v>
@@ -2023,27 +1747,21 @@
         <v>55</v>
       </c>
       <c r="D48" s="6">
-        <v>394549598.81</v>
+        <v>393216438.36000001</v>
       </c>
       <c r="E48" s="6">
-        <v>359596023.43000001</v>
+        <v>350212418.49000001</v>
       </c>
       <c r="F48" s="6">
-        <v>346696259.17000002</v>
-      </c>
-      <c r="G48" s="6">
-        <v>1425788.73</v>
-      </c>
-      <c r="H48" s="6">
-        <v>30573782.129999999</v>
-      </c>
-      <c r="I48" s="7">
-        <v>31999570.859999999</v>
-      </c>
+        <v>340044994.94999999</v>
+      </c>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B49" s="4">
         <v>2331</v>
@@ -2052,27 +1770,21 @@
         <v>56</v>
       </c>
       <c r="D49" s="6">
-        <v>35739703.740000002</v>
+        <v>33811040.590000004</v>
       </c>
       <c r="E49" s="6">
-        <v>34318152.899999999</v>
+        <v>33218643.649999999</v>
       </c>
       <c r="F49" s="6">
-        <v>33074380.829999998</v>
-      </c>
-      <c r="G49" s="6">
-        <v>420781.11</v>
-      </c>
-      <c r="H49" s="6">
-        <v>436480.49</v>
-      </c>
-      <c r="I49" s="7">
-        <v>857261.6</v>
-      </c>
+        <v>31654005.09</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B50" s="4">
         <v>2351</v>
@@ -2081,27 +1793,21 @@
         <v>57</v>
       </c>
       <c r="D50" s="6">
-        <v>431560939.48000002</v>
+        <v>411019703.14999998</v>
       </c>
       <c r="E50" s="6">
-        <v>399364373.02999997</v>
+        <v>396207773.82999998</v>
       </c>
       <c r="F50" s="6">
-        <v>391027226.75999999</v>
-      </c>
-      <c r="G50" s="6">
-        <v>1690845.8</v>
-      </c>
-      <c r="H50" s="6">
-        <v>7591910.9699999997</v>
-      </c>
-      <c r="I50" s="7">
-        <v>9282756.7699999996</v>
-      </c>
+        <v>386312319.37</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B51" s="4">
         <v>2371</v>
@@ -2110,27 +1816,21 @@
         <v>58</v>
       </c>
       <c r="D51" s="6">
-        <v>290312222.92000002</v>
+        <v>281022284.81</v>
       </c>
       <c r="E51" s="6">
-        <v>283815022.33999997</v>
+        <v>272651863.27999997</v>
       </c>
       <c r="F51" s="6">
-        <v>282551558.48000002</v>
-      </c>
-      <c r="G51" s="6">
-        <v>654297.56999999995</v>
-      </c>
-      <c r="H51" s="6">
-        <v>7082912.7699999996</v>
-      </c>
-      <c r="I51" s="7">
-        <v>7737210.3399999999</v>
-      </c>
+        <v>271364090.08999997</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B52" s="4">
         <v>2421</v>
@@ -2139,27 +1839,21 @@
         <v>59</v>
       </c>
       <c r="D52" s="6">
-        <v>61510642.640000001</v>
+        <v>53824647.210000001</v>
       </c>
       <c r="E52" s="6">
-        <v>43124254.630000003</v>
+        <v>33871287.270000003</v>
       </c>
       <c r="F52" s="6">
-        <v>41282826.789999999</v>
-      </c>
-      <c r="G52" s="6">
-        <v>713315.27</v>
-      </c>
-      <c r="H52" s="6">
-        <v>7206237.1500000004</v>
-      </c>
-      <c r="I52" s="7">
-        <v>7919552.4199999999</v>
-      </c>
+        <v>32392034.260000002</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B53" s="4">
         <v>2431</v>
@@ -2168,27 +1862,21 @@
         <v>60</v>
       </c>
       <c r="D53" s="6">
-        <v>7932027.7699999996</v>
+        <v>8106389.7300000004</v>
       </c>
       <c r="E53" s="6">
-        <v>7756446.6299999999</v>
+        <v>6808154.4400000004</v>
       </c>
       <c r="F53" s="6">
-        <v>7297654.8799999999</v>
-      </c>
-      <c r="G53" s="6">
-        <v>45611.95</v>
-      </c>
-      <c r="H53" s="6">
-        <v>40582.82</v>
-      </c>
-      <c r="I53" s="7">
-        <v>86194.77</v>
-      </c>
+        <v>6635544.6699999999</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B54" s="4">
         <v>2441</v>
@@ -2197,27 +1885,21 @@
         <v>61</v>
       </c>
       <c r="D54" s="6">
-        <v>19031476.379999999</v>
+        <v>18320816.57</v>
       </c>
       <c r="E54" s="6">
-        <v>18693505.57</v>
+        <v>17901288.280000001</v>
       </c>
       <c r="F54" s="6">
-        <v>18533956.489999998</v>
-      </c>
-      <c r="G54" s="6">
-        <v>87975.15</v>
-      </c>
-      <c r="H54" s="6">
-        <v>226885.18</v>
-      </c>
-      <c r="I54" s="7">
-        <v>314860.33</v>
-      </c>
+        <v>17655954.739999998</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B55" s="4">
         <v>2461</v>
@@ -2226,42 +1908,36 @@
         <v>62</v>
       </c>
       <c r="D55" s="6">
-        <v>4789292.1100000003</v>
+        <v>4028221.25</v>
       </c>
       <c r="E55" s="6">
-        <v>3903632.02</v>
+        <v>3832188.55</v>
       </c>
       <c r="F55" s="6">
-        <v>3547153</v>
-      </c>
-      <c r="G55" s="6">
-        <v>13266.26</v>
-      </c>
-      <c r="H55" s="6">
-        <v>175463.15</v>
-      </c>
-      <c r="I55" s="7">
-        <v>188729.41</v>
-      </c>
+        <v>3637560.66</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B56" s="4">
-        <v>2471</v>
+        <v>3041</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>63</v>
       </c>
       <c r="D56" s="6">
-        <v>12995181.74</v>
+        <v>399961543.69</v>
       </c>
       <c r="E56" s="6">
-        <v>9545227.8000000007</v>
+        <v>399961543.69</v>
       </c>
       <c r="F56" s="6">
-        <v>9172117.3000000007</v>
+        <v>399961543.69</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -2269,22 +1945,22 @@
     </row>
     <row r="57" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B57" s="4">
-        <v>3041</v>
+        <v>3051</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D57" s="6">
-        <v>411646902.57999998</v>
+        <v>135695037.88</v>
       </c>
       <c r="E57" s="6">
-        <v>411646902.57999998</v>
+        <v>135695037.88</v>
       </c>
       <c r="F57" s="6">
-        <v>411646902.57999998</v>
+        <v>135695037.88</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -2292,22 +1968,22 @@
     </row>
     <row r="58" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B58" s="4">
-        <v>3051</v>
+        <v>4091</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D58" s="6">
-        <v>150702794.75999999</v>
+        <v>4781856.8899999997</v>
       </c>
       <c r="E58" s="6">
-        <v>150702794.75999999</v>
+        <v>1781856.89</v>
       </c>
       <c r="F58" s="6">
-        <v>150702794.75999999</v>
+        <v>1780610.81</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -2315,469 +1991,2011 @@
     </row>
     <row r="59" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B59" s="4">
-        <v>4091</v>
+        <v>4101</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>66</v>
       </c>
       <c r="D59" s="6">
-        <v>610536.65</v>
+        <v>17635213.699999999</v>
       </c>
       <c r="E59" s="6">
-        <v>323136.65999999997</v>
+        <v>17616149.93</v>
       </c>
       <c r="F59" s="6">
-        <v>323136.65999999997</v>
-      </c>
-      <c r="G59" s="6">
-        <v>0</v>
-      </c>
-      <c r="H59" s="6">
-        <v>2867068.53</v>
-      </c>
-      <c r="I59" s="7">
-        <v>2867068.53</v>
-      </c>
+        <v>16185012.279999999</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="7"/>
     </row>
     <row r="60" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B60" s="4">
-        <v>4101</v>
+        <v>4141</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>67</v>
       </c>
       <c r="D60" s="6">
-        <v>16870000</v>
+        <v>32022766.899999999</v>
       </c>
       <c r="E60" s="6">
-        <v>16870000</v>
+        <v>22913023.719999999</v>
       </c>
       <c r="F60" s="6">
-        <v>15570000</v>
-      </c>
-      <c r="G60" s="6">
-        <v>0</v>
-      </c>
-      <c r="H60" s="6">
-        <v>0</v>
-      </c>
-      <c r="I60" s="7">
-        <v>0</v>
-      </c>
+        <v>22137652.859999999</v>
+      </c>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B61" s="4">
-        <v>4141</v>
+        <v>4251</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D61" s="6">
-        <v>10407251.17</v>
+        <v>191504888.5</v>
       </c>
       <c r="E61" s="6">
-        <v>6488589.5</v>
+        <v>184497317.71000001</v>
       </c>
       <c r="F61" s="6">
-        <v>6364731.3399999999</v>
-      </c>
-      <c r="G61" s="6">
-        <v>747392.63</v>
-      </c>
-      <c r="H61" s="6">
-        <v>8034402.6799999997</v>
-      </c>
-      <c r="I61" s="7">
-        <v>8781795.3100000005</v>
-      </c>
+        <v>182485356.66999999</v>
+      </c>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="7"/>
     </row>
     <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B62" s="4">
-        <v>4251</v>
+        <v>4291</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D62" s="6">
-        <v>172407716.30000001</v>
+        <v>11829504614.639999</v>
       </c>
       <c r="E62" s="6">
-        <v>169951293.66999999</v>
+        <v>11406407458.040001</v>
       </c>
       <c r="F62" s="6">
-        <v>168474678.25999999</v>
-      </c>
-      <c r="G62" s="6">
-        <v>1112168.8899999999</v>
-      </c>
-      <c r="H62" s="6">
-        <v>5271380.07</v>
-      </c>
-      <c r="I62" s="7">
-        <v>6383548.96</v>
-      </c>
+        <v>11283113714.34</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B63" s="4">
-        <v>4291</v>
+        <v>4331</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>70</v>
       </c>
       <c r="D63" s="6">
-        <v>12684000278.799999</v>
+        <v>1041559.94</v>
       </c>
       <c r="E63" s="6">
-        <v>12066473764.49</v>
+        <v>823642.04</v>
       </c>
       <c r="F63" s="6">
-        <v>11940374576.379999</v>
-      </c>
-      <c r="G63" s="6">
-        <v>622978466.21000004</v>
-      </c>
-      <c r="H63" s="6">
-        <v>547393802.41999996</v>
-      </c>
-      <c r="I63" s="7">
-        <v>1170372268.6300001</v>
-      </c>
+        <v>813093.72</v>
+      </c>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="7"/>
     </row>
     <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B64" s="4">
-        <v>4331</v>
+        <v>4341</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D64" s="6">
-        <v>3035441.45</v>
+        <v>4415220.16</v>
       </c>
       <c r="E64" s="6">
-        <v>97428.45</v>
+        <v>3506542.63</v>
       </c>
       <c r="F64" s="6">
-        <v>93102.96</v>
-      </c>
-      <c r="G64" s="6">
-        <v>0</v>
-      </c>
-      <c r="H64" s="6">
-        <v>206186.42</v>
-      </c>
-      <c r="I64" s="7">
-        <v>206186.42</v>
-      </c>
+        <v>2790383.33</v>
+      </c>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="7"/>
     </row>
     <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B65" s="4">
-        <v>4341</v>
+        <v>4381</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D65" s="6">
-        <v>2288740.7400000002</v>
+        <v>121090271.58</v>
       </c>
       <c r="E65" s="6">
-        <v>1318579.3999999999</v>
+        <v>82874506.280000001</v>
       </c>
       <c r="F65" s="6">
-        <v>1060943.48</v>
-      </c>
-      <c r="G65" s="6">
-        <v>223487.09</v>
-      </c>
-      <c r="H65" s="6">
-        <v>548165.38</v>
-      </c>
-      <c r="I65" s="7">
-        <v>771652.47</v>
-      </c>
+        <v>79003714.810000002</v>
+      </c>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="7"/>
     </row>
     <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B66" s="4">
-        <v>4381</v>
+        <v>4451</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>73</v>
       </c>
       <c r="D66" s="6">
-        <v>127170575.95</v>
+        <v>14312560.43</v>
       </c>
       <c r="E66" s="6">
-        <v>102885370.45</v>
+        <v>8943123.6799999997</v>
       </c>
       <c r="F66" s="6">
-        <v>98080707.200000003</v>
-      </c>
-      <c r="G66" s="6">
-        <v>0</v>
-      </c>
-      <c r="H66" s="6">
-        <v>21378670.300000001</v>
-      </c>
-      <c r="I66" s="7">
-        <v>21378670.300000001</v>
-      </c>
+        <v>8217694.4000000004</v>
+      </c>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="7"/>
     </row>
     <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B67" s="4">
-        <v>4451</v>
+        <v>4491</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>74</v>
       </c>
       <c r="D67" s="6">
-        <v>48631312.579999998</v>
+        <v>5173333.28</v>
       </c>
       <c r="E67" s="6">
-        <v>11932319.970000001</v>
+        <v>5153333.28</v>
       </c>
       <c r="F67" s="6">
-        <v>11013107.33</v>
-      </c>
-      <c r="G67" s="6">
-        <v>679.54</v>
-      </c>
-      <c r="H67" s="6">
-        <v>8080205.7800000003</v>
-      </c>
-      <c r="I67" s="7">
-        <v>8080885.3200000003</v>
-      </c>
+        <v>3822182.56</v>
+      </c>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="7"/>
     </row>
     <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B68" s="4">
-        <v>4491</v>
+        <v>4541</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>75</v>
       </c>
       <c r="D68" s="6">
-        <v>2634653.3199999998</v>
+        <v>391438.2</v>
       </c>
       <c r="E68" s="6">
-        <v>2500037.94</v>
+        <v>305805.64</v>
       </c>
       <c r="F68" s="6">
-        <v>1882700.63</v>
-      </c>
-      <c r="G68" s="6">
-        <v>0</v>
-      </c>
-      <c r="H68" s="6">
-        <v>15394</v>
-      </c>
-      <c r="I68" s="7">
-        <v>15394</v>
-      </c>
+        <v>288797.78999999998</v>
+      </c>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="7"/>
     </row>
     <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B69" s="4">
-        <v>4541</v>
+        <v>4551</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D69" s="6">
-        <v>350405</v>
+        <v>239438177.06999999</v>
       </c>
       <c r="E69" s="6">
-        <v>318593.90999999997</v>
+        <v>238618171.81</v>
       </c>
       <c r="F69" s="6">
-        <v>300914.63</v>
-      </c>
-      <c r="G69" s="6">
-        <v>0</v>
-      </c>
-      <c r="H69" s="6">
-        <v>26392.47</v>
-      </c>
-      <c r="I69" s="7">
-        <v>26392.47</v>
-      </c>
+        <v>238609881.40000001</v>
+      </c>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="7"/>
     </row>
     <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B70" s="4">
-        <v>4551</v>
+        <v>4601</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>77</v>
       </c>
       <c r="D70" s="6">
-        <v>148883049.19999999</v>
+        <v>5060964</v>
       </c>
       <c r="E70" s="6">
-        <v>148355490.34</v>
+        <v>1670773.97</v>
       </c>
       <c r="F70" s="6">
-        <v>148348943.52000001</v>
-      </c>
-      <c r="G70" s="6">
-        <v>0</v>
-      </c>
-      <c r="H70" s="6">
-        <v>620005.26</v>
-      </c>
-      <c r="I70" s="7">
-        <v>620005.26</v>
-      </c>
+        <v>1595111.21</v>
+      </c>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="7"/>
     </row>
     <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B71" s="4">
-        <v>4601</v>
+        <v>4691</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D71" s="6">
-        <v>1473191.28</v>
+        <v>49389640.210000001</v>
       </c>
       <c r="E71" s="6">
-        <v>1033455.88</v>
+        <v>15901164.57</v>
       </c>
       <c r="F71" s="6">
-        <v>987548.81</v>
-      </c>
-      <c r="G71" s="6">
-        <v>2887433.54</v>
-      </c>
-      <c r="H71" s="6">
-        <v>3042047.61</v>
-      </c>
-      <c r="I71" s="7">
-        <v>5929481.1500000004</v>
-      </c>
+        <v>13533037.66</v>
+      </c>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="7"/>
     </row>
     <row r="72" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B72" s="4">
-        <v>4691</v>
+        <v>4701</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>79</v>
       </c>
       <c r="D72" s="6">
-        <v>64705464.399999999</v>
+        <v>1242375.3</v>
       </c>
       <c r="E72" s="6">
-        <v>14436749.82</v>
+        <v>921616.21</v>
       </c>
       <c r="F72" s="6">
-        <v>9663966.0199999996</v>
-      </c>
-      <c r="G72" s="6">
-        <v>2093885.86</v>
-      </c>
-      <c r="H72" s="6">
-        <v>31330993.84</v>
-      </c>
-      <c r="I72" s="7">
-        <v>33424879.699999999</v>
-      </c>
+        <v>921884.45</v>
+      </c>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="7"/>
     </row>
     <row r="73" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B73" s="4">
-        <v>4701</v>
+        <v>4711</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>80</v>
       </c>
       <c r="D73" s="6">
-        <v>2107186.39</v>
+        <v>17508957839.759998</v>
       </c>
       <c r="E73" s="6">
-        <v>781389.39</v>
+        <v>17468843822.73</v>
       </c>
       <c r="F73" s="6">
-        <v>754127.26</v>
-      </c>
-      <c r="G73" s="6">
-        <v>0</v>
-      </c>
-      <c r="H73" s="6">
-        <v>86523.72</v>
-      </c>
-      <c r="I73" s="7">
-        <v>86523.72</v>
-      </c>
+        <v>17473304282.389999</v>
+      </c>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="7"/>
     </row>
     <row r="74" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>2025</v>
       </c>
       <c r="B74" s="4">
+        <v>1071</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6">
+        <v>0</v>
+      </c>
+      <c r="H74" s="6">
+        <v>4293686.1900000004</v>
+      </c>
+      <c r="I74" s="7">
+        <v>4293686.1900000004</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B75" s="4">
+        <v>1081</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6">
+        <v>11357399.470000001</v>
+      </c>
+      <c r="H75" s="6">
+        <v>2680004.75</v>
+      </c>
+      <c r="I75" s="7">
+        <v>14037404.220000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B76" s="4">
+        <v>1101</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6">
+        <v>0</v>
+      </c>
+      <c r="H76" s="6">
+        <v>57114.59</v>
+      </c>
+      <c r="I76" s="7">
+        <v>57114.59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B77" s="4">
+        <v>1191</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6">
+        <v>5956448.8899999997</v>
+      </c>
+      <c r="H77" s="6">
+        <v>38130787.079999998</v>
+      </c>
+      <c r="I77" s="7">
+        <v>44087235.969999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B78" s="4">
+        <v>1221</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6">
+        <v>3819.55</v>
+      </c>
+      <c r="H78" s="6">
+        <v>10240167.34</v>
+      </c>
+      <c r="I78" s="7">
+        <v>10243986.890000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B79" s="4">
+        <v>1231</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6">
+        <v>4468309.21</v>
+      </c>
+      <c r="H79" s="6">
+        <v>18499399.920000002</v>
+      </c>
+      <c r="I79" s="7">
+        <v>22967709.129999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B80" s="4">
+        <v>1251</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6">
+        <v>22568008.23</v>
+      </c>
+      <c r="H80" s="6">
+        <v>179457677.69</v>
+      </c>
+      <c r="I80" s="7">
+        <v>202025685.91999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B81" s="4">
+        <v>1261</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6">
+        <v>102690852.14</v>
+      </c>
+      <c r="H81" s="6">
+        <v>437921985.25</v>
+      </c>
+      <c r="I81" s="7">
+        <v>540612837.38999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B82" s="4">
+        <v>1271</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6">
+        <v>2520</v>
+      </c>
+      <c r="H82" s="6">
+        <v>2485549.7200000002</v>
+      </c>
+      <c r="I82" s="7">
+        <v>2488069.7200000002</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B83" s="4">
+        <v>1301</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6">
+        <v>11727528.060000001</v>
+      </c>
+      <c r="H83" s="6">
+        <v>201174882.84999999</v>
+      </c>
+      <c r="I83" s="7">
+        <v>212902410.91</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B84" s="4">
+        <v>1371</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6">
+        <v>271467.65000000002</v>
+      </c>
+      <c r="H84" s="6">
+        <v>5465504.5800000001</v>
+      </c>
+      <c r="I84" s="7">
+        <v>5736972.2300000004</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B85" s="4">
+        <v>1401</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6">
+        <v>4678551.78</v>
+      </c>
+      <c r="H85" s="6">
+        <v>71714800.709999993</v>
+      </c>
+      <c r="I85" s="7">
+        <v>76393352.489999995</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B86" s="4">
+        <v>1451</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6">
+        <v>4833097.2</v>
+      </c>
+      <c r="H86" s="6">
+        <v>108147895.72</v>
+      </c>
+      <c r="I86" s="7">
+        <v>112980992.92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B87" s="4">
+        <v>1481</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6">
+        <v>6492833.4299999997</v>
+      </c>
+      <c r="H87" s="6">
+        <v>13954481.02</v>
+      </c>
+      <c r="I87" s="7">
+        <v>20447314.449999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B88" s="4">
+        <v>1491</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6">
+        <v>1028658.15</v>
+      </c>
+      <c r="H88" s="6">
+        <v>17535020.600000001</v>
+      </c>
+      <c r="I88" s="7">
+        <v>18563678.75</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B89" s="4">
+        <v>1501</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6">
+        <v>9145522.5999999996</v>
+      </c>
+      <c r="H89" s="6">
+        <v>62616118.700000003</v>
+      </c>
+      <c r="I89" s="7">
+        <v>71761641.299999997</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B90" s="4">
+        <v>1511</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6">
+        <v>18355346.550000001</v>
+      </c>
+      <c r="H90" s="6">
+        <v>41103215.43</v>
+      </c>
+      <c r="I90" s="7">
+        <v>59458561.979999997</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B91" s="4">
+        <v>1521</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6">
+        <v>39281.15</v>
+      </c>
+      <c r="H91" s="6">
+        <v>907780.5</v>
+      </c>
+      <c r="I91" s="7">
+        <v>947061.65</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B92" s="4">
+        <v>1541</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6">
+        <v>0</v>
+      </c>
+      <c r="H92" s="6">
+        <v>351886.66</v>
+      </c>
+      <c r="I92" s="7">
+        <v>351886.66</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B93" s="4">
+        <v>1631</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6">
+        <v>138983.67999999999</v>
+      </c>
+      <c r="I93" s="7">
+        <v>138983.67999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B94" s="4">
+        <v>1711</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6">
+        <v>76618911.299999997</v>
+      </c>
+      <c r="I94" s="7">
+        <v>76618911.299999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B95" s="4">
+        <v>1721</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6">
+        <v>10152.64</v>
+      </c>
+      <c r="H95" s="6">
+        <v>276281.69</v>
+      </c>
+      <c r="I95" s="7">
+        <v>286434.33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B96" s="4">
+        <v>1911</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6">
+        <v>0</v>
+      </c>
+      <c r="H96" s="6">
+        <v>70456474.189999998</v>
+      </c>
+      <c r="I96" s="7">
+        <v>70456474.189999998</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B97" s="4">
+        <v>1915</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6">
+        <v>0</v>
+      </c>
+      <c r="H97" s="6">
+        <v>46.77</v>
+      </c>
+      <c r="I97" s="7">
+        <v>46.77</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B98" s="4">
+        <v>1916</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6">
+        <v>260833467.16</v>
+      </c>
+      <c r="H98" s="6">
+        <v>0</v>
+      </c>
+      <c r="I98" s="7">
+        <v>260833467.16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B99" s="4">
+        <v>1941</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6">
+        <v>27888.27</v>
+      </c>
+      <c r="H99" s="6">
+        <v>1669467.18</v>
+      </c>
+      <c r="I99" s="7">
+        <v>1697355.45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B100" s="4">
+        <v>2011</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6">
+        <v>1062515.58</v>
+      </c>
+      <c r="H100" s="6">
+        <v>92904525.540000007</v>
+      </c>
+      <c r="I100" s="7">
+        <v>93967041.120000005</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B101" s="4">
+        <v>2041</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6">
+        <v>3394.97</v>
+      </c>
+      <c r="H101" s="6">
+        <v>24471.67</v>
+      </c>
+      <c r="I101" s="7">
+        <v>27866.639999999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B102" s="4">
+        <v>2061</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6">
+        <v>11590.87</v>
+      </c>
+      <c r="H102" s="6">
+        <v>1026935.64</v>
+      </c>
+      <c r="I102" s="7">
+        <v>1038526.51</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B103" s="4">
+        <v>2071</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6">
+        <v>1239266.23</v>
+      </c>
+      <c r="H103" s="6">
+        <v>8506819.6199999992</v>
+      </c>
+      <c r="I103" s="7">
+        <v>9746085.8499999996</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B104" s="4">
+        <v>2091</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6">
+        <v>24329.43</v>
+      </c>
+      <c r="H104" s="6">
+        <v>2347292.71</v>
+      </c>
+      <c r="I104" s="7">
+        <v>2371622.14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B105" s="4">
+        <v>2101</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6">
+        <v>1333045.2</v>
+      </c>
+      <c r="H105" s="6">
+        <v>7655898.75</v>
+      </c>
+      <c r="I105" s="7">
+        <v>8988943.9499999993</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B106" s="4">
+        <v>2121</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6">
+        <v>294911.07</v>
+      </c>
+      <c r="H106" s="6">
+        <v>15606900.02</v>
+      </c>
+      <c r="I106" s="7">
+        <v>15901811.09</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B107" s="4">
+        <v>2151</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6">
+        <v>24887.1</v>
+      </c>
+      <c r="H107" s="6">
+        <v>1770214.54</v>
+      </c>
+      <c r="I107" s="7">
+        <v>1795101.64</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B108" s="4">
+        <v>2161</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6">
+        <v>0</v>
+      </c>
+      <c r="H108" s="6">
+        <v>416373.16</v>
+      </c>
+      <c r="I108" s="7">
+        <v>416373.16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B109" s="4">
+        <v>2171</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6">
+        <v>480546.01</v>
+      </c>
+      <c r="H109" s="6">
+        <v>177676.07</v>
+      </c>
+      <c r="I109" s="7">
+        <v>658222.07999999996</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B110" s="4">
+        <v>2181</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6">
+        <v>119258.05</v>
+      </c>
+      <c r="H110" s="6">
+        <v>2222004.25</v>
+      </c>
+      <c r="I110" s="7">
+        <v>2341262.2999999998</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B111" s="4">
+        <v>2201</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="6">
+        <v>6473.82</v>
+      </c>
+      <c r="H111" s="6">
+        <v>1262449.1299999999</v>
+      </c>
+      <c r="I111" s="7">
+        <v>1268922.95</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B112" s="4">
+        <v>2211</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6">
+        <v>84375.35</v>
+      </c>
+      <c r="H112" s="6">
+        <v>903154.46</v>
+      </c>
+      <c r="I112" s="7">
+        <v>987529.81</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B113" s="4">
+        <v>2241</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="6">
+        <v>10483113.83</v>
+      </c>
+      <c r="H113" s="6">
+        <v>1680822.65</v>
+      </c>
+      <c r="I113" s="7">
+        <v>12163936.48</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B114" s="4">
+        <v>2251</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6">
+        <v>0</v>
+      </c>
+      <c r="H114" s="6">
+        <v>1415037.52</v>
+      </c>
+      <c r="I114" s="7">
+        <v>1415037.52</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B115" s="4">
+        <v>2261</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6">
+        <v>38687418.560000002</v>
+      </c>
+      <c r="H115" s="6">
+        <v>130773841.95</v>
+      </c>
+      <c r="I115" s="7">
+        <v>169461260.50999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B116" s="4">
+        <v>2271</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6">
+        <v>18122531.300000001</v>
+      </c>
+      <c r="H116" s="6">
+        <v>63228349.740000002</v>
+      </c>
+      <c r="I116" s="7">
+        <v>81350881.040000007</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B117" s="4">
+        <v>2281</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D117" s="6"/>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="6">
+        <v>0</v>
+      </c>
+      <c r="H117" s="6">
+        <v>231057.02</v>
+      </c>
+      <c r="I117" s="7">
+        <v>231057.02</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B118" s="4">
+        <v>2301</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6">
+        <v>14178677.35</v>
+      </c>
+      <c r="H118" s="6">
+        <v>411934193.73000002</v>
+      </c>
+      <c r="I118" s="7">
+        <v>426112871.07999998</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B119" s="4">
+        <v>2311</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6">
+        <v>274974.01</v>
+      </c>
+      <c r="H119" s="6">
+        <v>39010212.219999999</v>
+      </c>
+      <c r="I119" s="7">
+        <v>39285186.229999997</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B120" s="4">
+        <v>2321</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6">
+        <v>1425788.73</v>
+      </c>
+      <c r="H120" s="6">
+        <v>30573782.129999999</v>
+      </c>
+      <c r="I120" s="7">
+        <v>31999570.859999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B121" s="4">
+        <v>2331</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D121" s="6"/>
+      <c r="E121" s="6"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="6">
+        <v>420781.11</v>
+      </c>
+      <c r="H121" s="6">
+        <v>436480.49</v>
+      </c>
+      <c r="I121" s="7">
+        <v>857261.6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B122" s="4">
+        <v>2351</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6">
+        <v>1690845.8</v>
+      </c>
+      <c r="H122" s="6">
+        <v>7591910.9699999997</v>
+      </c>
+      <c r="I122" s="7">
+        <v>9282756.7699999996</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B123" s="4">
+        <v>2371</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D123" s="6"/>
+      <c r="E123" s="6"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="6">
+        <v>654297.56999999995</v>
+      </c>
+      <c r="H123" s="6">
+        <v>7082912.7699999996</v>
+      </c>
+      <c r="I123" s="7">
+        <v>7737210.3399999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B124" s="4">
+        <v>2421</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D124" s="6"/>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="6">
+        <v>713315.27</v>
+      </c>
+      <c r="H124" s="6">
+        <v>7206237.1500000004</v>
+      </c>
+      <c r="I124" s="7">
+        <v>7919552.4199999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B125" s="4">
+        <v>2431</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D125" s="6"/>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6">
+        <v>45611.95</v>
+      </c>
+      <c r="H125" s="6">
+        <v>40582.82</v>
+      </c>
+      <c r="I125" s="7">
+        <v>86194.77</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B126" s="4">
+        <v>2441</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6">
+        <v>87975.15</v>
+      </c>
+      <c r="H126" s="6">
+        <v>226885.18</v>
+      </c>
+      <c r="I126" s="7">
+        <v>314860.33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B127" s="4">
+        <v>2461</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6">
+        <v>13266.26</v>
+      </c>
+      <c r="H127" s="6">
+        <v>175463.15</v>
+      </c>
+      <c r="I127" s="7">
+        <v>188729.41</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B128" s="4">
+        <v>2471</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="7"/>
+    </row>
+    <row r="129" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B129" s="4">
+        <v>3041</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="7"/>
+    </row>
+    <row r="130" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B130" s="4">
+        <v>3051</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D130" s="6"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="7"/>
+    </row>
+    <row r="131" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B131" s="4">
+        <v>4091</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="6">
+        <v>0</v>
+      </c>
+      <c r="H131" s="6">
+        <v>2867068.53</v>
+      </c>
+      <c r="I131" s="7">
+        <v>2867068.53</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B132" s="4">
+        <v>4101</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6">
+        <v>0</v>
+      </c>
+      <c r="H132" s="6">
+        <v>0</v>
+      </c>
+      <c r="I132" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B133" s="4">
+        <v>4141</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6">
+        <v>747392.63</v>
+      </c>
+      <c r="H133" s="6">
+        <v>8034402.6799999997</v>
+      </c>
+      <c r="I133" s="7">
+        <v>8781795.3100000005</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B134" s="4">
+        <v>4251</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6">
+        <v>1112168.8899999999</v>
+      </c>
+      <c r="H134" s="6">
+        <v>5271380.07</v>
+      </c>
+      <c r="I134" s="7">
+        <v>6383548.96</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B135" s="4">
+        <v>4291</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="6">
+        <v>622978466.21000004</v>
+      </c>
+      <c r="H135" s="6">
+        <v>547393802.41999996</v>
+      </c>
+      <c r="I135" s="7">
+        <v>1170372268.6300001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B136" s="4">
+        <v>4331</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="6">
+        <v>0</v>
+      </c>
+      <c r="H136" s="6">
+        <v>206186.42</v>
+      </c>
+      <c r="I136" s="7">
+        <v>206186.42</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B137" s="4">
+        <v>4341</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="6">
+        <v>223487.09</v>
+      </c>
+      <c r="H137" s="6">
+        <v>548165.38</v>
+      </c>
+      <c r="I137" s="7">
+        <v>771652.47</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B138" s="4">
+        <v>4381</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="6">
+        <v>0</v>
+      </c>
+      <c r="H138" s="6">
+        <v>21378670.300000001</v>
+      </c>
+      <c r="I138" s="7">
+        <v>21378670.300000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B139" s="4">
+        <v>4451</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="6">
+        <v>679.54</v>
+      </c>
+      <c r="H139" s="6">
+        <v>8080205.7800000003</v>
+      </c>
+      <c r="I139" s="7">
+        <v>8080885.3200000003</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B140" s="4">
+        <v>4491</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="6">
+        <v>0</v>
+      </c>
+      <c r="H140" s="6">
+        <v>15394</v>
+      </c>
+      <c r="I140" s="7">
+        <v>15394</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B141" s="4">
+        <v>4541</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="6">
+        <v>0</v>
+      </c>
+      <c r="H141" s="6">
+        <v>26392.47</v>
+      </c>
+      <c r="I141" s="7">
+        <v>26392.47</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B142" s="4">
+        <v>4551</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="6">
+        <v>0</v>
+      </c>
+      <c r="H142" s="6">
+        <v>620005.26</v>
+      </c>
+      <c r="I142" s="7">
+        <v>620005.26</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B143" s="4">
+        <v>4601</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="6">
+        <v>2887433.54</v>
+      </c>
+      <c r="H143" s="6">
+        <v>3042047.61</v>
+      </c>
+      <c r="I143" s="7">
+        <v>5929481.1500000004</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B144" s="4">
+        <v>4691</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
+      <c r="G144" s="6">
+        <v>2093885.86</v>
+      </c>
+      <c r="H144" s="6">
+        <v>31330993.84</v>
+      </c>
+      <c r="I144" s="7">
+        <v>33424879.699999999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B145" s="4">
+        <v>4701</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D145" s="6"/>
+      <c r="E145" s="6"/>
+      <c r="F145" s="6"/>
+      <c r="G145" s="6">
+        <v>0</v>
+      </c>
+      <c r="H145" s="6">
+        <v>86523.72</v>
+      </c>
+      <c r="I145" s="7">
+        <v>86523.72</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B146" s="4">
         <v>4711</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D74" s="6">
-        <v>18258352481.540001</v>
-      </c>
-      <c r="E74" s="6">
-        <v>18256651559.23</v>
-      </c>
-      <c r="F74" s="6">
-        <v>18259071357.130001</v>
-      </c>
-      <c r="G74" s="6">
+      <c r="C146" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D146" s="6"/>
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="6">
         <v>46065.66</v>
       </c>
-      <c r="H74" s="6">
+      <c r="H146" s="6">
         <v>2149146.04</v>
       </c>
-      <c r="I74" s="7">
+      <c r="I146" s="7">
         <v>2195211.7000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\OneDrive\Documents\html\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE180320-3898-471E-8C8D-88B2F2B6E024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,15 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>Ano de Exercício</t>
   </si>
   <si>
-    <t>Unidade Orçamentária - Código</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Nome</t>
+    <t>Unidade Orçamentária - Código/Nome</t>
+  </si>
+  <si>
+    <t>Unidade Orçamentária - Sigla</t>
   </si>
   <si>
     <t>Valor Despesa Empenhada</t>
@@ -48,229 +49,448 @@
     <t>Valor Pago RP</t>
   </si>
   <si>
-    <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>ADVOCACIA GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE FAZENDA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
-  </si>
-  <si>
-    <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
-  </si>
-  <si>
-    <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE GOVERNO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>CONTROLADORIA-GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA-GERAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
-  </si>
-  <si>
-    <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
-  </si>
-  <si>
-    <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-  </si>
-  <si>
-    <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
-  </si>
-  <si>
-    <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO JOAO PINHEIRO</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HELENA ANTIPOFF</t>
-  </si>
-  <si>
-    <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE ARTE DE OURO PRETO</t>
-  </si>
-  <si>
-    <t>FUNDACAO CLOVIS SALGADO</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
-  </si>
-  <si>
-    <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO EZEQUIEL DIAS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
-  </si>
-  <si>
-    <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
-  </si>
-  <si>
-    <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
-  </si>
-  <si>
-    <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE HABITACAO</t>
-  </si>
-  <si>
-    <t>FUNDO PENITENCIARIO ESTADUAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SAUDE</t>
-  </si>
-  <si>
-    <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
-  </si>
-  <si>
-    <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE CULTURA</t>
-  </si>
-  <si>
-    <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+    <t>1071 - GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>GABINETE MILITAR</t>
+  </si>
+  <si>
+    <t>1081 - ADVOCACIA GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>1101 - OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>OGE</t>
+  </si>
+  <si>
+    <t>1191 - SECRETARIA DE ESTADO DE FAZENDA</t>
+  </si>
+  <si>
+    <t>SEF</t>
+  </si>
+  <si>
+    <t>1221 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+  </si>
+  <si>
+    <t>SEDE</t>
+  </si>
+  <si>
+    <t>1231 - SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+  </si>
+  <si>
+    <t>SEAPA</t>
+  </si>
+  <si>
+    <t>1251 - POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PMMG</t>
+  </si>
+  <si>
+    <t>1261 - SECRETARIA DE ESTADO DE EDUCACAO</t>
+  </si>
+  <si>
+    <t>SEE</t>
+  </si>
+  <si>
+    <t>1271 - SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+  </si>
+  <si>
+    <t>SECULT</t>
+  </si>
+  <si>
+    <t>1301 - SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+  </si>
+  <si>
+    <t>SEINFRA</t>
+  </si>
+  <si>
+    <t>1371 - SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+  </si>
+  <si>
+    <t>SEMAD</t>
+  </si>
+  <si>
+    <t>1401 - CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>CBMMG</t>
+  </si>
+  <si>
+    <t>1451 - SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+  </si>
+  <si>
+    <t>SEJUSP</t>
+  </si>
+  <si>
+    <t>1481 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+  </si>
+  <si>
+    <t>SEDESE</t>
+  </si>
+  <si>
+    <t>1491 - SECRETARIA DE ESTADO DE GOVERNO</t>
+  </si>
+  <si>
+    <t>SEGOV</t>
+  </si>
+  <si>
+    <t>1501 - SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>SEPLAG</t>
+  </si>
+  <si>
+    <t>1511 - POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PCMG</t>
+  </si>
+  <si>
+    <t>1521 - CONTROLADORIA-GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>CGE</t>
+  </si>
+  <si>
+    <t>1541 - ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>ESP MG</t>
+  </si>
+  <si>
+    <t>1631 - SECRETARIA-GERAL</t>
+  </si>
+  <si>
+    <t>SEC. GERAL</t>
+  </si>
+  <si>
+    <t>1711 - SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+  </si>
+  <si>
+    <t>SECOM</t>
+  </si>
+  <si>
+    <t>1721 - SECRETARIA DE ESTADO DA CASA CIVIL</t>
+  </si>
+  <si>
+    <t>SCC</t>
+  </si>
+  <si>
+    <t>1911 - EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+  </si>
+  <si>
+    <t>EGE - SEF</t>
+  </si>
+  <si>
+    <t>1915 - PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+  </si>
+  <si>
+    <t>PARTICIPAÇÃO EMPRESAS</t>
+  </si>
+  <si>
+    <t>1916 - GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+  </si>
+  <si>
+    <t>GDPE - SEF</t>
+  </si>
+  <si>
+    <t>1941 - EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>EGE-SEPLAG</t>
+  </si>
+  <si>
+    <t>2011 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSEMG</t>
+  </si>
+  <si>
+    <t>2041 - LOTERIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>LEMG</t>
+  </si>
+  <si>
+    <t>2061 - FUNDACAO JOAO PINHEIRO</t>
+  </si>
+  <si>
+    <t>FJP</t>
+  </si>
+  <si>
+    <t>2071 - FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAPEMIG</t>
+  </si>
+  <si>
+    <t>2091 - FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+  </si>
+  <si>
+    <t>FEAM</t>
+  </si>
+  <si>
+    <t>2101 - INSTITUTO ESTADUAL DE FLORESTAS</t>
+  </si>
+  <si>
+    <t>IEF</t>
+  </si>
+  <si>
+    <t>2121 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSM</t>
+  </si>
+  <si>
+    <t>2151 - FUNDACAO HELENA ANTIPOFF</t>
+  </si>
+  <si>
+    <t>FHA</t>
+  </si>
+  <si>
+    <t>2161 - FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+  </si>
+  <si>
+    <t>FUCAM</t>
+  </si>
+  <si>
+    <t>2171 - FUNDACAO DE ARTE DE OURO PRETO</t>
+  </si>
+  <si>
+    <t>FAOP</t>
+  </si>
+  <si>
+    <t>2181 - FUNDACAO CLOVIS SALGADO</t>
+  </si>
+  <si>
+    <t>FCS</t>
+  </si>
+  <si>
+    <t>2201 - INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IEPHA</t>
+  </si>
+  <si>
+    <t>2211 - FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+  </si>
+  <si>
+    <t>TV MINAS</t>
+  </si>
+  <si>
+    <t>2241 - INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+  </si>
+  <si>
+    <t>IGAM</t>
+  </si>
+  <si>
+    <t>2251 - JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>JUCEMG</t>
+  </si>
+  <si>
+    <t>2261 - FUNDACAO EZEQUIEL DIAS</t>
+  </si>
+  <si>
+    <t>FUNED</t>
+  </si>
+  <si>
+    <t>2271 - FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FHEMIG</t>
+  </si>
+  <si>
+    <t>2281 - FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UTRAMIG</t>
+  </si>
+  <si>
+    <t>2301 - DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>DER-MG</t>
+  </si>
+  <si>
+    <t>2311 - UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+  </si>
+  <si>
+    <t>UNIMONTES</t>
+  </si>
+  <si>
+    <t>2321 - FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>HEMOMINAS</t>
+  </si>
+  <si>
+    <t>2331 - INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPEMMG</t>
+  </si>
+  <si>
+    <t>2351 - UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UEMG</t>
+  </si>
+  <si>
+    <t>2371 - INSTITUTO MINEIRO DE AGROPECUARIA</t>
+  </si>
+  <si>
+    <t>IMA</t>
+  </si>
+  <si>
+    <t>2421 - INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IDENE</t>
+  </si>
+  <si>
+    <t>2431 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
+  </si>
+  <si>
+    <t>AGÊNCIA RMBH</t>
+  </si>
+  <si>
+    <t>2441 - AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+  </si>
+  <si>
+    <t>ARSAE -MG</t>
+  </si>
+  <si>
+    <t>2461 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+  </si>
+  <si>
+    <t>ARMVA</t>
+  </si>
+  <si>
+    <t>2471 - AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>ARTEMIG</t>
+  </si>
+  <si>
+    <t>3041 - EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMATER</t>
+  </si>
+  <si>
+    <t>3051 - EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EPAMIG</t>
+  </si>
+  <si>
+    <t>4091 - FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+  </si>
+  <si>
+    <t>FIA</t>
+  </si>
+  <si>
+    <t>4101 - FUNDO ESTADUAL DE HABITACAO</t>
+  </si>
+  <si>
+    <t>FEH</t>
+  </si>
+  <si>
+    <t>4141 - FUNDO PENITENCIARIO ESTADUAL</t>
+  </si>
+  <si>
+    <t>FPE</t>
+  </si>
+  <si>
+    <t>4251 - FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+  </si>
+  <si>
+    <t>FEAS</t>
+  </si>
+  <si>
+    <t>4291 - FUNDO ESTADUAL DE SAUDE</t>
+  </si>
+  <si>
+    <t>FES</t>
+  </si>
+  <si>
+    <t>4331 - FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+  </si>
+  <si>
+    <t>FDM</t>
+  </si>
+  <si>
+    <t>4341 - FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+  </si>
+  <si>
+    <t>FHIDRO</t>
+  </si>
+  <si>
+    <t>4381 - FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>FUNTRANS</t>
+  </si>
+  <si>
+    <t>4451 - FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+  </si>
+  <si>
+    <t>FEPDC</t>
+  </si>
+  <si>
+    <t>4491 - FUNDO ESTADUAL DE CULTURA</t>
+  </si>
+  <si>
+    <t>FEC</t>
+  </si>
+  <si>
+    <t>4541 - FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAHMEMG</t>
+  </si>
+  <si>
+    <t>4551 - FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNAPEC</t>
+  </si>
+  <si>
+    <t>4601 - FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+  </si>
+  <si>
+    <t>FEI</t>
+  </si>
+  <si>
+    <t>4691 - FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FESP-MG</t>
+  </si>
+  <si>
+    <t>4701 - FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FET-MG</t>
+  </si>
+  <si>
+    <t>4711 - FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FFP - MG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###,###,###,##0.00"/>
   </numFmts>
@@ -384,39 +604,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -449,9 +669,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -484,6 +721,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -545,13 +799,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -560,6 +807,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -624,24 +878,44 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="119.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
     <col min="4" max="6" width="17.28515625" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
     <col min="8" max="8" width="25.140625" customWidth="1"/>
@@ -649,14 +923,14 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="34.700000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -682,11 +956,11 @@
       <c r="A2" s="4">
         <v>2025</v>
       </c>
-      <c r="B2" s="4">
-        <v>1071</v>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="6">
         <v>55898902.780000001</v>
@@ -711,11 +985,11 @@
       <c r="A3" s="4">
         <v>2025</v>
       </c>
-      <c r="B3" s="4">
-        <v>1081</v>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="6">
         <v>1023743951.58</v>
@@ -740,11 +1014,11 @@
       <c r="A4" s="4">
         <v>2025</v>
       </c>
-      <c r="B4" s="4">
-        <v>1101</v>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6">
         <v>18048368.199999999</v>
@@ -769,11 +1043,11 @@
       <c r="A5" s="4">
         <v>2025</v>
       </c>
-      <c r="B5" s="4">
-        <v>1191</v>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6">
         <v>1886784188.8099999</v>
@@ -798,11 +1072,11 @@
       <c r="A6" s="4">
         <v>2025</v>
       </c>
-      <c r="B6" s="4">
-        <v>1221</v>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6">
         <v>425928118.32999998</v>
@@ -827,11 +1101,11 @@
       <c r="A7" s="4">
         <v>2025</v>
       </c>
-      <c r="B7" s="4">
-        <v>1231</v>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6">
         <v>319941879.06999999</v>
@@ -856,11 +1130,11 @@
       <c r="A8" s="4">
         <v>2025</v>
       </c>
-      <c r="B8" s="4">
-        <v>1251</v>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6">
         <v>17184629357.540001</v>
@@ -885,11 +1159,11 @@
       <c r="A9" s="4">
         <v>2025</v>
       </c>
-      <c r="B9" s="4">
-        <v>1261</v>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" s="6">
         <v>20024070516.279999</v>
@@ -914,11 +1188,11 @@
       <c r="A10" s="4">
         <v>2025</v>
       </c>
-      <c r="B10" s="4">
-        <v>1271</v>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6">
         <v>261449910.33000001</v>
@@ -943,11 +1217,11 @@
       <c r="A11" s="4">
         <v>2025</v>
       </c>
-      <c r="B11" s="4">
-        <v>1301</v>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6">
         <v>480636059.57999998</v>
@@ -972,11 +1246,11 @@
       <c r="A12" s="4">
         <v>2025</v>
       </c>
-      <c r="B12" s="4">
-        <v>1371</v>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D12" s="6">
         <v>185286819.99000001</v>
@@ -1001,11 +1275,11 @@
       <c r="A13" s="4">
         <v>2025</v>
       </c>
-      <c r="B13" s="4">
-        <v>1401</v>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6">
         <v>2074027252.0699999</v>
@@ -1030,11 +1304,11 @@
       <c r="A14" s="4">
         <v>2025</v>
       </c>
-      <c r="B14" s="4">
-        <v>1451</v>
+      <c r="B14" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6">
         <v>4556477829.6899996</v>
@@ -1059,11 +1333,11 @@
       <c r="A15" s="4">
         <v>2025</v>
       </c>
-      <c r="B15" s="4">
-        <v>1481</v>
+      <c r="B15" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D15" s="6">
         <v>338412512.00999999</v>
@@ -1088,11 +1362,11 @@
       <c r="A16" s="4">
         <v>2025</v>
       </c>
-      <c r="B16" s="4">
-        <v>1491</v>
+      <c r="B16" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D16" s="6">
         <v>971196665.48000002</v>
@@ -1117,11 +1391,11 @@
       <c r="A17" s="4">
         <v>2025</v>
       </c>
-      <c r="B17" s="4">
-        <v>1501</v>
+      <c r="B17" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6">
         <v>940771355.50999999</v>
@@ -1146,11 +1420,11 @@
       <c r="A18" s="4">
         <v>2025</v>
       </c>
-      <c r="B18" s="4">
-        <v>1511</v>
+      <c r="B18" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D18" s="6">
         <v>3138279917.0599999</v>
@@ -1175,11 +1449,11 @@
       <c r="A19" s="4">
         <v>2025</v>
       </c>
-      <c r="B19" s="4">
-        <v>1521</v>
+      <c r="B19" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D19" s="6">
         <v>70667226.109999999</v>
@@ -1204,11 +1478,11 @@
       <c r="A20" s="4">
         <v>2025</v>
       </c>
-      <c r="B20" s="4">
-        <v>1541</v>
+      <c r="B20" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D20" s="6">
         <v>25352006.23</v>
@@ -1233,11 +1507,11 @@
       <c r="A21" s="4">
         <v>2025</v>
       </c>
-      <c r="B21" s="4">
-        <v>1631</v>
+      <c r="B21" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D21" s="6">
         <v>12493555.880000001</v>
@@ -1262,11 +1536,11 @@
       <c r="A22" s="4">
         <v>2025</v>
       </c>
-      <c r="B22" s="4">
-        <v>1711</v>
+      <c r="B22" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D22" s="6">
         <v>181181663.88</v>
@@ -1291,11 +1565,11 @@
       <c r="A23" s="4">
         <v>2025</v>
       </c>
-      <c r="B23" s="4">
-        <v>1721</v>
+      <c r="B23" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D23" s="6">
         <v>10652572.939999999</v>
@@ -1320,11 +1594,11 @@
       <c r="A24" s="4">
         <v>2025</v>
       </c>
-      <c r="B24" s="4">
-        <v>1911</v>
+      <c r="B24" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D24" s="6">
         <v>1211264345.4300001</v>
@@ -1349,11 +1623,11 @@
       <c r="A25" s="4">
         <v>2025</v>
       </c>
-      <c r="B25" s="4">
-        <v>1915</v>
+      <c r="B25" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D25" s="6">
         <v>20043002.559999999</v>
@@ -1378,11 +1652,11 @@
       <c r="A26" s="4">
         <v>2025</v>
       </c>
-      <c r="B26" s="4">
-        <v>1916</v>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D26" s="6">
         <v>6570721631.0600004</v>
@@ -1407,11 +1681,11 @@
       <c r="A27" s="4">
         <v>2025</v>
       </c>
-      <c r="B27" s="4">
-        <v>1941</v>
+      <c r="B27" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D27" s="6">
         <v>194535650.21000001</v>
@@ -1436,11 +1710,11 @@
       <c r="A28" s="4">
         <v>2025</v>
       </c>
-      <c r="B28" s="4">
-        <v>2011</v>
+      <c r="B28" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D28" s="6">
         <v>2066687330.24</v>
@@ -1465,11 +1739,11 @@
       <c r="A29" s="4">
         <v>2025</v>
       </c>
-      <c r="B29" s="4">
-        <v>2041</v>
+      <c r="B29" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D29" s="6">
         <v>2901561.62</v>
@@ -1494,11 +1768,11 @@
       <c r="A30" s="4">
         <v>2025</v>
       </c>
-      <c r="B30" s="4">
-        <v>2061</v>
+      <c r="B30" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D30" s="6">
         <v>70806633.620000005</v>
@@ -1523,11 +1797,11 @@
       <c r="A31" s="4">
         <v>2025</v>
       </c>
-      <c r="B31" s="4">
-        <v>2071</v>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D31" s="6">
         <v>585603048.33000004</v>
@@ -1552,11 +1826,11 @@
       <c r="A32" s="4">
         <v>2025</v>
       </c>
-      <c r="B32" s="4">
-        <v>2091</v>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D32" s="6">
         <v>75621728.879999995</v>
@@ -1581,11 +1855,11 @@
       <c r="A33" s="4">
         <v>2025</v>
       </c>
-      <c r="B33" s="4">
-        <v>2101</v>
+      <c r="B33" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D33" s="6">
         <v>217212201.81999999</v>
@@ -1610,11 +1884,11 @@
       <c r="A34" s="4">
         <v>2025</v>
       </c>
-      <c r="B34" s="4">
-        <v>2121</v>
+      <c r="B34" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D34" s="6">
         <v>3302390465.79</v>
@@ -1639,11 +1913,11 @@
       <c r="A35" s="4">
         <v>2025</v>
       </c>
-      <c r="B35" s="4">
-        <v>2151</v>
+      <c r="B35" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D35" s="6">
         <v>81750398.859999999</v>
@@ -1668,11 +1942,11 @@
       <c r="A36" s="4">
         <v>2025</v>
       </c>
-      <c r="B36" s="4">
-        <v>2161</v>
+      <c r="B36" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D36" s="6">
         <v>6356895.04</v>
@@ -1697,11 +1971,11 @@
       <c r="A37" s="4">
         <v>2025</v>
       </c>
-      <c r="B37" s="4">
-        <v>2171</v>
+      <c r="B37" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D37" s="6">
         <v>9439748.6199999992</v>
@@ -1726,11 +2000,11 @@
       <c r="A38" s="4">
         <v>2025</v>
       </c>
-      <c r="B38" s="4">
-        <v>2181</v>
+      <c r="B38" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D38" s="6">
         <v>63217552.93</v>
@@ -1755,11 +2029,11 @@
       <c r="A39" s="4">
         <v>2025</v>
       </c>
-      <c r="B39" s="4">
-        <v>2201</v>
+      <c r="B39" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="D39" s="6">
         <v>28359171.850000001</v>
@@ -1784,11 +2058,11 @@
       <c r="A40" s="4">
         <v>2025</v>
       </c>
-      <c r="B40" s="4">
-        <v>2211</v>
+      <c r="B40" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="D40" s="6">
         <v>16376327.77</v>
@@ -1813,11 +2087,11 @@
       <c r="A41" s="4">
         <v>2025</v>
       </c>
-      <c r="B41" s="4">
-        <v>2241</v>
+      <c r="B41" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D41" s="6">
         <v>195257062.84999999</v>
@@ -1842,11 +2116,11 @@
       <c r="A42" s="4">
         <v>2025</v>
       </c>
-      <c r="B42" s="4">
-        <v>2251</v>
+      <c r="B42" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D42" s="6">
         <v>41105200.07</v>
@@ -1871,11 +2145,11 @@
       <c r="A43" s="4">
         <v>2025</v>
       </c>
-      <c r="B43" s="4">
-        <v>2261</v>
+      <c r="B43" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="D43" s="6">
         <v>553211607.35000002</v>
@@ -1900,11 +2174,11 @@
       <c r="A44" s="4">
         <v>2025</v>
       </c>
-      <c r="B44" s="4">
-        <v>2271</v>
+      <c r="B44" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D44" s="6">
         <v>2478485587.5</v>
@@ -1929,11 +2203,11 @@
       <c r="A45" s="4">
         <v>2025</v>
       </c>
-      <c r="B45" s="4">
-        <v>2281</v>
+      <c r="B45" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D45" s="6">
         <v>7417117.2199999997</v>
@@ -1958,11 +2232,11 @@
       <c r="A46" s="4">
         <v>2025</v>
       </c>
-      <c r="B46" s="4">
-        <v>2301</v>
+      <c r="B46" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D46" s="6">
         <v>2143327357.7</v>
@@ -1987,11 +2261,11 @@
       <c r="A47" s="4">
         <v>2025</v>
       </c>
-      <c r="B47" s="4">
-        <v>2311</v>
+      <c r="B47" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="D47" s="6">
         <v>533150763.61000001</v>
@@ -2016,11 +2290,11 @@
       <c r="A48" s="4">
         <v>2025</v>
       </c>
-      <c r="B48" s="4">
-        <v>2321</v>
+      <c r="B48" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="D48" s="6">
         <v>394549598.81</v>
@@ -2045,11 +2319,11 @@
       <c r="A49" s="4">
         <v>2025</v>
       </c>
-      <c r="B49" s="4">
-        <v>2331</v>
+      <c r="B49" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D49" s="6">
         <v>35739703.740000002</v>
@@ -2074,11 +2348,11 @@
       <c r="A50" s="4">
         <v>2025</v>
       </c>
-      <c r="B50" s="4">
-        <v>2351</v>
+      <c r="B50" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D50" s="6">
         <v>431560939.48000002</v>
@@ -2103,11 +2377,11 @@
       <c r="A51" s="4">
         <v>2025</v>
       </c>
-      <c r="B51" s="4">
-        <v>2371</v>
+      <c r="B51" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="D51" s="6">
         <v>290312222.92000002</v>
@@ -2132,11 +2406,11 @@
       <c r="A52" s="4">
         <v>2025</v>
       </c>
-      <c r="B52" s="4">
-        <v>2421</v>
+      <c r="B52" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="D52" s="6">
         <v>61510642.640000001</v>
@@ -2161,11 +2435,11 @@
       <c r="A53" s="4">
         <v>2025</v>
       </c>
-      <c r="B53" s="4">
-        <v>2431</v>
+      <c r="B53" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D53" s="6">
         <v>7932027.7699999996</v>
@@ -2190,11 +2464,11 @@
       <c r="A54" s="4">
         <v>2025</v>
       </c>
-      <c r="B54" s="4">
-        <v>2441</v>
+      <c r="B54" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D54" s="6">
         <v>19031476.379999999</v>
@@ -2219,11 +2493,11 @@
       <c r="A55" s="4">
         <v>2025</v>
       </c>
-      <c r="B55" s="4">
-        <v>2461</v>
+      <c r="B55" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D55" s="6">
         <v>4789292.1100000003</v>
@@ -2248,11 +2522,11 @@
       <c r="A56" s="4">
         <v>2025</v>
       </c>
-      <c r="B56" s="4">
-        <v>2471</v>
+      <c r="B56" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="D56" s="6">
         <v>12995181.74</v>
@@ -2271,11 +2545,11 @@
       <c r="A57" s="4">
         <v>2025</v>
       </c>
-      <c r="B57" s="4">
-        <v>3041</v>
+      <c r="B57" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="D57" s="6">
         <v>411646902.57999998</v>
@@ -2294,11 +2568,11 @@
       <c r="A58" s="4">
         <v>2025</v>
       </c>
-      <c r="B58" s="4">
-        <v>3051</v>
+      <c r="B58" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="D58" s="6">
         <v>150702794.75999999</v>
@@ -2317,11 +2591,11 @@
       <c r="A59" s="4">
         <v>2025</v>
       </c>
-      <c r="B59" s="4">
-        <v>4091</v>
+      <c r="B59" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D59" s="6">
         <v>610536.65</v>
@@ -2346,11 +2620,11 @@
       <c r="A60" s="4">
         <v>2025</v>
       </c>
-      <c r="B60" s="4">
-        <v>4101</v>
+      <c r="B60" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="D60" s="6">
         <v>16870000</v>
@@ -2375,11 +2649,11 @@
       <c r="A61" s="4">
         <v>2025</v>
       </c>
-      <c r="B61" s="4">
-        <v>4141</v>
+      <c r="B61" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D61" s="6">
         <v>10407251.17</v>
@@ -2404,11 +2678,11 @@
       <c r="A62" s="4">
         <v>2025</v>
       </c>
-      <c r="B62" s="4">
-        <v>4251</v>
+      <c r="B62" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="D62" s="6">
         <v>172407716.30000001</v>
@@ -2433,11 +2707,11 @@
       <c r="A63" s="4">
         <v>2025</v>
       </c>
-      <c r="B63" s="4">
-        <v>4291</v>
+      <c r="B63" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="D63" s="6">
         <v>12684000278.799999</v>
@@ -2462,11 +2736,11 @@
       <c r="A64" s="4">
         <v>2025</v>
       </c>
-      <c r="B64" s="4">
-        <v>4331</v>
+      <c r="B64" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="D64" s="6">
         <v>3035441.45</v>
@@ -2491,11 +2765,11 @@
       <c r="A65" s="4">
         <v>2025</v>
       </c>
-      <c r="B65" s="4">
-        <v>4341</v>
+      <c r="B65" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="D65" s="6">
         <v>2288740.7400000002</v>
@@ -2520,11 +2794,11 @@
       <c r="A66" s="4">
         <v>2025</v>
       </c>
-      <c r="B66" s="4">
-        <v>4381</v>
+      <c r="B66" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="D66" s="6">
         <v>127170575.95</v>
@@ -2549,11 +2823,11 @@
       <c r="A67" s="4">
         <v>2025</v>
       </c>
-      <c r="B67" s="4">
-        <v>4451</v>
+      <c r="B67" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="D67" s="6">
         <v>48631312.579999998</v>
@@ -2578,11 +2852,11 @@
       <c r="A68" s="4">
         <v>2025</v>
       </c>
-      <c r="B68" s="4">
-        <v>4491</v>
+      <c r="B68" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="D68" s="6">
         <v>2634653.3199999998</v>
@@ -2607,11 +2881,11 @@
       <c r="A69" s="4">
         <v>2025</v>
       </c>
-      <c r="B69" s="4">
-        <v>4541</v>
+      <c r="B69" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="D69" s="6">
         <v>350405</v>
@@ -2636,11 +2910,11 @@
       <c r="A70" s="4">
         <v>2025</v>
       </c>
-      <c r="B70" s="4">
-        <v>4551</v>
+      <c r="B70" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="D70" s="6">
         <v>148883049.19999999</v>
@@ -2665,11 +2939,11 @@
       <c r="A71" s="4">
         <v>2025</v>
       </c>
-      <c r="B71" s="4">
-        <v>4601</v>
+      <c r="B71" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D71" s="6">
         <v>1473191.28</v>
@@ -2694,11 +2968,11 @@
       <c r="A72" s="4">
         <v>2025</v>
       </c>
-      <c r="B72" s="4">
-        <v>4691</v>
+      <c r="B72" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="D72" s="6">
         <v>64705464.399999999</v>
@@ -2723,11 +2997,11 @@
       <c r="A73" s="4">
         <v>2025</v>
       </c>
-      <c r="B73" s="4">
-        <v>4701</v>
+      <c r="B73" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="D73" s="6">
         <v>2107186.39</v>
@@ -2752,11 +3026,11 @@
       <c r="A74" s="4">
         <v>2025</v>
       </c>
-      <c r="B74" s="4">
-        <v>4711</v>
+      <c r="B74" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="D74" s="6">
         <v>18258352481.540001</v>

--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,25 +870,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3051</v>
+        <v>3151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150702794.76</v>
+        <v>30003569.6</v>
       </c>
       <c r="F13" t="n">
-        <v>150702794.76</v>
+        <v>30003569.6</v>
       </c>
       <c r="G13" t="n">
-        <v>150702794.76</v>
+        <v>30003569.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -900,35 +900,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25352006.23</v>
+        <v>150702794.76</v>
       </c>
       <c r="F14" t="n">
-        <v>23581392.72</v>
+        <v>150702794.76</v>
       </c>
       <c r="G14" t="n">
-        <v>22865578.49</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>351886.66</v>
-      </c>
-      <c r="J14" t="n">
-        <v>351886.66</v>
-      </c>
+        <v>150702794.76</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -936,34 +930,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>350405</v>
+        <v>25352006.23</v>
       </c>
       <c r="F15" t="n">
-        <v>318593.91</v>
+        <v>23581392.72</v>
       </c>
       <c r="G15" t="n">
-        <v>300914.63</v>
+        <v>22865578.49</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>26392.47</v>
+        <v>351886.66</v>
       </c>
       <c r="J15" t="n">
-        <v>26392.47</v>
+        <v>351886.66</v>
       </c>
     </row>
     <row r="16">
@@ -972,34 +966,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9439748.619999999</v>
+        <v>350405</v>
       </c>
       <c r="F16" t="n">
-        <v>9225890.4</v>
+        <v>318593.91</v>
       </c>
       <c r="G16" t="n">
-        <v>8465439.720000001</v>
+        <v>300914.63</v>
       </c>
       <c r="H16" t="n">
-        <v>480546.01</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>177676.07</v>
+        <v>26392.47</v>
       </c>
       <c r="J16" t="n">
-        <v>658222.08</v>
+        <v>26392.47</v>
       </c>
     </row>
     <row r="17">
@@ -1008,34 +1002,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>585603048.33</v>
+        <v>9439748.619999999</v>
       </c>
       <c r="F17" t="n">
-        <v>580710591.1900001</v>
+        <v>9225890.4</v>
       </c>
       <c r="G17" t="n">
-        <v>574854711.54</v>
+        <v>8465439.720000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1239266.23</v>
+        <v>480546.01</v>
       </c>
       <c r="I17" t="n">
-        <v>8506819.619999999</v>
+        <v>177676.07</v>
       </c>
       <c r="J17" t="n">
-        <v>9746085.85</v>
+        <v>658222.08</v>
       </c>
     </row>
     <row r="18">
@@ -1044,34 +1038,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>63217552.93</v>
+        <v>585603048.33</v>
       </c>
       <c r="F18" t="n">
-        <v>60940567.95</v>
+        <v>580710591.1900001</v>
       </c>
       <c r="G18" t="n">
-        <v>56959723.43</v>
+        <v>574854711.54</v>
       </c>
       <c r="H18" t="n">
-        <v>119258.05</v>
+        <v>1239266.23</v>
       </c>
       <c r="I18" t="n">
-        <v>2222004.25</v>
+        <v>8506819.619999999</v>
       </c>
       <c r="J18" t="n">
-        <v>2341262.3</v>
+        <v>9746085.85</v>
       </c>
     </row>
     <row r="19">
@@ -1080,34 +1074,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3035441.45</v>
+        <v>63217552.93</v>
       </c>
       <c r="F19" t="n">
-        <v>97428.45</v>
+        <v>60940567.95</v>
       </c>
       <c r="G19" t="n">
-        <v>93102.96000000001</v>
+        <v>56959723.43</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>119258.05</v>
       </c>
       <c r="I19" t="n">
-        <v>206186.42</v>
+        <v>2222004.25</v>
       </c>
       <c r="J19" t="n">
-        <v>206186.42</v>
+        <v>2341262.3</v>
       </c>
     </row>
     <row r="20">
@@ -1116,34 +1110,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>75621728.88</v>
+        <v>3035441.45</v>
       </c>
       <c r="F20" t="n">
-        <v>74134505.91</v>
+        <v>97428.45</v>
       </c>
       <c r="G20" t="n">
-        <v>72540998.40000001</v>
+        <v>93102.96000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>24329.43</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2347292.71</v>
+        <v>206186.42</v>
       </c>
       <c r="J20" t="n">
-        <v>2371622.14</v>
+        <v>206186.42</v>
       </c>
     </row>
     <row r="21">
@@ -1152,34 +1146,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>172407716.3</v>
+        <v>75621728.88</v>
       </c>
       <c r="F21" t="n">
-        <v>169951293.67</v>
+        <v>74134505.91</v>
       </c>
       <c r="G21" t="n">
-        <v>168474678.26</v>
+        <v>72540998.40000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1112168.89</v>
+        <v>24329.43</v>
       </c>
       <c r="I21" t="n">
-        <v>5271380.07</v>
+        <v>2347292.71</v>
       </c>
       <c r="J21" t="n">
-        <v>6383548.96</v>
+        <v>2371622.14</v>
       </c>
     </row>
     <row r="22">
@@ -1188,34 +1182,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2634653.32</v>
+        <v>172407716.3</v>
       </c>
       <c r="F22" t="n">
-        <v>2500037.94</v>
+        <v>169951293.67</v>
       </c>
       <c r="G22" t="n">
-        <v>1882700.63</v>
+        <v>168474678.26</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1112168.89</v>
       </c>
       <c r="I22" t="n">
-        <v>15394</v>
+        <v>5271380.07</v>
       </c>
       <c r="J22" t="n">
-        <v>15394</v>
+        <v>6383548.96</v>
       </c>
     </row>
     <row r="23">
@@ -1224,34 +1218,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4101</v>
+        <v>4491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16870000</v>
+        <v>2634653.32</v>
       </c>
       <c r="F23" t="n">
-        <v>16870000</v>
+        <v>2500037.94</v>
       </c>
       <c r="G23" t="n">
-        <v>15570000</v>
+        <v>1882700.63</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>15394</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>15394</v>
       </c>
     </row>
     <row r="24">
@@ -1260,34 +1254,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4601</v>
+        <v>4101</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1473191.28</v>
+        <v>16870000</v>
       </c>
       <c r="F24" t="n">
-        <v>1033455.88</v>
+        <v>16870000</v>
       </c>
       <c r="G24" t="n">
-        <v>987548.8100000001</v>
+        <v>15570000</v>
       </c>
       <c r="H24" t="n">
-        <v>2887433.54</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3042047.61</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>5929481.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1296,34 +1290,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4451</v>
+        <v>4601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48631312.58</v>
+        <v>1473191.28</v>
       </c>
       <c r="F25" t="n">
-        <v>11932319.97</v>
+        <v>1033455.88</v>
       </c>
       <c r="G25" t="n">
-        <v>11013107.33</v>
+        <v>987548.8100000001</v>
       </c>
       <c r="H25" t="n">
-        <v>679.54</v>
+        <v>2887433.54</v>
       </c>
       <c r="I25" t="n">
-        <v>8080205.78</v>
+        <v>3042047.61</v>
       </c>
       <c r="J25" t="n">
-        <v>8080885.32</v>
+        <v>5929481.15</v>
       </c>
     </row>
     <row r="26">
@@ -1692,34 +1686,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2161</v>
+        <v>4631</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6356895.04</v>
+        <v>712687568.61</v>
       </c>
       <c r="F36" t="n">
-        <v>5950697.58</v>
+        <v>645428218.54</v>
       </c>
       <c r="G36" t="n">
-        <v>5865105.78</v>
+        <v>535779525.63</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>416373.16</v>
+        <v>35286533.51</v>
       </c>
       <c r="J36" t="n">
-        <v>416373.16</v>
+        <v>35286533.51</v>
       </c>
     </row>
     <row r="37">
@@ -1728,34 +1722,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4551</v>
+        <v>2161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>148883049.2</v>
+        <v>6356895.04</v>
       </c>
       <c r="F37" t="n">
-        <v>148355490.34</v>
+        <v>5950697.58</v>
       </c>
       <c r="G37" t="n">
-        <v>148348943.52</v>
+        <v>5865105.78</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>620005.26</v>
+        <v>416373.16</v>
       </c>
       <c r="J37" t="n">
-        <v>620005.26</v>
+        <v>416373.16</v>
       </c>
     </row>
     <row r="38">
@@ -1764,34 +1758,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2261</v>
+        <v>4551</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>553211607.35</v>
+        <v>148883049.2</v>
       </c>
       <c r="F38" t="n">
-        <v>369463545.18</v>
+        <v>148355490.34</v>
       </c>
       <c r="G38" t="n">
-        <v>355249323.08</v>
+        <v>148348943.52</v>
       </c>
       <c r="H38" t="n">
-        <v>38687418.56</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>130773841.95</v>
+        <v>620005.26</v>
       </c>
       <c r="J38" t="n">
-        <v>169461260.51</v>
+        <v>620005.26</v>
       </c>
     </row>
     <row r="39">
@@ -1800,34 +1794,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNDIF</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4381</v>
+        <v>4421</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>127170575.95</v>
+        <v>3658.62</v>
       </c>
       <c r="F39" t="n">
-        <v>102885370.45</v>
+        <v>3658.62</v>
       </c>
       <c r="G39" t="n">
-        <v>98080707.2</v>
+        <v>3658.62</v>
       </c>
       <c r="H39" t="n">
+        <v>895.13</v>
+      </c>
+      <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="I39" t="n">
-        <v>21378670.3</v>
-      </c>
       <c r="J39" t="n">
-        <v>21378670.3</v>
+        <v>895.13</v>
       </c>
     </row>
     <row r="40">
@@ -1836,34 +1830,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1071</v>
+        <v>2261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>55898902.78</v>
+        <v>553211607.35</v>
       </c>
       <c r="F40" t="n">
-        <v>34921981.44</v>
+        <v>369463545.18</v>
       </c>
       <c r="G40" t="n">
-        <v>32307667.05</v>
+        <v>355249323.08</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>38687418.56</v>
       </c>
       <c r="I40" t="n">
-        <v>4293686.19</v>
+        <v>130773841.95</v>
       </c>
       <c r="J40" t="n">
-        <v>4293686.19</v>
+        <v>169461260.51</v>
       </c>
     </row>
     <row r="41">
@@ -1872,34 +1866,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1916</v>
+        <v>4381</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6570721631.06</v>
+        <v>127170575.95</v>
       </c>
       <c r="F41" t="n">
-        <v>6570721631.06</v>
+        <v>102885370.45</v>
       </c>
       <c r="G41" t="n">
-        <v>6497797081.7</v>
+        <v>98080707.2</v>
       </c>
       <c r="H41" t="n">
-        <v>260833467.16</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>21378670.3</v>
       </c>
       <c r="J41" t="n">
-        <v>260833467.16</v>
+        <v>21378670.3</v>
       </c>
     </row>
     <row r="42">
@@ -1908,34 +1902,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2321</v>
+        <v>1071</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>394549598.81</v>
+        <v>55898902.78</v>
       </c>
       <c r="F42" t="n">
-        <v>359596023.43</v>
+        <v>34921981.44</v>
       </c>
       <c r="G42" t="n">
-        <v>346696259.17</v>
+        <v>32307667.05</v>
       </c>
       <c r="H42" t="n">
-        <v>1425788.73</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>30573782.13</v>
+        <v>4293686.19</v>
       </c>
       <c r="J42" t="n">
-        <v>31999570.86</v>
+        <v>4293686.19</v>
       </c>
     </row>
     <row r="43">
@@ -1944,34 +1938,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2421</v>
+        <v>1916</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>61510642.64</v>
+        <v>6570721631.06</v>
       </c>
       <c r="F43" t="n">
-        <v>43124254.63</v>
+        <v>6570721631.06</v>
       </c>
       <c r="G43" t="n">
-        <v>41282826.79</v>
+        <v>6497797081.7</v>
       </c>
       <c r="H43" t="n">
-        <v>713315.27</v>
+        <v>260833467.16</v>
       </c>
       <c r="I43" t="n">
-        <v>7206237.15</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>7919552.42</v>
+        <v>260833467.16</v>
       </c>
     </row>
     <row r="44">
@@ -1980,34 +1974,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2101</v>
+        <v>2321</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>217212201.82</v>
+        <v>394549598.81</v>
       </c>
       <c r="F44" t="n">
-        <v>204765475.8</v>
+        <v>359596023.43</v>
       </c>
       <c r="G44" t="n">
-        <v>196759897.63</v>
+        <v>346696259.17</v>
       </c>
       <c r="H44" t="n">
-        <v>1333045.2</v>
+        <v>1425788.73</v>
       </c>
       <c r="I44" t="n">
-        <v>7655898.75</v>
+        <v>30573782.13</v>
       </c>
       <c r="J44" t="n">
-        <v>8988943.949999999</v>
+        <v>31999570.86</v>
       </c>
     </row>
     <row r="45">
@@ -2016,34 +2010,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2201</v>
+        <v>2421</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>28359171.85</v>
+        <v>61510642.64</v>
       </c>
       <c r="F45" t="n">
-        <v>27321777.4</v>
+        <v>43124254.63</v>
       </c>
       <c r="G45" t="n">
-        <v>25220175.31</v>
+        <v>41282826.79</v>
       </c>
       <c r="H45" t="n">
-        <v>6473.82</v>
+        <v>713315.27</v>
       </c>
       <c r="I45" t="n">
-        <v>1262449.13</v>
+        <v>7206237.15</v>
       </c>
       <c r="J45" t="n">
-        <v>1268922.95</v>
+        <v>7919552.42</v>
       </c>
     </row>
     <row r="46">
@@ -2052,34 +2046,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2241</v>
+        <v>2101</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>195257062.85</v>
+        <v>217212201.82</v>
       </c>
       <c r="F46" t="n">
-        <v>182522813.41</v>
+        <v>204765475.8</v>
       </c>
       <c r="G46" t="n">
-        <v>181974009.41</v>
+        <v>196759897.63</v>
       </c>
       <c r="H46" t="n">
-        <v>10483113.83</v>
+        <v>1333045.2</v>
       </c>
       <c r="I46" t="n">
-        <v>1680822.65</v>
+        <v>7655898.75</v>
       </c>
       <c r="J46" t="n">
-        <v>12163936.48</v>
+        <v>8988943.949999999</v>
       </c>
     </row>
     <row r="47">
@@ -2088,34 +2082,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2371</v>
+        <v>2201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>290312222.92</v>
+        <v>28359171.85</v>
       </c>
       <c r="F47" t="n">
-        <v>283815022.34</v>
+        <v>27321777.4</v>
       </c>
       <c r="G47" t="n">
-        <v>282551558.48</v>
+        <v>25220175.31</v>
       </c>
       <c r="H47" t="n">
-        <v>654297.5699999999</v>
+        <v>6473.82</v>
       </c>
       <c r="I47" t="n">
-        <v>7082912.77</v>
+        <v>1262449.13</v>
       </c>
       <c r="J47" t="n">
-        <v>7737210.34</v>
+        <v>1268922.95</v>
       </c>
     </row>
     <row r="48">
@@ -2124,34 +2118,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2331</v>
+        <v>2241</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>35739703.74</v>
+        <v>195257062.85</v>
       </c>
       <c r="F48" t="n">
-        <v>34318152.9</v>
+        <v>182522813.41</v>
       </c>
       <c r="G48" t="n">
-        <v>33074380.83</v>
+        <v>181974009.41</v>
       </c>
       <c r="H48" t="n">
-        <v>420781.11</v>
+        <v>10483113.83</v>
       </c>
       <c r="I48" t="n">
-        <v>436480.49</v>
+        <v>1680822.65</v>
       </c>
       <c r="J48" t="n">
-        <v>857261.6</v>
+        <v>12163936.48</v>
       </c>
     </row>
     <row r="49">
@@ -2160,34 +2154,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2011</v>
+        <v>2371</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2066687330.24</v>
+        <v>290312222.92</v>
       </c>
       <c r="F49" t="n">
-        <v>1811898139.4</v>
+        <v>283815022.34</v>
       </c>
       <c r="G49" t="n">
-        <v>1767628149.66</v>
+        <v>282551558.48</v>
       </c>
       <c r="H49" t="n">
-        <v>1062515.58</v>
+        <v>654297.5699999999</v>
       </c>
       <c r="I49" t="n">
-        <v>92904525.54000001</v>
+        <v>7082912.77</v>
       </c>
       <c r="J49" t="n">
-        <v>93967041.12</v>
+        <v>7737210.34</v>
       </c>
     </row>
     <row r="50">
@@ -2196,34 +2190,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2121</v>
+        <v>2331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3302390465.79</v>
+        <v>35739703.74</v>
       </c>
       <c r="F50" t="n">
-        <v>3251209178.87</v>
+        <v>34318152.9</v>
       </c>
       <c r="G50" t="n">
-        <v>3202602086.92</v>
+        <v>33074380.83</v>
       </c>
       <c r="H50" t="n">
-        <v>294911.07</v>
+        <v>420781.11</v>
       </c>
       <c r="I50" t="n">
-        <v>15606900.02</v>
+        <v>436480.49</v>
       </c>
       <c r="J50" t="n">
-        <v>15901811.09</v>
+        <v>857261.6</v>
       </c>
     </row>
     <row r="51">
@@ -2232,34 +2226,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2251</v>
+        <v>2011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>41105200.07</v>
+        <v>2066687330.24</v>
       </c>
       <c r="F51" t="n">
-        <v>38759738.47</v>
+        <v>1811898139.4</v>
       </c>
       <c r="G51" t="n">
-        <v>36259002.32</v>
+        <v>1767628149.66</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1062515.58</v>
       </c>
       <c r="I51" t="n">
-        <v>1415037.52</v>
+        <v>92904525.54000001</v>
       </c>
       <c r="J51" t="n">
-        <v>1415037.52</v>
+        <v>93967041.12</v>
       </c>
     </row>
     <row r="52">
@@ -2268,34 +2262,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2041</v>
+        <v>2121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2901561.62</v>
+        <v>3302390465.79</v>
       </c>
       <c r="F52" t="n">
-        <v>2865088.76</v>
+        <v>3251209178.87</v>
       </c>
       <c r="G52" t="n">
-        <v>2860275.95</v>
+        <v>3202602086.92</v>
       </c>
       <c r="H52" t="n">
-        <v>3394.97</v>
+        <v>294911.07</v>
       </c>
       <c r="I52" t="n">
-        <v>24471.67</v>
+        <v>15606900.02</v>
       </c>
       <c r="J52" t="n">
-        <v>27866.64</v>
+        <v>15901811.09</v>
       </c>
     </row>
     <row r="53">
@@ -2304,34 +2298,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1101</v>
+        <v>2251</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>18048368.2</v>
+        <v>41105200.07</v>
       </c>
       <c r="F53" t="n">
-        <v>17928588.51</v>
+        <v>38759738.47</v>
       </c>
       <c r="G53" t="n">
-        <v>17774694.27</v>
+        <v>36259002.32</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>57114.59</v>
+        <v>1415037.52</v>
       </c>
       <c r="J53" t="n">
-        <v>57114.59</v>
+        <v>1415037.52</v>
       </c>
     </row>
     <row r="54">
@@ -2340,34 +2334,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1915</v>
+        <v>2041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>20043002.56</v>
+        <v>2901561.62</v>
       </c>
       <c r="F54" t="n">
-        <v>20043002.56</v>
+        <v>2865088.76</v>
       </c>
       <c r="G54" t="n">
-        <v>20043002.56</v>
+        <v>2860275.95</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>3394.97</v>
       </c>
       <c r="I54" t="n">
-        <v>46.77</v>
+        <v>24471.67</v>
       </c>
       <c r="J54" t="n">
-        <v>46.77</v>
+        <v>27866.64</v>
       </c>
     </row>
     <row r="55">
@@ -2376,34 +2370,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1511</v>
+        <v>1101</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3138279917.06</v>
+        <v>18048368.2</v>
       </c>
       <c r="F55" t="n">
-        <v>3076106533.57</v>
+        <v>17928588.51</v>
       </c>
       <c r="G55" t="n">
-        <v>3055981056.68</v>
+        <v>17774694.27</v>
       </c>
       <c r="H55" t="n">
-        <v>18355346.55</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>41103215.43</v>
+        <v>57114.59</v>
       </c>
       <c r="J55" t="n">
-        <v>59458561.98</v>
+        <v>57114.59</v>
       </c>
     </row>
     <row r="56">
@@ -2412,34 +2406,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1251</v>
+        <v>1915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>17184629357.54</v>
+        <v>20043002.56</v>
       </c>
       <c r="F56" t="n">
-        <v>16913388822.07</v>
+        <v>20043002.56</v>
       </c>
       <c r="G56" t="n">
-        <v>16881355805.92</v>
+        <v>20043002.56</v>
       </c>
       <c r="H56" t="n">
-        <v>22568008.23</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>179457677.69</v>
+        <v>46.77</v>
       </c>
       <c r="J56" t="n">
-        <v>202025685.92</v>
+        <v>46.77</v>
       </c>
     </row>
     <row r="57">
@@ -2448,34 +2442,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1721</v>
+        <v>1511</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>10652572.94</v>
+        <v>3138279917.06</v>
       </c>
       <c r="F57" t="n">
-        <v>10295525.12</v>
+        <v>3076106533.57</v>
       </c>
       <c r="G57" t="n">
-        <v>9939287.65</v>
+        <v>3055981056.68</v>
       </c>
       <c r="H57" t="n">
-        <v>10152.64</v>
+        <v>18355346.55</v>
       </c>
       <c r="I57" t="n">
-        <v>276281.69</v>
+        <v>41103215.43</v>
       </c>
       <c r="J57" t="n">
-        <v>286434.33</v>
+        <v>59458561.98</v>
       </c>
     </row>
     <row r="58">
@@ -2484,34 +2478,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1231</v>
+        <v>1251</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>319941879.07</v>
+        <v>17184629357.54</v>
       </c>
       <c r="F58" t="n">
-        <v>286029024.67</v>
+        <v>16913388822.07</v>
       </c>
       <c r="G58" t="n">
-        <v>275453889.56</v>
+        <v>16881355805.92</v>
       </c>
       <c r="H58" t="n">
-        <v>4468309.21</v>
+        <v>22568008.23</v>
       </c>
       <c r="I58" t="n">
-        <v>18499399.92</v>
+        <v>179457677.69</v>
       </c>
       <c r="J58" t="n">
-        <v>22967709.13</v>
+        <v>202025685.92</v>
       </c>
     </row>
     <row r="59">
@@ -2520,34 +2514,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1631</v>
+        <v>1721</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>12493555.88</v>
+        <v>10652572.94</v>
       </c>
       <c r="F59" t="n">
-        <v>12400512.79</v>
+        <v>10295525.12</v>
       </c>
       <c r="G59" t="n">
-        <v>12257285.88</v>
+        <v>9939287.65</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>10152.64</v>
       </c>
       <c r="I59" t="n">
-        <v>138983.68</v>
+        <v>276281.69</v>
       </c>
       <c r="J59" t="n">
-        <v>138983.68</v>
+        <v>286434.33</v>
       </c>
     </row>
     <row r="60">
@@ -2556,34 +2550,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1711</v>
+        <v>1231</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>181181663.88</v>
+        <v>319941879.07</v>
       </c>
       <c r="F60" t="n">
-        <v>101620737.74</v>
+        <v>286029024.67</v>
       </c>
       <c r="G60" t="n">
-        <v>97019401.54000001</v>
+        <v>275453889.56</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>4468309.21</v>
       </c>
       <c r="I60" t="n">
-        <v>76618911.3</v>
+        <v>18499399.92</v>
       </c>
       <c r="J60" t="n">
-        <v>76618911.3</v>
+        <v>22967709.13</v>
       </c>
     </row>
     <row r="61">
@@ -2592,34 +2586,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1271</v>
+        <v>1631</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>261449910.33</v>
+        <v>12493555.88</v>
       </c>
       <c r="F61" t="n">
-        <v>260070135.18</v>
+        <v>12400512.79</v>
       </c>
       <c r="G61" t="n">
-        <v>257629551.13</v>
+        <v>12257285.88</v>
       </c>
       <c r="H61" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>2485549.72</v>
+        <v>138983.68</v>
       </c>
       <c r="J61" t="n">
-        <v>2488069.72</v>
+        <v>138983.68</v>
       </c>
     </row>
     <row r="62">
@@ -2628,34 +2622,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1221</v>
+        <v>1711</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>425928118.33</v>
+        <v>181181663.88</v>
       </c>
       <c r="F62" t="n">
-        <v>106813200.9</v>
+        <v>101620737.74</v>
       </c>
       <c r="G62" t="n">
-        <v>104972627.41</v>
+        <v>97019401.54000001</v>
       </c>
       <c r="H62" t="n">
-        <v>3819.55</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>10240167.34</v>
+        <v>76618911.3</v>
       </c>
       <c r="J62" t="n">
-        <v>10243986.89</v>
+        <v>76618911.3</v>
       </c>
     </row>
     <row r="63">
@@ -2664,34 +2658,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1481</v>
+        <v>1271</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>338412512.01</v>
+        <v>261449910.33</v>
       </c>
       <c r="F63" t="n">
-        <v>284330922.14</v>
+        <v>260070135.18</v>
       </c>
       <c r="G63" t="n">
-        <v>273376533.99</v>
+        <v>257629551.13</v>
       </c>
       <c r="H63" t="n">
-        <v>6492833.43</v>
+        <v>2520</v>
       </c>
       <c r="I63" t="n">
-        <v>13954481.02</v>
+        <v>2485549.72</v>
       </c>
       <c r="J63" t="n">
-        <v>20447314.45</v>
+        <v>2488069.72</v>
       </c>
     </row>
     <row r="64">
@@ -2700,34 +2694,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>20024070516.28</v>
+        <v>425928118.33</v>
       </c>
       <c r="F64" t="n">
-        <v>19817333122</v>
+        <v>106813200.9</v>
       </c>
       <c r="G64" t="n">
-        <v>19583419698.99</v>
+        <v>104972627.41</v>
       </c>
       <c r="H64" t="n">
-        <v>102690852.14</v>
+        <v>3819.55</v>
       </c>
       <c r="I64" t="n">
-        <v>437921985.25</v>
+        <v>10240167.34</v>
       </c>
       <c r="J64" t="n">
-        <v>540612837.39</v>
+        <v>10243986.89</v>
       </c>
     </row>
     <row r="65">
@@ -2736,34 +2730,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1191</v>
+        <v>1481</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1886784188.81</v>
+        <v>338412512.01</v>
       </c>
       <c r="F65" t="n">
-        <v>1792612515.59</v>
+        <v>284330922.14</v>
       </c>
       <c r="G65" t="n">
-        <v>1767643635.43</v>
+        <v>273376533.99</v>
       </c>
       <c r="H65" t="n">
-        <v>5956448.89</v>
+        <v>6492833.43</v>
       </c>
       <c r="I65" t="n">
-        <v>38130787.08</v>
+        <v>13954481.02</v>
       </c>
       <c r="J65" t="n">
-        <v>44087235.97</v>
+        <v>20447314.45</v>
       </c>
     </row>
     <row r="66">
@@ -2772,34 +2766,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1491</v>
+        <v>1261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>971196665.48</v>
+        <v>20024070516.28</v>
       </c>
       <c r="F66" t="n">
-        <v>965761230.4299999</v>
+        <v>19817333122</v>
       </c>
       <c r="G66" t="n">
-        <v>950181400.99</v>
+        <v>19583419698.99</v>
       </c>
       <c r="H66" t="n">
-        <v>1028658.15</v>
+        <v>102690852.14</v>
       </c>
       <c r="I66" t="n">
-        <v>17535020.6</v>
+        <v>437921985.25</v>
       </c>
       <c r="J66" t="n">
-        <v>18563678.75</v>
+        <v>540612837.39</v>
       </c>
     </row>
     <row r="67">
@@ -2808,34 +2802,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1301</v>
+        <v>1191</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>480636059.58</v>
+        <v>1886784188.81</v>
       </c>
       <c r="F67" t="n">
-        <v>393222333.81</v>
+        <v>1792612515.59</v>
       </c>
       <c r="G67" t="n">
-        <v>363896390.26</v>
+        <v>1767643635.43</v>
       </c>
       <c r="H67" t="n">
-        <v>11727528.06</v>
+        <v>5956448.89</v>
       </c>
       <c r="I67" t="n">
-        <v>201174882.85</v>
+        <v>38130787.08</v>
       </c>
       <c r="J67" t="n">
-        <v>212902410.91</v>
+        <v>44087235.97</v>
       </c>
     </row>
     <row r="68">
@@ -2844,34 +2838,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1451</v>
+        <v>1491</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4556477829.69</v>
+        <v>971196665.48</v>
       </c>
       <c r="F68" t="n">
-        <v>4357599952.24</v>
+        <v>965761230.4299999</v>
       </c>
       <c r="G68" t="n">
-        <v>4322020545.17</v>
+        <v>950181400.99</v>
       </c>
       <c r="H68" t="n">
-        <v>4833097.2</v>
+        <v>1028658.15</v>
       </c>
       <c r="I68" t="n">
-        <v>108147895.72</v>
+        <v>17535020.6</v>
       </c>
       <c r="J68" t="n">
-        <v>112980992.92</v>
+        <v>18563678.75</v>
       </c>
     </row>
     <row r="69">
@@ -2880,34 +2874,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185286819.99</v>
+        <v>480636059.58</v>
       </c>
       <c r="F69" t="n">
-        <v>178437283.68</v>
+        <v>393222333.81</v>
       </c>
       <c r="G69" t="n">
-        <v>172648640.16</v>
+        <v>363896390.26</v>
       </c>
       <c r="H69" t="n">
-        <v>271467.65</v>
+        <v>11727528.06</v>
       </c>
       <c r="I69" t="n">
-        <v>5465504.58</v>
+        <v>201174882.85</v>
       </c>
       <c r="J69" t="n">
-        <v>5736972.23</v>
+        <v>212902410.91</v>
       </c>
     </row>
     <row r="70">
@@ -2916,34 +2910,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>940771355.51</v>
+        <v>4556477829.69</v>
       </c>
       <c r="F70" t="n">
-        <v>840171011.05</v>
+        <v>4357599952.24</v>
       </c>
       <c r="G70" t="n">
-        <v>779489331.71</v>
+        <v>4322020545.17</v>
       </c>
       <c r="H70" t="n">
-        <v>9145522.6</v>
+        <v>4833097.2</v>
       </c>
       <c r="I70" t="n">
-        <v>62616118.7</v>
+        <v>108147895.72</v>
       </c>
       <c r="J70" t="n">
-        <v>71761641.3</v>
+        <v>112980992.92</v>
       </c>
     </row>
     <row r="71">
@@ -2952,34 +2946,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2211</v>
+        <v>1371</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>16376327.77</v>
+        <v>185286819.99</v>
       </c>
       <c r="F71" t="n">
-        <v>15665660.91</v>
+        <v>178437283.68</v>
       </c>
       <c r="G71" t="n">
-        <v>14963532.88</v>
+        <v>172648640.16</v>
       </c>
       <c r="H71" t="n">
-        <v>84375.35000000001</v>
+        <v>271467.65</v>
       </c>
       <c r="I71" t="n">
-        <v>903154.46</v>
+        <v>5465504.58</v>
       </c>
       <c r="J71" t="n">
-        <v>987529.8100000001</v>
+        <v>5736972.23</v>
       </c>
     </row>
     <row r="72">
@@ -2988,34 +2982,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2351</v>
+        <v>1501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>431560939.48</v>
+        <v>940771355.51</v>
       </c>
       <c r="F72" t="n">
-        <v>399364373.03</v>
+        <v>840171011.05</v>
       </c>
       <c r="G72" t="n">
-        <v>391027226.76</v>
+        <v>779489331.71</v>
       </c>
       <c r="H72" t="n">
-        <v>1690845.8</v>
+        <v>9145522.6</v>
       </c>
       <c r="I72" t="n">
-        <v>7591910.97</v>
+        <v>62616118.7</v>
       </c>
       <c r="J72" t="n">
-        <v>9282756.77</v>
+        <v>71761641.3</v>
       </c>
     </row>
     <row r="73">
@@ -3024,34 +3018,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2311</v>
+        <v>2211</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>533150763.61</v>
+        <v>16376327.77</v>
       </c>
       <c r="F73" t="n">
-        <v>503448723.24</v>
+        <v>15665660.91</v>
       </c>
       <c r="G73" t="n">
-        <v>492058770.59</v>
+        <v>14963532.88</v>
       </c>
       <c r="H73" t="n">
-        <v>274974.01</v>
+        <v>84375.35000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>39010212.22</v>
+        <v>903154.46</v>
       </c>
       <c r="J73" t="n">
-        <v>39285186.23</v>
+        <v>987529.8100000001</v>
       </c>
     </row>
     <row r="74">
@@ -3060,33 +3054,105 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>431560939.48</v>
+      </c>
+      <c r="F74" t="n">
+        <v>399364373.03</v>
+      </c>
+      <c r="G74" t="n">
+        <v>391027226.76</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1690845.8</v>
+      </c>
+      <c r="I74" t="n">
+        <v>7591910.97</v>
+      </c>
+      <c r="J74" t="n">
+        <v>9282756.77</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>533150763.61</v>
+      </c>
+      <c r="F75" t="n">
+        <v>503448723.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>492058770.59</v>
+      </c>
+      <c r="H75" t="n">
+        <v>274974.01</v>
+      </c>
+      <c r="I75" t="n">
+        <v>39010212.22</v>
+      </c>
+      <c r="J75" t="n">
+        <v>39285186.23</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C76" t="n">
         <v>2281</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E76" t="n">
         <v>7417117.22</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F76" t="n">
         <v>6859782.46</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G76" t="n">
         <v>6435691.91</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H76" t="n">
         <v>0</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I76" t="n">
         <v>231057.02</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J76" t="n">
         <v>231057.02</v>
       </c>
     </row>

--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,34 +558,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARMVA</t>
+          <t>ALMG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2461</v>
+        <v>1011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4789292.11</v>
+        <v>2149209573.3</v>
       </c>
       <c r="F4" t="n">
-        <v>3903632.02</v>
+        <v>2108068512.69</v>
       </c>
       <c r="G4" t="n">
-        <v>3547153</v>
+        <v>2091020383.51</v>
       </c>
       <c r="H4" t="n">
-        <v>13266.26</v>
+        <v>762.97</v>
       </c>
       <c r="I4" t="n">
-        <v>175463.15</v>
+        <v>40404763.93</v>
       </c>
       <c r="J4" t="n">
-        <v>188729.41</v>
+        <v>40405526.9</v>
       </c>
     </row>
     <row r="5">
@@ -594,34 +594,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARSAE -MG</t>
+          <t>ARMVA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2441</v>
+        <v>2461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19031476.38</v>
+        <v>4789292.11</v>
       </c>
       <c r="F5" t="n">
-        <v>18693505.57</v>
+        <v>3903632.02</v>
       </c>
       <c r="G5" t="n">
-        <v>18533956.49</v>
+        <v>3547153</v>
       </c>
       <c r="H5" t="n">
-        <v>87975.14999999999</v>
+        <v>13266.26</v>
       </c>
       <c r="I5" t="n">
-        <v>226885.18</v>
+        <v>175463.15</v>
       </c>
       <c r="J5" t="n">
-        <v>314860.33</v>
+        <v>188729.41</v>
       </c>
     </row>
     <row r="6">
@@ -630,29 +630,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARTEMIG</t>
+          <t>ARSAE -MG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2471</v>
+        <v>2441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
+          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12995181.74</v>
+        <v>19031476.38</v>
       </c>
       <c r="F6" t="n">
-        <v>9545227.800000001</v>
+        <v>18693505.57</v>
       </c>
       <c r="G6" t="n">
-        <v>9172117.300000001</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>18533956.49</v>
+      </c>
+      <c r="H6" t="n">
+        <v>87975.14999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>226885.18</v>
+      </c>
+      <c r="J6" t="n">
+        <v>314860.33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -660,35 +666,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CBMMG</t>
+          <t>ARTEMIG</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1401</v>
+        <v>2471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2074027252.07</v>
+        <v>12995181.74</v>
       </c>
       <c r="F7" t="n">
-        <v>1999073232.13</v>
+        <v>9545227.800000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1988491760.28</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4678551.78</v>
-      </c>
-      <c r="I7" t="n">
-        <v>71714800.70999999</v>
-      </c>
-      <c r="J7" t="n">
-        <v>76393352.48999999</v>
-      </c>
+        <v>9172117.300000001</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CGE</t>
+          <t>CBMMG</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1521</v>
+        <v>1401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CONTROLADORIA-GERAL DO ESTADO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70667226.11</v>
+        <v>2074027252.07</v>
       </c>
       <c r="F8" t="n">
-        <v>69307261.73999999</v>
+        <v>1999073232.13</v>
       </c>
       <c r="G8" t="n">
-        <v>69083242.06</v>
+        <v>1988491760.28</v>
       </c>
       <c r="H8" t="n">
-        <v>39281.15</v>
+        <v>4678551.78</v>
       </c>
       <c r="I8" t="n">
-        <v>907780.5</v>
+        <v>71714800.70999999</v>
       </c>
       <c r="J8" t="n">
-        <v>947061.65</v>
+        <v>76393352.48999999</v>
       </c>
     </row>
     <row r="9">
@@ -732,34 +732,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DER-MG</t>
+          <t>CGE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2301</v>
+        <v>1521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>CONTROLADORIA-GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2143327357.7</v>
+        <v>70667226.11</v>
       </c>
       <c r="F9" t="n">
-        <v>1655881609.23</v>
+        <v>69307261.73999999</v>
       </c>
       <c r="G9" t="n">
-        <v>1611441301.37</v>
+        <v>69083242.06</v>
       </c>
       <c r="H9" t="n">
-        <v>14178677.35</v>
+        <v>39281.15</v>
       </c>
       <c r="I9" t="n">
-        <v>411934193.73</v>
+        <v>907780.5</v>
       </c>
       <c r="J9" t="n">
-        <v>426112871.08</v>
+        <v>947061.65</v>
       </c>
     </row>
     <row r="10">
@@ -768,34 +768,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EGE - SEF</t>
+          <t>DEF PUB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1911</v>
+        <v>1441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1211264345.43</v>
+        <v>1096185910.71</v>
       </c>
       <c r="F10" t="n">
-        <v>1127569424.8</v>
+        <v>1073000349.22</v>
       </c>
       <c r="G10" t="n">
-        <v>1127569424.8</v>
+        <v>1062452304.51</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>245007.27</v>
       </c>
       <c r="I10" t="n">
-        <v>70456474.19</v>
+        <v>19268306.91</v>
       </c>
       <c r="J10" t="n">
-        <v>70456474.19</v>
+        <v>19513314.18</v>
       </c>
     </row>
     <row r="11">
@@ -804,34 +804,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EGE-SEPLAG</t>
+          <t>DER-MG</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1941</v>
+        <v>2301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>194535650.21</v>
+        <v>2143327357.7</v>
       </c>
       <c r="F11" t="n">
-        <v>193268761.55</v>
+        <v>1655881609.23</v>
       </c>
       <c r="G11" t="n">
-        <v>193178812.25</v>
+        <v>1611441301.37</v>
       </c>
       <c r="H11" t="n">
-        <v>27888.27</v>
+        <v>14178677.35</v>
       </c>
       <c r="I11" t="n">
-        <v>1669467.18</v>
+        <v>411934193.73</v>
       </c>
       <c r="J11" t="n">
-        <v>1697355.45</v>
+        <v>426112871.08</v>
       </c>
     </row>
     <row r="12">
@@ -840,29 +840,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EMATER</t>
+          <t>EGE - SEF</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3041</v>
+        <v>1911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>411646902.58</v>
+        <v>1211264345.43</v>
       </c>
       <c r="F12" t="n">
-        <v>411646902.58</v>
+        <v>1127569424.8</v>
       </c>
       <c r="G12" t="n">
-        <v>411646902.58</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>1127569424.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>70456474.19</v>
+      </c>
+      <c r="J12" t="n">
+        <v>70456474.19</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -870,29 +876,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>EGE-SEPLAG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3151</v>
+        <v>1941</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30003569.6</v>
+        <v>194535650.21</v>
       </c>
       <c r="F13" t="n">
-        <v>30003569.6</v>
+        <v>193268761.55</v>
       </c>
       <c r="G13" t="n">
-        <v>30003569.6</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>193178812.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>27888.27</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1669467.18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1697355.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -900,25 +912,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMATER</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3051</v>
+        <v>3041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>150702794.76</v>
+        <v>411646902.58</v>
       </c>
       <c r="F14" t="n">
-        <v>150702794.76</v>
+        <v>411646902.58</v>
       </c>
       <c r="G14" t="n">
-        <v>150702794.76</v>
+        <v>411646902.58</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -930,35 +942,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1541</v>
+        <v>3151</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25352006.23</v>
+        <v>30003569.6</v>
       </c>
       <c r="F15" t="n">
-        <v>23581392.72</v>
+        <v>30003569.6</v>
       </c>
       <c r="G15" t="n">
-        <v>22865578.49</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>351886.66</v>
-      </c>
-      <c r="J15" t="n">
-        <v>351886.66</v>
-      </c>
+        <v>30003569.6</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -966,35 +972,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4541</v>
+        <v>3051</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>350405</v>
+        <v>150702794.76</v>
       </c>
       <c r="F16" t="n">
-        <v>318593.91</v>
+        <v>150702794.76</v>
       </c>
       <c r="G16" t="n">
-        <v>300914.63</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>26392.47</v>
-      </c>
-      <c r="J16" t="n">
-        <v>26392.47</v>
-      </c>
+        <v>150702794.76</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1002,34 +1002,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2171</v>
+        <v>1541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9439748.619999999</v>
+        <v>25352006.23</v>
       </c>
       <c r="F17" t="n">
-        <v>9225890.4</v>
+        <v>23581392.72</v>
       </c>
       <c r="G17" t="n">
-        <v>8465439.720000001</v>
+        <v>22865578.49</v>
       </c>
       <c r="H17" t="n">
-        <v>480546.01</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>177676.07</v>
+        <v>351886.66</v>
       </c>
       <c r="J17" t="n">
-        <v>658222.08</v>
+        <v>351886.66</v>
       </c>
     </row>
     <row r="18">
@@ -1038,34 +1038,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2071</v>
+        <v>4541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>585603048.33</v>
+        <v>350405</v>
       </c>
       <c r="F18" t="n">
-        <v>580710591.1900001</v>
+        <v>318593.91</v>
       </c>
       <c r="G18" t="n">
-        <v>574854711.54</v>
+        <v>300914.63</v>
       </c>
       <c r="H18" t="n">
-        <v>1239266.23</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>8506819.619999999</v>
+        <v>26392.47</v>
       </c>
       <c r="J18" t="n">
-        <v>9746085.85</v>
+        <v>26392.47</v>
       </c>
     </row>
     <row r="19">
@@ -1074,34 +1074,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2181</v>
+        <v>2171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>63217552.93</v>
+        <v>9439748.619999999</v>
       </c>
       <c r="F19" t="n">
-        <v>60940567.95</v>
+        <v>9225890.4</v>
       </c>
       <c r="G19" t="n">
-        <v>56959723.43</v>
+        <v>8465439.720000001</v>
       </c>
       <c r="H19" t="n">
-        <v>119258.05</v>
+        <v>480546.01</v>
       </c>
       <c r="I19" t="n">
-        <v>2222004.25</v>
+        <v>177676.07</v>
       </c>
       <c r="J19" t="n">
-        <v>2341262.3</v>
+        <v>658222.08</v>
       </c>
     </row>
     <row r="20">
@@ -1110,34 +1110,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4331</v>
+        <v>2071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3035441.45</v>
+        <v>585603048.33</v>
       </c>
       <c r="F20" t="n">
-        <v>97428.45</v>
+        <v>580710591.1900001</v>
       </c>
       <c r="G20" t="n">
-        <v>93102.96000000001</v>
+        <v>574854711.54</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1239266.23</v>
       </c>
       <c r="I20" t="n">
-        <v>206186.42</v>
+        <v>8506819.619999999</v>
       </c>
       <c r="J20" t="n">
-        <v>206186.42</v>
+        <v>9746085.85</v>
       </c>
     </row>
     <row r="21">
@@ -1146,34 +1146,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2091</v>
+        <v>2181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>75621728.88</v>
+        <v>63217552.93</v>
       </c>
       <c r="F21" t="n">
-        <v>74134505.91</v>
+        <v>60940567.95</v>
       </c>
       <c r="G21" t="n">
-        <v>72540998.40000001</v>
+        <v>56959723.43</v>
       </c>
       <c r="H21" t="n">
-        <v>24329.43</v>
+        <v>119258.05</v>
       </c>
       <c r="I21" t="n">
-        <v>2347292.71</v>
+        <v>2222004.25</v>
       </c>
       <c r="J21" t="n">
-        <v>2371622.14</v>
+        <v>2341262.3</v>
       </c>
     </row>
     <row r="22">
@@ -1182,34 +1182,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4251</v>
+        <v>4331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>172407716.3</v>
+        <v>3035441.45</v>
       </c>
       <c r="F22" t="n">
-        <v>169951293.67</v>
+        <v>97428.45</v>
       </c>
       <c r="G22" t="n">
-        <v>168474678.26</v>
+        <v>93102.96000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>1112168.89</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>5271380.07</v>
+        <v>206186.42</v>
       </c>
       <c r="J22" t="n">
-        <v>6383548.96</v>
+        <v>206186.42</v>
       </c>
     </row>
     <row r="23">
@@ -1218,34 +1218,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4491</v>
+        <v>2091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2634653.32</v>
+        <v>75621728.88</v>
       </c>
       <c r="F23" t="n">
-        <v>2500037.94</v>
+        <v>74134505.91</v>
       </c>
       <c r="G23" t="n">
-        <v>1882700.63</v>
+        <v>72540998.40000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>24329.43</v>
       </c>
       <c r="I23" t="n">
-        <v>15394</v>
+        <v>2347292.71</v>
       </c>
       <c r="J23" t="n">
-        <v>15394</v>
+        <v>2371622.14</v>
       </c>
     </row>
     <row r="24">
@@ -1254,34 +1254,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4101</v>
+        <v>4251</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>16870000</v>
+        <v>172407716.3</v>
       </c>
       <c r="F24" t="n">
-        <v>16870000</v>
+        <v>169951293.67</v>
       </c>
       <c r="G24" t="n">
-        <v>15570000</v>
+        <v>168474678.26</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1112168.89</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5271380.07</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>6383548.96</v>
       </c>
     </row>
     <row r="25">
@@ -1290,34 +1290,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4601</v>
+        <v>4491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1473191.28</v>
+        <v>2634653.32</v>
       </c>
       <c r="F25" t="n">
-        <v>1033455.88</v>
+        <v>2500037.94</v>
       </c>
       <c r="G25" t="n">
-        <v>987548.8100000001</v>
+        <v>1882700.63</v>
       </c>
       <c r="H25" t="n">
-        <v>2887433.54</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3042047.61</v>
+        <v>15394</v>
       </c>
       <c r="J25" t="n">
-        <v>5929481.15</v>
+        <v>15394</v>
       </c>
     </row>
     <row r="26">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4291</v>
+        <v>4101</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12684000278.8</v>
+        <v>16870000</v>
       </c>
       <c r="F26" t="n">
-        <v>12066473764.49</v>
+        <v>16870000</v>
       </c>
       <c r="G26" t="n">
-        <v>11940374576.38</v>
+        <v>15570000</v>
       </c>
       <c r="H26" t="n">
-        <v>622978466.21</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>547393802.42</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1170372268.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1362,34 +1362,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4691</v>
+        <v>4601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>64705464.4</v>
+        <v>1473191.28</v>
       </c>
       <c r="F27" t="n">
-        <v>14436749.82</v>
+        <v>1033455.88</v>
       </c>
       <c r="G27" t="n">
-        <v>9663966.02</v>
+        <v>987548.8100000001</v>
       </c>
       <c r="H27" t="n">
-        <v>2093885.86</v>
+        <v>2887433.54</v>
       </c>
       <c r="I27" t="n">
-        <v>31330993.84</v>
+        <v>3042047.61</v>
       </c>
       <c r="J27" t="n">
-        <v>33424879.7</v>
+        <v>5929481.15</v>
       </c>
     </row>
     <row r="28">
@@ -1398,34 +1398,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4701</v>
+        <v>4451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2107186.39</v>
+        <v>48631312.58</v>
       </c>
       <c r="F28" t="n">
-        <v>781389.39</v>
+        <v>11932319.97</v>
       </c>
       <c r="G28" t="n">
-        <v>754127.26</v>
+        <v>11013107.33</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>679.54</v>
       </c>
       <c r="I28" t="n">
-        <v>86523.72</v>
+        <v>8080205.78</v>
       </c>
       <c r="J28" t="n">
-        <v>86523.72</v>
+        <v>8080885.32</v>
       </c>
     </row>
     <row r="29">
@@ -1434,34 +1434,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4711</v>
+        <v>4031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>18258352481.54</v>
+        <v>2589774328.16</v>
       </c>
       <c r="F29" t="n">
-        <v>18256651559.23</v>
+        <v>2175663822.83</v>
       </c>
       <c r="G29" t="n">
-        <v>18259071357.13</v>
+        <v>1951730257.86</v>
       </c>
       <c r="H29" t="n">
-        <v>46065.66</v>
+        <v>4528727.26</v>
       </c>
       <c r="I29" t="n">
-        <v>2149146.04</v>
+        <v>173911941.97</v>
       </c>
       <c r="J29" t="n">
-        <v>2195211.7</v>
+        <v>178440669.23</v>
       </c>
     </row>
     <row r="30">
@@ -1470,34 +1470,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2151</v>
+        <v>4291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>81750398.86</v>
+        <v>12684000278.8</v>
       </c>
       <c r="F30" t="n">
-        <v>76284993.93000001</v>
+        <v>12066473764.49</v>
       </c>
       <c r="G30" t="n">
-        <v>75483300.69</v>
+        <v>11940374576.38</v>
       </c>
       <c r="H30" t="n">
-        <v>24887.1</v>
+        <v>622978466.21</v>
       </c>
       <c r="I30" t="n">
-        <v>1770214.54</v>
+        <v>547393802.42</v>
       </c>
       <c r="J30" t="n">
-        <v>1795101.64</v>
+        <v>1170372268.63</v>
       </c>
     </row>
     <row r="31">
@@ -1506,34 +1506,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2271</v>
+        <v>4691</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2478485587.5</v>
+        <v>64705464.4</v>
       </c>
       <c r="F31" t="n">
-        <v>2347428600.43</v>
+        <v>14436749.82</v>
       </c>
       <c r="G31" t="n">
-        <v>2300004443.95</v>
+        <v>9663966.02</v>
       </c>
       <c r="H31" t="n">
-        <v>18122531.3</v>
+        <v>2093885.86</v>
       </c>
       <c r="I31" t="n">
-        <v>63228349.74</v>
+        <v>31330993.84</v>
       </c>
       <c r="J31" t="n">
-        <v>81350881.04000001</v>
+        <v>33424879.7</v>
       </c>
     </row>
     <row r="32">
@@ -1542,34 +1542,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4341</v>
+        <v>4701</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2288740.74</v>
+        <v>2107186.39</v>
       </c>
       <c r="F32" t="n">
-        <v>1318579.4</v>
+        <v>781389.39</v>
       </c>
       <c r="G32" t="n">
-        <v>1060943.48</v>
+        <v>754127.26</v>
       </c>
       <c r="H32" t="n">
-        <v>223487.09</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>548165.38</v>
+        <v>86523.72</v>
       </c>
       <c r="J32" t="n">
-        <v>771652.47</v>
+        <v>86523.72</v>
       </c>
     </row>
     <row r="33">
@@ -1578,34 +1578,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4091</v>
+        <v>4711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>610536.65</v>
+        <v>18258352481.54</v>
       </c>
       <c r="F33" t="n">
-        <v>323136.66</v>
+        <v>18256651559.23</v>
       </c>
       <c r="G33" t="n">
-        <v>323136.66</v>
+        <v>18259071357.13</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>46065.66</v>
       </c>
       <c r="I33" t="n">
-        <v>2867068.53</v>
+        <v>2149146.04</v>
       </c>
       <c r="J33" t="n">
-        <v>2867068.53</v>
+        <v>2195211.7</v>
       </c>
     </row>
     <row r="34">
@@ -1614,34 +1614,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2061</v>
+        <v>2151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>70806633.62</v>
+        <v>81750398.86</v>
       </c>
       <c r="F34" t="n">
-        <v>68325905.25</v>
+        <v>76284993.93000001</v>
       </c>
       <c r="G34" t="n">
-        <v>67044604.87</v>
+        <v>75483300.69</v>
       </c>
       <c r="H34" t="n">
-        <v>11590.87</v>
+        <v>24887.1</v>
       </c>
       <c r="I34" t="n">
-        <v>1026935.64</v>
+        <v>1770214.54</v>
       </c>
       <c r="J34" t="n">
-        <v>1038526.51</v>
+        <v>1795101.64</v>
       </c>
     </row>
     <row r="35">
@@ -1650,34 +1650,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4141</v>
+        <v>2271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10407251.17</v>
+        <v>2478485587.5</v>
       </c>
       <c r="F35" t="n">
-        <v>6488589.5</v>
+        <v>2347428600.43</v>
       </c>
       <c r="G35" t="n">
-        <v>6364731.34</v>
+        <v>2300004443.95</v>
       </c>
       <c r="H35" t="n">
-        <v>747392.63</v>
+        <v>18122531.3</v>
       </c>
       <c r="I35" t="n">
-        <v>8034402.68</v>
+        <v>63228349.74</v>
       </c>
       <c r="J35" t="n">
-        <v>8781795.310000001</v>
+        <v>81350881.04000001</v>
       </c>
     </row>
     <row r="36">
@@ -1686,34 +1686,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4631</v>
+        <v>4341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>712687568.61</v>
+        <v>2288740.74</v>
       </c>
       <c r="F36" t="n">
-        <v>645428218.54</v>
+        <v>1318579.4</v>
       </c>
       <c r="G36" t="n">
-        <v>535779525.63</v>
+        <v>1060943.48</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>223487.09</v>
       </c>
       <c r="I36" t="n">
-        <v>35286533.51</v>
+        <v>548165.38</v>
       </c>
       <c r="J36" t="n">
-        <v>35286533.51</v>
+        <v>771652.47</v>
       </c>
     </row>
     <row r="37">
@@ -1722,34 +1722,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2161</v>
+        <v>4091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6356895.04</v>
+        <v>610536.65</v>
       </c>
       <c r="F37" t="n">
-        <v>5950697.58</v>
+        <v>323136.66</v>
       </c>
       <c r="G37" t="n">
-        <v>5865105.78</v>
+        <v>323136.66</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>416373.16</v>
+        <v>2867068.53</v>
       </c>
       <c r="J37" t="n">
-        <v>416373.16</v>
+        <v>2867068.53</v>
       </c>
     </row>
     <row r="38">
@@ -1758,34 +1758,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4551</v>
+        <v>2061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>148883049.2</v>
+        <v>70806633.62</v>
       </c>
       <c r="F38" t="n">
-        <v>148355490.34</v>
+        <v>68325905.25</v>
       </c>
       <c r="G38" t="n">
-        <v>148348943.52</v>
+        <v>67044604.87</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>11590.87</v>
       </c>
       <c r="I38" t="n">
-        <v>620005.26</v>
+        <v>1026935.64</v>
       </c>
       <c r="J38" t="n">
-        <v>620005.26</v>
+        <v>1038526.51</v>
       </c>
     </row>
     <row r="39">
@@ -1794,34 +1794,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FUNDIF</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4421</v>
+        <v>4141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3658.62</v>
+        <v>10407251.17</v>
       </c>
       <c r="F39" t="n">
-        <v>3658.62</v>
+        <v>6488589.5</v>
       </c>
       <c r="G39" t="n">
-        <v>3658.62</v>
+        <v>6364731.34</v>
       </c>
       <c r="H39" t="n">
-        <v>895.13</v>
+        <v>747392.63</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>8034402.68</v>
       </c>
       <c r="J39" t="n">
-        <v>895.13</v>
+        <v>8781795.310000001</v>
       </c>
     </row>
     <row r="40">
@@ -1830,34 +1830,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2261</v>
+        <v>4631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>553211607.35</v>
+        <v>712687568.61</v>
       </c>
       <c r="F40" t="n">
-        <v>369463545.18</v>
+        <v>645428218.54</v>
       </c>
       <c r="G40" t="n">
-        <v>355249323.08</v>
+        <v>535779525.63</v>
       </c>
       <c r="H40" t="n">
-        <v>38687418.56</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>130773841.95</v>
+        <v>35286533.51</v>
       </c>
       <c r="J40" t="n">
-        <v>169461260.51</v>
+        <v>35286533.51</v>
       </c>
     </row>
     <row r="41">
@@ -1866,34 +1866,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4381</v>
+        <v>2161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>127170575.95</v>
+        <v>6356895.04</v>
       </c>
       <c r="F41" t="n">
-        <v>102885370.45</v>
+        <v>5950697.58</v>
       </c>
       <c r="G41" t="n">
-        <v>98080707.2</v>
+        <v>5865105.78</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>21378670.3</v>
+        <v>416373.16</v>
       </c>
       <c r="J41" t="n">
-        <v>21378670.3</v>
+        <v>416373.16</v>
       </c>
     </row>
     <row r="42">
@@ -1902,34 +1902,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1071</v>
+        <v>4551</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>55898902.78</v>
+        <v>148883049.2</v>
       </c>
       <c r="F42" t="n">
-        <v>34921981.44</v>
+        <v>148355490.34</v>
       </c>
       <c r="G42" t="n">
-        <v>32307667.05</v>
+        <v>148348943.52</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>4293686.19</v>
+        <v>620005.26</v>
       </c>
       <c r="J42" t="n">
-        <v>4293686.19</v>
+        <v>620005.26</v>
       </c>
     </row>
     <row r="43">
@@ -1938,34 +1938,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNDALEMG</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1916</v>
+        <v>4121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO ESPECIAL DA ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6570721631.06</v>
+        <v>7461545.44</v>
       </c>
       <c r="F43" t="n">
-        <v>6570721631.06</v>
+        <v>5846301.44</v>
       </c>
       <c r="G43" t="n">
-        <v>6497797081.7</v>
+        <v>5378597.3</v>
       </c>
       <c r="H43" t="n">
-        <v>260833467.16</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>704278.4</v>
       </c>
       <c r="J43" t="n">
-        <v>260833467.16</v>
+        <v>704278.4</v>
       </c>
     </row>
     <row r="44">
@@ -1974,34 +1974,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>FUNDIF</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2321</v>
+        <v>4421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>394549598.81</v>
+        <v>3658.62</v>
       </c>
       <c r="F44" t="n">
-        <v>359596023.43</v>
+        <v>3658.62</v>
       </c>
       <c r="G44" t="n">
-        <v>346696259.17</v>
+        <v>3658.62</v>
       </c>
       <c r="H44" t="n">
-        <v>1425788.73</v>
+        <v>895.13</v>
       </c>
       <c r="I44" t="n">
-        <v>30573782.13</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>31999570.86</v>
+        <v>895.13</v>
       </c>
     </row>
     <row r="45">
@@ -2010,34 +2010,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2421</v>
+        <v>2261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>61510642.64</v>
+        <v>553211607.35</v>
       </c>
       <c r="F45" t="n">
-        <v>43124254.63</v>
+        <v>369463545.18</v>
       </c>
       <c r="G45" t="n">
-        <v>41282826.79</v>
+        <v>355249323.08</v>
       </c>
       <c r="H45" t="n">
-        <v>713315.27</v>
+        <v>38687418.56</v>
       </c>
       <c r="I45" t="n">
-        <v>7206237.15</v>
+        <v>130773841.95</v>
       </c>
       <c r="J45" t="n">
-        <v>7919552.42</v>
+        <v>169461260.51</v>
       </c>
     </row>
     <row r="46">
@@ -2046,34 +2046,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2101</v>
+        <v>4441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>217212201.82</v>
+        <v>39626206.59</v>
       </c>
       <c r="F46" t="n">
-        <v>204765475.8</v>
+        <v>16926860.87</v>
       </c>
       <c r="G46" t="n">
-        <v>196759897.63</v>
+        <v>14755140.25</v>
       </c>
       <c r="H46" t="n">
-        <v>1333045.2</v>
+        <v>45219.46</v>
       </c>
       <c r="I46" t="n">
-        <v>7655898.75</v>
+        <v>6004181.02</v>
       </c>
       <c r="J46" t="n">
-        <v>8988943.949999999</v>
+        <v>6049400.48</v>
       </c>
     </row>
     <row r="47">
@@ -2082,34 +2082,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2201</v>
+        <v>4381</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>28359171.85</v>
+        <v>127170575.95</v>
       </c>
       <c r="F47" t="n">
-        <v>27321777.4</v>
+        <v>102885370.45</v>
       </c>
       <c r="G47" t="n">
-        <v>25220175.31</v>
+        <v>98080707.2</v>
       </c>
       <c r="H47" t="n">
-        <v>6473.82</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1262449.13</v>
+        <v>21378670.3</v>
       </c>
       <c r="J47" t="n">
-        <v>1268922.95</v>
+        <v>21378670.3</v>
       </c>
     </row>
     <row r="48">
@@ -2118,34 +2118,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2241</v>
+        <v>1071</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>195257062.85</v>
+        <v>55898902.78</v>
       </c>
       <c r="F48" t="n">
-        <v>182522813.41</v>
+        <v>34921981.44</v>
       </c>
       <c r="G48" t="n">
-        <v>181974009.41</v>
+        <v>32307667.05</v>
       </c>
       <c r="H48" t="n">
-        <v>10483113.83</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1680822.65</v>
+        <v>4293686.19</v>
       </c>
       <c r="J48" t="n">
-        <v>12163936.48</v>
+        <v>4293686.19</v>
       </c>
     </row>
     <row r="49">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2371</v>
+        <v>1916</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>290312222.92</v>
+        <v>6570721631.06</v>
       </c>
       <c r="F49" t="n">
-        <v>283815022.34</v>
+        <v>6570721631.06</v>
       </c>
       <c r="G49" t="n">
-        <v>282551558.48</v>
+        <v>6497797081.7</v>
       </c>
       <c r="H49" t="n">
-        <v>654297.5699999999</v>
+        <v>260833467.16</v>
       </c>
       <c r="I49" t="n">
-        <v>7082912.77</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>7737210.34</v>
+        <v>260833467.16</v>
       </c>
     </row>
     <row r="50">
@@ -2190,34 +2190,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2331</v>
+        <v>2321</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>35739703.74</v>
+        <v>394549598.81</v>
       </c>
       <c r="F50" t="n">
-        <v>34318152.9</v>
+        <v>359596023.43</v>
       </c>
       <c r="G50" t="n">
-        <v>33074380.83</v>
+        <v>346696259.17</v>
       </c>
       <c r="H50" t="n">
-        <v>420781.11</v>
+        <v>1425788.73</v>
       </c>
       <c r="I50" t="n">
-        <v>436480.49</v>
+        <v>30573782.13</v>
       </c>
       <c r="J50" t="n">
-        <v>857261.6</v>
+        <v>31999570.86</v>
       </c>
     </row>
     <row r="51">
@@ -2226,34 +2226,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2011</v>
+        <v>2421</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2066687330.24</v>
+        <v>61510642.64</v>
       </c>
       <c r="F51" t="n">
-        <v>1811898139.4</v>
+        <v>43124254.63</v>
       </c>
       <c r="G51" t="n">
-        <v>1767628149.66</v>
+        <v>41282826.79</v>
       </c>
       <c r="H51" t="n">
-        <v>1062515.58</v>
+        <v>713315.27</v>
       </c>
       <c r="I51" t="n">
-        <v>92904525.54000001</v>
+        <v>7206237.15</v>
       </c>
       <c r="J51" t="n">
-        <v>93967041.12</v>
+        <v>7919552.42</v>
       </c>
     </row>
     <row r="52">
@@ -2262,34 +2262,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3302390465.79</v>
+        <v>217212201.82</v>
       </c>
       <c r="F52" t="n">
-        <v>3251209178.87</v>
+        <v>204765475.8</v>
       </c>
       <c r="G52" t="n">
-        <v>3202602086.92</v>
+        <v>196759897.63</v>
       </c>
       <c r="H52" t="n">
-        <v>294911.07</v>
+        <v>1333045.2</v>
       </c>
       <c r="I52" t="n">
-        <v>15606900.02</v>
+        <v>7655898.75</v>
       </c>
       <c r="J52" t="n">
-        <v>15901811.09</v>
+        <v>8988943.949999999</v>
       </c>
     </row>
     <row r="53">
@@ -2298,34 +2298,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2251</v>
+        <v>2201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>41105200.07</v>
+        <v>28359171.85</v>
       </c>
       <c r="F53" t="n">
-        <v>38759738.47</v>
+        <v>27321777.4</v>
       </c>
       <c r="G53" t="n">
-        <v>36259002.32</v>
+        <v>25220175.31</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>6473.82</v>
       </c>
       <c r="I53" t="n">
-        <v>1415037.52</v>
+        <v>1262449.13</v>
       </c>
       <c r="J53" t="n">
-        <v>1415037.52</v>
+        <v>1268922.95</v>
       </c>
     </row>
     <row r="54">
@@ -2334,34 +2334,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2041</v>
+        <v>2241</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2901561.62</v>
+        <v>195257062.85</v>
       </c>
       <c r="F54" t="n">
-        <v>2865088.76</v>
+        <v>182522813.41</v>
       </c>
       <c r="G54" t="n">
-        <v>2860275.95</v>
+        <v>181974009.41</v>
       </c>
       <c r="H54" t="n">
-        <v>3394.97</v>
+        <v>10483113.83</v>
       </c>
       <c r="I54" t="n">
-        <v>24471.67</v>
+        <v>1680822.65</v>
       </c>
       <c r="J54" t="n">
-        <v>27866.64</v>
+        <v>12163936.48</v>
       </c>
     </row>
     <row r="55">
@@ -2370,34 +2370,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1101</v>
+        <v>2371</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>18048368.2</v>
+        <v>290312222.92</v>
       </c>
       <c r="F55" t="n">
-        <v>17928588.51</v>
+        <v>283815022.34</v>
       </c>
       <c r="G55" t="n">
-        <v>17774694.27</v>
+        <v>282551558.48</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>654297.5699999999</v>
       </c>
       <c r="I55" t="n">
-        <v>57114.59</v>
+        <v>7082912.77</v>
       </c>
       <c r="J55" t="n">
-        <v>57114.59</v>
+        <v>7737210.34</v>
       </c>
     </row>
     <row r="56">
@@ -2406,34 +2406,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1915</v>
+        <v>2331</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20043002.56</v>
+        <v>35739703.74</v>
       </c>
       <c r="F56" t="n">
-        <v>20043002.56</v>
+        <v>34318152.9</v>
       </c>
       <c r="G56" t="n">
-        <v>20043002.56</v>
+        <v>33074380.83</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>420781.11</v>
       </c>
       <c r="I56" t="n">
-        <v>46.77</v>
+        <v>436480.49</v>
       </c>
       <c r="J56" t="n">
-        <v>46.77</v>
+        <v>857261.6</v>
       </c>
     </row>
     <row r="57">
@@ -2442,35 +2442,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1511</v>
+        <v>2361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3138279917.06</v>
+        <v>68465842.09</v>
       </c>
       <c r="F57" t="n">
-        <v>3076106533.57</v>
+        <v>68465842.09</v>
       </c>
       <c r="G57" t="n">
-        <v>3055981056.68</v>
-      </c>
-      <c r="H57" t="n">
-        <v>18355346.55</v>
-      </c>
-      <c r="I57" t="n">
-        <v>41103215.43</v>
-      </c>
-      <c r="J57" t="n">
-        <v>59458561.98</v>
-      </c>
+        <v>68465842.09</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2478,34 +2472,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1251</v>
+        <v>2011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>17184629357.54</v>
+        <v>2066687330.24</v>
       </c>
       <c r="F58" t="n">
-        <v>16913388822.07</v>
+        <v>1811898139.4</v>
       </c>
       <c r="G58" t="n">
-        <v>16881355805.92</v>
+        <v>1767628149.66</v>
       </c>
       <c r="H58" t="n">
-        <v>22568008.23</v>
+        <v>1062515.58</v>
       </c>
       <c r="I58" t="n">
-        <v>179457677.69</v>
+        <v>92904525.54000001</v>
       </c>
       <c r="J58" t="n">
-        <v>202025685.92</v>
+        <v>93967041.12</v>
       </c>
     </row>
     <row r="59">
@@ -2514,34 +2508,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1721</v>
+        <v>2121</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>10652572.94</v>
+        <v>3302390465.79</v>
       </c>
       <c r="F59" t="n">
-        <v>10295525.12</v>
+        <v>3251209178.87</v>
       </c>
       <c r="G59" t="n">
-        <v>9939287.65</v>
+        <v>3202602086.92</v>
       </c>
       <c r="H59" t="n">
-        <v>10152.64</v>
+        <v>294911.07</v>
       </c>
       <c r="I59" t="n">
-        <v>276281.69</v>
+        <v>15606900.02</v>
       </c>
       <c r="J59" t="n">
-        <v>286434.33</v>
+        <v>15901811.09</v>
       </c>
     </row>
     <row r="60">
@@ -2550,34 +2544,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1231</v>
+        <v>2251</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>319941879.07</v>
+        <v>41105200.07</v>
       </c>
       <c r="F60" t="n">
-        <v>286029024.67</v>
+        <v>38759738.47</v>
       </c>
       <c r="G60" t="n">
-        <v>275453889.56</v>
+        <v>36259002.32</v>
       </c>
       <c r="H60" t="n">
-        <v>4468309.21</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>18499399.92</v>
+        <v>1415037.52</v>
       </c>
       <c r="J60" t="n">
-        <v>22967709.13</v>
+        <v>1415037.52</v>
       </c>
     </row>
     <row r="61">
@@ -2586,34 +2580,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1631</v>
+        <v>2041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>12493555.88</v>
+        <v>2901561.62</v>
       </c>
       <c r="F61" t="n">
-        <v>12400512.79</v>
+        <v>2865088.76</v>
       </c>
       <c r="G61" t="n">
-        <v>12257285.88</v>
+        <v>2860275.95</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3394.97</v>
       </c>
       <c r="I61" t="n">
-        <v>138983.68</v>
+        <v>24471.67</v>
       </c>
       <c r="J61" t="n">
-        <v>138983.68</v>
+        <v>27866.64</v>
       </c>
     </row>
     <row r="62">
@@ -2622,34 +2616,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1711</v>
+        <v>1101</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>181181663.88</v>
+        <v>18048368.2</v>
       </c>
       <c r="F62" t="n">
-        <v>101620737.74</v>
+        <v>17928588.51</v>
       </c>
       <c r="G62" t="n">
-        <v>97019401.54000001</v>
+        <v>17774694.27</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>76618911.3</v>
+        <v>57114.59</v>
       </c>
       <c r="J62" t="n">
-        <v>76618911.3</v>
+        <v>57114.59</v>
       </c>
     </row>
     <row r="63">
@@ -2658,34 +2652,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1271</v>
+        <v>1915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>261449910.33</v>
+        <v>20043002.56</v>
       </c>
       <c r="F63" t="n">
-        <v>260070135.18</v>
+        <v>20043002.56</v>
       </c>
       <c r="G63" t="n">
-        <v>257629551.13</v>
+        <v>20043002.56</v>
       </c>
       <c r="H63" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2485549.72</v>
+        <v>46.77</v>
       </c>
       <c r="J63" t="n">
-        <v>2488069.72</v>
+        <v>46.77</v>
       </c>
     </row>
     <row r="64">
@@ -2694,34 +2688,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1221</v>
+        <v>1511</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>425928118.33</v>
+        <v>3138279917.06</v>
       </c>
       <c r="F64" t="n">
-        <v>106813200.9</v>
+        <v>3076106533.57</v>
       </c>
       <c r="G64" t="n">
-        <v>104972627.41</v>
+        <v>3055981056.68</v>
       </c>
       <c r="H64" t="n">
-        <v>3819.55</v>
+        <v>18355346.55</v>
       </c>
       <c r="I64" t="n">
-        <v>10240167.34</v>
+        <v>41103215.43</v>
       </c>
       <c r="J64" t="n">
-        <v>10243986.89</v>
+        <v>59458561.98</v>
       </c>
     </row>
     <row r="65">
@@ -2730,34 +2724,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1481</v>
+        <v>1091</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>338412512.01</v>
+        <v>4236732028.37</v>
       </c>
       <c r="F65" t="n">
-        <v>284330922.14</v>
+        <v>4141114287.8</v>
       </c>
       <c r="G65" t="n">
-        <v>273376533.99</v>
+        <v>4100009275.29</v>
       </c>
       <c r="H65" t="n">
-        <v>6492833.43</v>
+        <v>5441376.69</v>
       </c>
       <c r="I65" t="n">
-        <v>13954481.02</v>
+        <v>90708170.09999999</v>
       </c>
       <c r="J65" t="n">
-        <v>20447314.45</v>
+        <v>96149546.79000001</v>
       </c>
     </row>
     <row r="66">
@@ -2766,34 +2760,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>20024070516.28</v>
+        <v>17184629357.54</v>
       </c>
       <c r="F66" t="n">
-        <v>19817333122</v>
+        <v>16913388822.07</v>
       </c>
       <c r="G66" t="n">
-        <v>19583419698.99</v>
+        <v>16881355805.92</v>
       </c>
       <c r="H66" t="n">
-        <v>102690852.14</v>
+        <v>22568008.23</v>
       </c>
       <c r="I66" t="n">
-        <v>437921985.25</v>
+        <v>179457677.69</v>
       </c>
       <c r="J66" t="n">
-        <v>540612837.39</v>
+        <v>202025685.92</v>
       </c>
     </row>
     <row r="67">
@@ -2802,34 +2796,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1191</v>
+        <v>1721</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1886784188.81</v>
+        <v>10652572.94</v>
       </c>
       <c r="F67" t="n">
-        <v>1792612515.59</v>
+        <v>10295525.12</v>
       </c>
       <c r="G67" t="n">
-        <v>1767643635.43</v>
+        <v>9939287.65</v>
       </c>
       <c r="H67" t="n">
-        <v>5956448.89</v>
+        <v>10152.64</v>
       </c>
       <c r="I67" t="n">
-        <v>38130787.08</v>
+        <v>276281.69</v>
       </c>
       <c r="J67" t="n">
-        <v>44087235.97</v>
+        <v>286434.33</v>
       </c>
     </row>
     <row r="68">
@@ -2838,34 +2832,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1491</v>
+        <v>1231</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>971196665.48</v>
+        <v>319941879.07</v>
       </c>
       <c r="F68" t="n">
-        <v>965761230.4299999</v>
+        <v>286029024.67</v>
       </c>
       <c r="G68" t="n">
-        <v>950181400.99</v>
+        <v>275453889.56</v>
       </c>
       <c r="H68" t="n">
-        <v>1028658.15</v>
+        <v>4468309.21</v>
       </c>
       <c r="I68" t="n">
-        <v>17535020.6</v>
+        <v>18499399.92</v>
       </c>
       <c r="J68" t="n">
-        <v>18563678.75</v>
+        <v>22967709.13</v>
       </c>
     </row>
     <row r="69">
@@ -2874,34 +2868,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1301</v>
+        <v>1631</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>480636059.58</v>
+        <v>12493555.88</v>
       </c>
       <c r="F69" t="n">
-        <v>393222333.81</v>
+        <v>12400512.79</v>
       </c>
       <c r="G69" t="n">
-        <v>363896390.26</v>
+        <v>12257285.88</v>
       </c>
       <c r="H69" t="n">
-        <v>11727528.06</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>201174882.85</v>
+        <v>138983.68</v>
       </c>
       <c r="J69" t="n">
-        <v>212902410.91</v>
+        <v>138983.68</v>
       </c>
     </row>
     <row r="70">
@@ -2910,34 +2904,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1451</v>
+        <v>1711</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4556477829.69</v>
+        <v>181181663.88</v>
       </c>
       <c r="F70" t="n">
-        <v>4357599952.24</v>
+        <v>101620737.74</v>
       </c>
       <c r="G70" t="n">
-        <v>4322020545.17</v>
+        <v>97019401.54000001</v>
       </c>
       <c r="H70" t="n">
-        <v>4833097.2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>108147895.72</v>
+        <v>76618911.3</v>
       </c>
       <c r="J70" t="n">
-        <v>112980992.92</v>
+        <v>76618911.3</v>
       </c>
     </row>
     <row r="71">
@@ -2946,34 +2940,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1371</v>
+        <v>1271</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185286819.99</v>
+        <v>261449910.33</v>
       </c>
       <c r="F71" t="n">
-        <v>178437283.68</v>
+        <v>260070135.18</v>
       </c>
       <c r="G71" t="n">
-        <v>172648640.16</v>
+        <v>257629551.13</v>
       </c>
       <c r="H71" t="n">
-        <v>271467.65</v>
+        <v>2520</v>
       </c>
       <c r="I71" t="n">
-        <v>5465504.58</v>
+        <v>2485549.72</v>
       </c>
       <c r="J71" t="n">
-        <v>5736972.23</v>
+        <v>2488069.72</v>
       </c>
     </row>
     <row r="72">
@@ -2982,34 +2976,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1501</v>
+        <v>1221</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>940771355.51</v>
+        <v>425928118.33</v>
       </c>
       <c r="F72" t="n">
-        <v>840171011.05</v>
+        <v>106813200.9</v>
       </c>
       <c r="G72" t="n">
-        <v>779489331.71</v>
+        <v>104972627.41</v>
       </c>
       <c r="H72" t="n">
-        <v>9145522.6</v>
+        <v>3819.55</v>
       </c>
       <c r="I72" t="n">
-        <v>62616118.7</v>
+        <v>10240167.34</v>
       </c>
       <c r="J72" t="n">
-        <v>71761641.3</v>
+        <v>10243986.89</v>
       </c>
     </row>
     <row r="73">
@@ -3018,34 +3012,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2211</v>
+        <v>1481</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>16376327.77</v>
+        <v>338412512.01</v>
       </c>
       <c r="F73" t="n">
-        <v>15665660.91</v>
+        <v>284330922.14</v>
       </c>
       <c r="G73" t="n">
-        <v>14963532.88</v>
+        <v>273376533.99</v>
       </c>
       <c r="H73" t="n">
-        <v>84375.35000000001</v>
+        <v>6492833.43</v>
       </c>
       <c r="I73" t="n">
-        <v>903154.46</v>
+        <v>13954481.02</v>
       </c>
       <c r="J73" t="n">
-        <v>987529.8100000001</v>
+        <v>20447314.45</v>
       </c>
     </row>
     <row r="74">
@@ -3054,34 +3048,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2351</v>
+        <v>1261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>431560939.48</v>
+        <v>20024070516.28</v>
       </c>
       <c r="F74" t="n">
-        <v>399364373.03</v>
+        <v>19817333122</v>
       </c>
       <c r="G74" t="n">
-        <v>391027226.76</v>
+        <v>19583419698.99</v>
       </c>
       <c r="H74" t="n">
-        <v>1690845.8</v>
+        <v>102690852.14</v>
       </c>
       <c r="I74" t="n">
-        <v>7591910.97</v>
+        <v>437921985.25</v>
       </c>
       <c r="J74" t="n">
-        <v>9282756.77</v>
+        <v>540612837.39</v>
       </c>
     </row>
     <row r="75">
@@ -3090,34 +3084,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2311</v>
+        <v>1191</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>533150763.61</v>
+        <v>1886784188.81</v>
       </c>
       <c r="F75" t="n">
-        <v>503448723.24</v>
+        <v>1792612515.59</v>
       </c>
       <c r="G75" t="n">
-        <v>492058770.59</v>
+        <v>1767643635.43</v>
       </c>
       <c r="H75" t="n">
-        <v>274974.01</v>
+        <v>5956448.89</v>
       </c>
       <c r="I75" t="n">
-        <v>39010212.22</v>
+        <v>38130787.08</v>
       </c>
       <c r="J75" t="n">
-        <v>39285186.23</v>
+        <v>44087235.97</v>
       </c>
     </row>
     <row r="76">
@@ -3126,33 +3120,423 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>SEGOV</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>971196665.48</v>
+      </c>
+      <c r="F76" t="n">
+        <v>965761230.4299999</v>
+      </c>
+      <c r="G76" t="n">
+        <v>950181400.99</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1028658.15</v>
+      </c>
+      <c r="I76" t="n">
+        <v>17535020.6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>18563678.75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SEINFRA</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>480636059.58</v>
+      </c>
+      <c r="F77" t="n">
+        <v>393222333.81</v>
+      </c>
+      <c r="G77" t="n">
+        <v>363896390.26</v>
+      </c>
+      <c r="H77" t="n">
+        <v>11727528.06</v>
+      </c>
+      <c r="I77" t="n">
+        <v>201174882.85</v>
+      </c>
+      <c r="J77" t="n">
+        <v>212902410.91</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SEJUSP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1451</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4556477829.69</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4357599952.24</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4322020545.17</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4833097.2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>108147895.72</v>
+      </c>
+      <c r="J78" t="n">
+        <v>112980992.92</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SEMAD</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>185286819.99</v>
+      </c>
+      <c r="F79" t="n">
+        <v>178437283.68</v>
+      </c>
+      <c r="G79" t="n">
+        <v>172648640.16</v>
+      </c>
+      <c r="H79" t="n">
+        <v>271467.65</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5465504.58</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5736972.23</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SEPLAG</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>940771355.51</v>
+      </c>
+      <c r="F80" t="n">
+        <v>840171011.05</v>
+      </c>
+      <c r="G80" t="n">
+        <v>779489331.71</v>
+      </c>
+      <c r="H80" t="n">
+        <v>9145522.6</v>
+      </c>
+      <c r="I80" t="n">
+        <v>62616118.7</v>
+      </c>
+      <c r="J80" t="n">
+        <v>71761641.3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TCEMG</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1497702565.35</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1459808527.61</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1447340682.34</v>
+      </c>
+      <c r="H81" t="n">
+        <v>33256.58</v>
+      </c>
+      <c r="I81" t="n">
+        <v>28511863.55</v>
+      </c>
+      <c r="J81" t="n">
+        <v>28545120.13</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TJMG</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>10945290220.95</v>
+      </c>
+      <c r="F82" t="n">
+        <v>10945290220.95</v>
+      </c>
+      <c r="G82" t="n">
+        <v>10946228265.22</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TJMMG</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>164960722.27</v>
+      </c>
+      <c r="F83" t="n">
+        <v>159274638.21</v>
+      </c>
+      <c r="G83" t="n">
+        <v>157731413.39</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>6499456.92</v>
+      </c>
+      <c r="J83" t="n">
+        <v>6499456.92</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TV MINAS</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2211</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>16376327.77</v>
+      </c>
+      <c r="F84" t="n">
+        <v>15665660.91</v>
+      </c>
+      <c r="G84" t="n">
+        <v>14963532.88</v>
+      </c>
+      <c r="H84" t="n">
+        <v>84375.35000000001</v>
+      </c>
+      <c r="I84" t="n">
+        <v>903154.46</v>
+      </c>
+      <c r="J84" t="n">
+        <v>987529.8100000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>431560939.48</v>
+      </c>
+      <c r="F85" t="n">
+        <v>399364373.03</v>
+      </c>
+      <c r="G85" t="n">
+        <v>391027226.76</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1690845.8</v>
+      </c>
+      <c r="I85" t="n">
+        <v>7591910.97</v>
+      </c>
+      <c r="J85" t="n">
+        <v>9282756.77</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>533150763.61</v>
+      </c>
+      <c r="F86" t="n">
+        <v>503448723.24</v>
+      </c>
+      <c r="G86" t="n">
+        <v>492058770.59</v>
+      </c>
+      <c r="H86" t="n">
+        <v>274974.01</v>
+      </c>
+      <c r="I86" t="n">
+        <v>39010212.22</v>
+      </c>
+      <c r="J86" t="n">
+        <v>39285186.23</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C87" t="n">
         <v>2281</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E87" t="n">
         <v>7417117.22</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F87" t="n">
         <v>6859782.46</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G87" t="n">
         <v>6435691.91</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H87" t="n">
         <v>0</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I87" t="n">
         <v>231057.02</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J87" t="n">
         <v>231057.02</v>
       </c>
     </row>

--- a/upload/orgao2025.xlsx
+++ b/upload/orgao2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,10 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Valor Pago Processado</t>
+          <t>Valor Liquidado RP</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Pago Não Processado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Valor Pago RP</t>
         </is>
@@ -498,21 +493,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1023743951.58</v>
+        <v>35640126.45</v>
       </c>
       <c r="F2" t="n">
-        <v>1014541849.87</v>
+        <v>27348088.54</v>
       </c>
       <c r="G2" t="n">
-        <v>759567117.27</v>
+        <v>20438708.9</v>
       </c>
       <c r="H2" t="n">
-        <v>11357399.47</v>
+        <v>2761361.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2680004.75</v>
-      </c>
-      <c r="J2" t="n">
         <v>14037404.22</v>
       </c>
     </row>
@@ -534,21 +526,18 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7932027.77</v>
+        <v>3225983.07</v>
       </c>
       <c r="F3" t="n">
-        <v>7756446.63</v>
+        <v>3093158.3</v>
       </c>
       <c r="G3" t="n">
-        <v>7297654.88</v>
+        <v>2631436.82</v>
       </c>
       <c r="H3" t="n">
-        <v>45611.95</v>
+        <v>40931.07</v>
       </c>
       <c r="I3" t="n">
-        <v>40582.82</v>
-      </c>
-      <c r="J3" t="n">
         <v>86194.77</v>
       </c>
     </row>
@@ -570,21 +559,18 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2149209573.3</v>
+        <v>180752861.99</v>
       </c>
       <c r="F4" t="n">
-        <v>2108068512.69</v>
+        <v>146764885.94</v>
       </c>
       <c r="G4" t="n">
-        <v>2091020383.51</v>
+        <v>133127529.7</v>
       </c>
       <c r="H4" t="n">
-        <v>762.97</v>
+        <v>42443642.8</v>
       </c>
       <c r="I4" t="n">
-        <v>40404763.93</v>
-      </c>
-      <c r="J4" t="n">
         <v>40405526.9</v>
       </c>
     </row>
@@ -606,21 +592,18 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4789292.11</v>
+        <v>2521986.68</v>
       </c>
       <c r="F5" t="n">
-        <v>3903632.02</v>
+        <v>1647855.54</v>
       </c>
       <c r="G5" t="n">
-        <v>3547153</v>
+        <v>1285030.9</v>
       </c>
       <c r="H5" t="n">
-        <v>13266.26</v>
+        <v>179384.15</v>
       </c>
       <c r="I5" t="n">
-        <v>175463.15</v>
-      </c>
-      <c r="J5" t="n">
         <v>188729.41</v>
       </c>
     </row>
@@ -642,21 +625,18 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19031476.38</v>
+        <v>2325270.98</v>
       </c>
       <c r="F6" t="n">
-        <v>18693505.57</v>
+        <v>2026027.35</v>
       </c>
       <c r="G6" t="n">
-        <v>18533956.49</v>
+        <v>1865779.96</v>
       </c>
       <c r="H6" t="n">
-        <v>87975.14999999999</v>
+        <v>239308.51</v>
       </c>
       <c r="I6" t="n">
-        <v>226885.18</v>
-      </c>
-      <c r="J6" t="n">
         <v>314860.33</v>
       </c>
     </row>
@@ -678,17 +658,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12995181.74</v>
+        <v>8531156.08</v>
       </c>
       <c r="F7" t="n">
-        <v>9545227.800000001</v>
+        <v>5315265.48</v>
       </c>
       <c r="G7" t="n">
-        <v>9172117.300000001</v>
+        <v>4942154.98</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -708,21 +687,18 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2074027252.07</v>
+        <v>126194932.14</v>
       </c>
       <c r="F8" t="n">
-        <v>1999073232.13</v>
+        <v>52021493.06</v>
       </c>
       <c r="G8" t="n">
-        <v>1988491760.28</v>
+        <v>46111572.42</v>
       </c>
       <c r="H8" t="n">
-        <v>4678551.78</v>
+        <v>75929172.04000001</v>
       </c>
       <c r="I8" t="n">
-        <v>71714800.70999999</v>
-      </c>
-      <c r="J8" t="n">
         <v>76393352.48999999</v>
       </c>
     </row>
@@ -744,21 +720,18 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70667226.11</v>
+        <v>5232552.78</v>
       </c>
       <c r="F9" t="n">
-        <v>69307261.73999999</v>
+        <v>3872588.41</v>
       </c>
       <c r="G9" t="n">
-        <v>69083242.06</v>
+        <v>3646547.81</v>
       </c>
       <c r="H9" t="n">
-        <v>39281.15</v>
+        <v>915269.58</v>
       </c>
       <c r="I9" t="n">
-        <v>907780.5</v>
-      </c>
-      <c r="J9" t="n">
         <v>947061.65</v>
       </c>
     </row>
@@ -780,21 +753,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1096185910.71</v>
+        <v>130365415.96</v>
       </c>
       <c r="F10" t="n">
-        <v>1073000349.22</v>
+        <v>111505603.48</v>
       </c>
       <c r="G10" t="n">
-        <v>1062452304.51</v>
+        <v>100336825.21</v>
       </c>
       <c r="H10" t="n">
-        <v>245007.27</v>
+        <v>20653850.41</v>
       </c>
       <c r="I10" t="n">
-        <v>19268306.91</v>
-      </c>
-      <c r="J10" t="n">
         <v>19513314.18</v>
       </c>
     </row>
@@ -816,21 +786,18 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2143327357.7</v>
+        <v>1815023530.84</v>
       </c>
       <c r="F11" t="n">
-        <v>1655881609.23</v>
+        <v>1332106225.01</v>
       </c>
       <c r="G11" t="n">
-        <v>1611441301.37</v>
+        <v>1297735416.5</v>
       </c>
       <c r="H11" t="n">
-        <v>14178677.35</v>
+        <v>420007538.96</v>
       </c>
       <c r="I11" t="n">
-        <v>411934193.73</v>
-      </c>
-      <c r="J11" t="n">
         <v>426112871.08</v>
       </c>
     </row>
@@ -851,24 +818,15 @@
           <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>1211264345.43</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1127569424.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1127569424.8</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>70456474.19</v>
       </c>
       <c r="I12" t="n">
         <v>70456474.19</v>
       </c>
-      <c r="J12" t="n">
-        <v>70456474.19</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -888,21 +846,18 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>194535650.21</v>
+        <v>2536179.04</v>
       </c>
       <c r="F13" t="n">
-        <v>193268761.55</v>
+        <v>1269290.38</v>
       </c>
       <c r="G13" t="n">
-        <v>193178812.25</v>
+        <v>1179341.08</v>
       </c>
       <c r="H13" t="n">
-        <v>27888.27</v>
+        <v>1701683.69</v>
       </c>
       <c r="I13" t="n">
-        <v>1669467.18</v>
-      </c>
-      <c r="J13" t="n">
         <v>1697355.45</v>
       </c>
     </row>
@@ -934,7 +889,6 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -964,7 +918,6 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -972,29 +925,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMG - ADM. DIRETA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3051</v>
+        <v>9999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>150702794.76</v>
-      </c>
-      <c r="F16" t="n">
-        <v>150702794.76</v>
-      </c>
-      <c r="G16" t="n">
-        <v>150702794.76</v>
-      </c>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1002,35 +948,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>25352006.23</v>
+        <v>150702794.76</v>
       </c>
       <c r="F17" t="n">
-        <v>23581392.72</v>
+        <v>150702794.76</v>
       </c>
       <c r="G17" t="n">
-        <v>22865578.49</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>351886.66</v>
-      </c>
-      <c r="J17" t="n">
-        <v>351886.66</v>
-      </c>
+        <v>150702794.76</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1038,34 +977,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>350405</v>
+        <v>7783341.19</v>
       </c>
       <c r="F18" t="n">
-        <v>318593.91</v>
+        <v>6018691.52</v>
       </c>
       <c r="G18" t="n">
-        <v>300914.63</v>
+        <v>5313682.37</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>392566.27</v>
       </c>
       <c r="I18" t="n">
-        <v>26392.47</v>
-      </c>
-      <c r="J18" t="n">
-        <v>26392.47</v>
+        <v>351886.66</v>
       </c>
     </row>
     <row r="19">
@@ -1074,34 +1010,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9439748.619999999</v>
+        <v>350405</v>
       </c>
       <c r="F19" t="n">
-        <v>9225890.4</v>
+        <v>318593.91</v>
       </c>
       <c r="G19" t="n">
-        <v>8465439.720000001</v>
+        <v>300914.63</v>
       </c>
       <c r="H19" t="n">
-        <v>480546.01</v>
+        <v>27969.18</v>
       </c>
       <c r="I19" t="n">
-        <v>177676.07</v>
-      </c>
-      <c r="J19" t="n">
-        <v>658222.08</v>
+        <v>26392.47</v>
       </c>
     </row>
     <row r="20">
@@ -1110,34 +1043,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>585603048.33</v>
+        <v>1235187.01</v>
       </c>
       <c r="F20" t="n">
-        <v>580710591.1900001</v>
+        <v>1064156.13</v>
       </c>
       <c r="G20" t="n">
-        <v>574854711.54</v>
+        <v>896988.4300000001</v>
       </c>
       <c r="H20" t="n">
-        <v>1239266.23</v>
+        <v>190937.95</v>
       </c>
       <c r="I20" t="n">
-        <v>8506819.619999999</v>
-      </c>
-      <c r="J20" t="n">
-        <v>9746085.85</v>
+        <v>658222.08</v>
       </c>
     </row>
     <row r="21">
@@ -1146,34 +1076,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>63217552.93</v>
+        <v>27869971.53</v>
       </c>
       <c r="F21" t="n">
-        <v>60940567.95</v>
+        <v>25264175.03</v>
       </c>
       <c r="G21" t="n">
-        <v>56959723.43</v>
+        <v>22782142.66</v>
       </c>
       <c r="H21" t="n">
-        <v>119258.05</v>
+        <v>8558052.460000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2222004.25</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2341262.3</v>
+        <v>9746085.85</v>
       </c>
     </row>
     <row r="22">
@@ -1182,34 +1109,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3035441.45</v>
+        <v>13581081.19</v>
       </c>
       <c r="F22" t="n">
-        <v>97428.45</v>
+        <v>11714881.88</v>
       </c>
       <c r="G22" t="n">
-        <v>93102.96000000001</v>
+        <v>9835446.02</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2383236.78</v>
       </c>
       <c r="I22" t="n">
-        <v>206186.42</v>
-      </c>
-      <c r="J22" t="n">
-        <v>206186.42</v>
+        <v>2341262.3</v>
       </c>
     </row>
     <row r="23">
@@ -1218,34 +1142,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>75621728.88</v>
+        <v>3035441.45</v>
       </c>
       <c r="F23" t="n">
-        <v>74134505.91</v>
+        <v>97428.45</v>
       </c>
       <c r="G23" t="n">
-        <v>72540998.40000001</v>
+        <v>93102.96000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>24329.43</v>
+        <v>207143.08</v>
       </c>
       <c r="I23" t="n">
-        <v>2347292.71</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2371622.14</v>
+        <v>206186.42</v>
       </c>
     </row>
     <row r="24">
@@ -1254,34 +1175,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>172407716.3</v>
+        <v>14859750.61</v>
       </c>
       <c r="F24" t="n">
-        <v>169951293.67</v>
+        <v>13424327.01</v>
       </c>
       <c r="G24" t="n">
-        <v>168474678.26</v>
+        <v>12076459.73</v>
       </c>
       <c r="H24" t="n">
-        <v>1112168.89</v>
+        <v>2410023.68</v>
       </c>
       <c r="I24" t="n">
-        <v>5271380.07</v>
-      </c>
-      <c r="J24" t="n">
-        <v>6383548.96</v>
+        <v>2371622.14</v>
       </c>
     </row>
     <row r="25">
@@ -1290,34 +1208,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2634653.32</v>
+        <v>13274750.2</v>
       </c>
       <c r="F25" t="n">
-        <v>2500037.94</v>
+        <v>11938543.5</v>
       </c>
       <c r="G25" t="n">
-        <v>1882700.63</v>
+        <v>10570226.5</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>5368668.26</v>
       </c>
       <c r="I25" t="n">
-        <v>15394</v>
-      </c>
-      <c r="J25" t="n">
-        <v>15394</v>
+        <v>6383548.96</v>
       </c>
     </row>
     <row r="26">
@@ -1326,34 +1241,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4101</v>
+        <v>4491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>16870000</v>
-      </c>
-      <c r="F26" t="n">
-        <v>16870000</v>
-      </c>
-      <c r="G26" t="n">
-        <v>15570000</v>
-      </c>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
+        <v>15394</v>
       </c>
     </row>
     <row r="27">
@@ -1362,34 +1268,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4601</v>
+        <v>4101</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1473191.28</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1033455.88</v>
-      </c>
-      <c r="G27" t="n">
-        <v>987548.8100000001</v>
-      </c>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>2887433.54</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3042047.61</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5929481.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1398,34 +1295,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4451</v>
+        <v>4601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>48631312.58</v>
+        <v>1471355</v>
       </c>
       <c r="F28" t="n">
-        <v>11932319.97</v>
+        <v>1031619.6</v>
       </c>
       <c r="G28" t="n">
-        <v>11013107.33</v>
+        <v>985712.53</v>
       </c>
       <c r="H28" t="n">
-        <v>679.54</v>
+        <v>3181616.43</v>
       </c>
       <c r="I28" t="n">
-        <v>8080205.78</v>
-      </c>
-      <c r="J28" t="n">
-        <v>8080885.32</v>
+        <v>5929481.15</v>
       </c>
     </row>
     <row r="29">
@@ -1434,34 +1328,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FEPJ</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4031</v>
+        <v>4451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2589774328.16</v>
+        <v>40501588.84</v>
       </c>
       <c r="F29" t="n">
-        <v>2175663822.83</v>
+        <v>6180545.94</v>
       </c>
       <c r="G29" t="n">
-        <v>1951730257.86</v>
+        <v>5253987.28</v>
       </c>
       <c r="H29" t="n">
-        <v>4528727.26</v>
+        <v>8721781.609999999</v>
       </c>
       <c r="I29" t="n">
-        <v>173911941.97</v>
-      </c>
-      <c r="J29" t="n">
-        <v>178440669.23</v>
+        <v>8080885.32</v>
       </c>
     </row>
     <row r="30">
@@ -1470,34 +1361,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4291</v>
+        <v>4031</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>12684000278.8</v>
+        <v>1966774928.17</v>
       </c>
       <c r="F30" t="n">
-        <v>12066473764.49</v>
+        <v>1592888479.61</v>
       </c>
       <c r="G30" t="n">
-        <v>11940374576.38</v>
+        <v>1375394217.6</v>
       </c>
       <c r="H30" t="n">
-        <v>622978466.21</v>
+        <v>192997790.17</v>
       </c>
       <c r="I30" t="n">
-        <v>547393802.42</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1170372268.63</v>
+        <v>178440669.23</v>
       </c>
     </row>
     <row r="31">
@@ -1506,34 +1394,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4691</v>
+        <v>4291</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>64705464.4</v>
+        <v>1362287082.92</v>
       </c>
       <c r="F31" t="n">
-        <v>14436749.82</v>
+        <v>1006982665.41</v>
       </c>
       <c r="G31" t="n">
-        <v>9663966.02</v>
+        <v>930049430.41</v>
       </c>
       <c r="H31" t="n">
-        <v>2093885.86</v>
+        <v>554412568.12</v>
       </c>
       <c r="I31" t="n">
-        <v>31330993.84</v>
-      </c>
-      <c r="J31" t="n">
-        <v>33424879.7</v>
+        <v>1170372268.63</v>
       </c>
     </row>
     <row r="32">
@@ -1542,34 +1427,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4701</v>
+        <v>4691</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2107186.39</v>
+        <v>64693569.4</v>
       </c>
       <c r="F32" t="n">
-        <v>781389.39</v>
+        <v>14424854.82</v>
       </c>
       <c r="G32" t="n">
-        <v>754127.26</v>
+        <v>9652071.02</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>31972987.06</v>
       </c>
       <c r="I32" t="n">
-        <v>86523.72</v>
-      </c>
-      <c r="J32" t="n">
-        <v>86523.72</v>
+        <v>33424879.7</v>
       </c>
     </row>
     <row r="33">
@@ -1578,34 +1460,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4711</v>
+        <v>4701</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>18258352481.54</v>
+        <v>2061486.56</v>
       </c>
       <c r="F33" t="n">
-        <v>18256651559.23</v>
+        <v>735736.86</v>
       </c>
       <c r="G33" t="n">
-        <v>18259071357.13</v>
+        <v>707772.7</v>
       </c>
       <c r="H33" t="n">
-        <v>46065.66</v>
+        <v>86697.3</v>
       </c>
       <c r="I33" t="n">
-        <v>2149146.04</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2195211.7</v>
+        <v>86523.72</v>
       </c>
     </row>
     <row r="34">
@@ -1614,34 +1493,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2151</v>
+        <v>4711</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>81750398.86</v>
-      </c>
-      <c r="F34" t="n">
-        <v>76284993.93000001</v>
-      </c>
-      <c r="G34" t="n">
-        <v>75483300.69</v>
-      </c>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>24887.1</v>
+        <v>2149146.04</v>
       </c>
       <c r="I34" t="n">
-        <v>1770214.54</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1795101.64</v>
+        <v>2195211.7</v>
       </c>
     </row>
     <row r="35">
@@ -1650,34 +1520,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2271</v>
+        <v>2151</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2478485587.5</v>
+        <v>22445706.24</v>
       </c>
       <c r="F35" t="n">
-        <v>2347428600.43</v>
+        <v>16980301.31</v>
       </c>
       <c r="G35" t="n">
-        <v>2300004443.95</v>
+        <v>16174330.85</v>
       </c>
       <c r="H35" t="n">
-        <v>18122531.3</v>
+        <v>1843192.21</v>
       </c>
       <c r="I35" t="n">
-        <v>63228349.74</v>
-      </c>
-      <c r="J35" t="n">
-        <v>81350881.04000001</v>
+        <v>1795101.64</v>
       </c>
     </row>
     <row r="36">
@@ -1686,34 +1553,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4341</v>
+        <v>2271</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2288740.74</v>
+        <v>690392850.63</v>
       </c>
       <c r="F36" t="n">
-        <v>1318579.4</v>
+        <v>565744045.79</v>
       </c>
       <c r="G36" t="n">
-        <v>1060943.48</v>
+        <v>521637562.78</v>
       </c>
       <c r="H36" t="n">
-        <v>223487.09</v>
+        <v>65739905.52</v>
       </c>
       <c r="I36" t="n">
-        <v>548165.38</v>
-      </c>
-      <c r="J36" t="n">
-        <v>771652.47</v>
+        <v>81350881.04000001</v>
       </c>
     </row>
     <row r="37">
@@ -1722,34 +1586,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4091</v>
+        <v>4341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>610536.65</v>
+        <v>781858.49</v>
       </c>
       <c r="F37" t="n">
-        <v>323136.66</v>
+        <v>708840.6800000001</v>
       </c>
       <c r="G37" t="n">
-        <v>323136.66</v>
+        <v>589023.61</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>677235.17</v>
       </c>
       <c r="I37" t="n">
-        <v>2867068.53</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2867068.53</v>
+        <v>771652.47</v>
       </c>
     </row>
     <row r="38">
@@ -1758,34 +1619,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2061</v>
+        <v>4091</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>70806633.62</v>
+        <v>610536.65</v>
       </c>
       <c r="F38" t="n">
-        <v>68325905.25</v>
+        <v>323136.66</v>
       </c>
       <c r="G38" t="n">
-        <v>67044604.87</v>
+        <v>323136.66</v>
       </c>
       <c r="H38" t="n">
-        <v>11590.87</v>
+        <v>3000000</v>
       </c>
       <c r="I38" t="n">
-        <v>1026935.64</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1038526.51</v>
+        <v>2867068.53</v>
       </c>
     </row>
     <row r="39">
@@ -1794,34 +1652,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4141</v>
+        <v>2061</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10407251.17</v>
+        <v>12717266.18</v>
       </c>
       <c r="F39" t="n">
-        <v>6488589.5</v>
+        <v>10263123.01</v>
       </c>
       <c r="G39" t="n">
-        <v>6364731.34</v>
+        <v>9059338.279999999</v>
       </c>
       <c r="H39" t="n">
-        <v>747392.63</v>
+        <v>1136626.26</v>
       </c>
       <c r="I39" t="n">
-        <v>8034402.68</v>
-      </c>
-      <c r="J39" t="n">
-        <v>8781795.310000001</v>
+        <v>1038526.51</v>
       </c>
     </row>
     <row r="40">
@@ -1830,34 +1685,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4631</v>
+        <v>4141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>712687568.61</v>
+        <v>10407251.17</v>
       </c>
       <c r="F40" t="n">
-        <v>645428218.54</v>
+        <v>6488589.5</v>
       </c>
       <c r="G40" t="n">
-        <v>535779525.63</v>
+        <v>6364731.34</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>8129791.86</v>
       </c>
       <c r="I40" t="n">
-        <v>35286533.51</v>
-      </c>
-      <c r="J40" t="n">
-        <v>35286533.51</v>
+        <v>8781795.310000001</v>
       </c>
     </row>
     <row r="41">
@@ -1866,34 +1718,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2161</v>
+        <v>4631</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6356895.04</v>
+        <v>551297494.41</v>
       </c>
       <c r="F41" t="n">
-        <v>5950697.58</v>
+        <v>499038144.34</v>
       </c>
       <c r="G41" t="n">
-        <v>5865105.78</v>
+        <v>470142063.07</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>38807692.05</v>
       </c>
       <c r="I41" t="n">
-        <v>416373.16</v>
-      </c>
-      <c r="J41" t="n">
-        <v>416373.16</v>
+        <v>35286533.51</v>
       </c>
     </row>
     <row r="42">
@@ -1902,34 +1751,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4551</v>
+        <v>2161</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>148883049.2</v>
+        <v>1306128.89</v>
       </c>
       <c r="F42" t="n">
-        <v>148355490.34</v>
+        <v>912344.8100000001</v>
       </c>
       <c r="G42" t="n">
-        <v>148348943.52</v>
+        <v>834776.1</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>419440.72</v>
       </c>
       <c r="I42" t="n">
-        <v>620005.26</v>
-      </c>
-      <c r="J42" t="n">
-        <v>620005.26</v>
+        <v>416373.16</v>
       </c>
     </row>
     <row r="43">
@@ -1938,34 +1784,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FUNDALEMG</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4121</v>
+        <v>4551</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DA ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>7461545.44</v>
-      </c>
-      <c r="F43" t="n">
-        <v>5846301.44</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5378597.3</v>
-      </c>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>620005.26</v>
       </c>
       <c r="I43" t="n">
-        <v>704278.4</v>
-      </c>
-      <c r="J43" t="n">
-        <v>704278.4</v>
+        <v>620005.26</v>
       </c>
     </row>
     <row r="44">
@@ -1974,34 +1811,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FUNDIF</t>
+          <t>FUNDALEMG</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4421</v>
+        <v>4121</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>3658.62</v>
-      </c>
-      <c r="F44" t="n">
-        <v>3658.62</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3658.62</v>
-      </c>
+          <t>FUNDO ESPECIAL DA ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>895.13</v>
+        <v>765520</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>895.13</v>
+        <v>704278.4</v>
       </c>
     </row>
     <row r="45">
@@ -2010,34 +1838,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUNDIF</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2261</v>
+        <v>4421</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>553211607.35</v>
+        <v>3658.62</v>
       </c>
       <c r="F45" t="n">
-        <v>369463545.18</v>
+        <v>3658.62</v>
       </c>
       <c r="G45" t="n">
-        <v>355249323.08</v>
+        <v>3658.62</v>
       </c>
       <c r="H45" t="n">
-        <v>38687418.56</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>130773841.95</v>
-      </c>
-      <c r="J45" t="n">
-        <v>169461260.51</v>
+        <v>895.13</v>
       </c>
     </row>
     <row r="46">
@@ -2046,34 +1871,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FUNEMP</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4441</v>
+        <v>2261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>39626206.59</v>
+        <v>428927250.96</v>
       </c>
       <c r="F46" t="n">
-        <v>16926860.87</v>
+        <v>245649458.6</v>
       </c>
       <c r="G46" t="n">
-        <v>14755140.25</v>
+        <v>232061768.64</v>
       </c>
       <c r="H46" t="n">
-        <v>45219.46</v>
+        <v>131728444.02</v>
       </c>
       <c r="I46" t="n">
-        <v>6004181.02</v>
-      </c>
-      <c r="J46" t="n">
-        <v>6049400.48</v>
+        <v>169461260.51</v>
       </c>
     </row>
     <row r="47">
@@ -2082,34 +1904,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4381</v>
+        <v>4441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>127170575.95</v>
+        <v>14649640.67</v>
       </c>
       <c r="F47" t="n">
-        <v>102885370.45</v>
+        <v>1173096.28</v>
       </c>
       <c r="G47" t="n">
-        <v>98080707.2</v>
+        <v>1098197.52</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>6266323.05</v>
       </c>
       <c r="I47" t="n">
-        <v>21378670.3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>21378670.3</v>
+        <v>6049400.48</v>
       </c>
     </row>
     <row r="48">
@@ -2118,34 +1937,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1071</v>
+        <v>4381</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>55898902.78</v>
+        <v>127170575.95</v>
       </c>
       <c r="F48" t="n">
-        <v>34921981.44</v>
+        <v>102885370.45</v>
       </c>
       <c r="G48" t="n">
-        <v>32307667.05</v>
+        <v>98080707.2</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>22672867.63</v>
       </c>
       <c r="I48" t="n">
-        <v>4293686.19</v>
-      </c>
-      <c r="J48" t="n">
-        <v>4293686.19</v>
+        <v>21378670.3</v>
       </c>
     </row>
     <row r="49">
@@ -2154,34 +1970,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1916</v>
+        <v>1071</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6570721631.06</v>
+        <v>42308464.76</v>
       </c>
       <c r="F49" t="n">
-        <v>6570721631.06</v>
+        <v>21358582.02</v>
       </c>
       <c r="G49" t="n">
-        <v>6497797081.7</v>
+        <v>18612466.32</v>
       </c>
       <c r="H49" t="n">
-        <v>260833467.16</v>
+        <v>4382188.45</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>260833467.16</v>
+        <v>4293686.19</v>
       </c>
     </row>
     <row r="50">
@@ -2190,34 +2003,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2321</v>
+        <v>1916</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>394549598.81</v>
-      </c>
-      <c r="F50" t="n">
-        <v>359596023.43</v>
-      </c>
-      <c r="G50" t="n">
-        <v>346696259.17</v>
-      </c>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>1425788.73</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>30573782.13</v>
-      </c>
-      <c r="J50" t="n">
-        <v>31999570.86</v>
+        <v>260833467.16</v>
       </c>
     </row>
     <row r="51">
@@ -2226,34 +2030,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2421</v>
+        <v>2321</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61510642.64</v>
+        <v>193219059.3</v>
       </c>
       <c r="F51" t="n">
-        <v>43124254.63</v>
+        <v>159089336.34</v>
       </c>
       <c r="G51" t="n">
-        <v>41282826.79</v>
+        <v>146621312.05</v>
       </c>
       <c r="H51" t="n">
-        <v>713315.27</v>
+        <v>31236043.19</v>
       </c>
       <c r="I51" t="n">
-        <v>7206237.15</v>
-      </c>
-      <c r="J51" t="n">
-        <v>7919552.42</v>
+        <v>31999570.86</v>
       </c>
     </row>
     <row r="52">
@@ -2262,34 +2063,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2101</v>
+        <v>2421</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>217212201.82</v>
+        <v>50527838.19</v>
       </c>
       <c r="F52" t="n">
-        <v>204765475.8</v>
+        <v>32397666.62</v>
       </c>
       <c r="G52" t="n">
-        <v>196759897.63</v>
+        <v>30535778.74</v>
       </c>
       <c r="H52" t="n">
-        <v>1333045.2</v>
+        <v>7267490.57</v>
       </c>
       <c r="I52" t="n">
-        <v>7655898.75</v>
-      </c>
-      <c r="J52" t="n">
-        <v>8988943.949999999</v>
+        <v>7919552.42</v>
       </c>
     </row>
     <row r="53">
@@ -2298,34 +2096,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>28359171.85</v>
+        <v>66037057.46</v>
       </c>
       <c r="F53" t="n">
-        <v>27321777.4</v>
+        <v>54393468.32</v>
       </c>
       <c r="G53" t="n">
-        <v>25220175.31</v>
+        <v>46702934.5</v>
       </c>
       <c r="H53" t="n">
-        <v>6473.82</v>
+        <v>7940873.29</v>
       </c>
       <c r="I53" t="n">
-        <v>1262449.13</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1268922.95</v>
+        <v>8988943.949999999</v>
       </c>
     </row>
     <row r="54">
@@ -2334,34 +2129,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2241</v>
+        <v>2201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>195257062.85</v>
+        <v>7461044.53</v>
       </c>
       <c r="F54" t="n">
-        <v>182522813.41</v>
+        <v>6460996.99</v>
       </c>
       <c r="G54" t="n">
-        <v>181974009.41</v>
+        <v>5227305.54</v>
       </c>
       <c r="H54" t="n">
-        <v>10483113.83</v>
+        <v>1361879.35</v>
       </c>
       <c r="I54" t="n">
-        <v>1680822.65</v>
-      </c>
-      <c r="J54" t="n">
-        <v>12163936.48</v>
+        <v>1268922.95</v>
       </c>
     </row>
     <row r="55">
@@ -2370,34 +2162,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2371</v>
+        <v>2241</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>290312222.92</v>
+        <v>11120593.8</v>
       </c>
       <c r="F55" t="n">
-        <v>283815022.34</v>
+        <v>8241778.19</v>
       </c>
       <c r="G55" t="n">
-        <v>282551558.48</v>
+        <v>7818133.01</v>
       </c>
       <c r="H55" t="n">
-        <v>654297.5699999999</v>
+        <v>1720598.04</v>
       </c>
       <c r="I55" t="n">
-        <v>7082912.77</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7737210.34</v>
+        <v>12163936.48</v>
       </c>
     </row>
     <row r="56">
@@ -2406,34 +2195,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2331</v>
+        <v>2371</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>35739703.74</v>
+        <v>19321334.79</v>
       </c>
       <c r="F56" t="n">
-        <v>34318152.9</v>
+        <v>13523260.73</v>
       </c>
       <c r="G56" t="n">
-        <v>33074380.83</v>
+        <v>12243617.37</v>
       </c>
       <c r="H56" t="n">
-        <v>420781.11</v>
+        <v>7206218.74</v>
       </c>
       <c r="I56" t="n">
-        <v>436480.49</v>
-      </c>
-      <c r="J56" t="n">
-        <v>857261.6</v>
+        <v>7737210.34</v>
       </c>
     </row>
     <row r="57">
@@ -2442,29 +2228,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IPLEMG</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2361</v>
+        <v>2331</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>68465842.09</v>
+        <v>13676692.59</v>
       </c>
       <c r="F57" t="n">
-        <v>68465842.09</v>
+        <v>12255641.75</v>
       </c>
       <c r="G57" t="n">
-        <v>68465842.09</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+        <v>10913131.12</v>
+      </c>
+      <c r="H57" t="n">
+        <v>449499.79</v>
+      </c>
+      <c r="I57" t="n">
+        <v>857261.6</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2472,35 +2261,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2011</v>
+        <v>2361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2066687330.24</v>
+        <v>68465842.09</v>
       </c>
       <c r="F58" t="n">
-        <v>1811898139.4</v>
+        <v>68465842.09</v>
       </c>
       <c r="G58" t="n">
-        <v>1767628149.66</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1062515.58</v>
-      </c>
-      <c r="I58" t="n">
-        <v>92904525.54000001</v>
-      </c>
-      <c r="J58" t="n">
-        <v>93967041.12</v>
-      </c>
+        <v>68465842.09</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2508,34 +2290,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2121</v>
+        <v>2011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3302390465.79</v>
+        <v>317588972.65</v>
       </c>
       <c r="F59" t="n">
-        <v>3251209178.87</v>
+        <v>242449485.72</v>
       </c>
       <c r="G59" t="n">
-        <v>3202602086.92</v>
+        <v>224900638.49</v>
       </c>
       <c r="H59" t="n">
-        <v>294911.07</v>
+        <v>96695021.44</v>
       </c>
       <c r="I59" t="n">
-        <v>15606900.02</v>
-      </c>
-      <c r="J59" t="n">
-        <v>15901811.09</v>
+        <v>93967041.12</v>
       </c>
     </row>
     <row r="60">
@@ -2544,34 +2323,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2251</v>
+        <v>2121</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>41105200.07</v>
+        <v>102305375.99</v>
       </c>
       <c r="F60" t="n">
-        <v>38759738.47</v>
+        <v>88759441.81</v>
       </c>
       <c r="G60" t="n">
-        <v>36259002.32</v>
+        <v>81528414.51000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>16902644.95</v>
       </c>
       <c r="I60" t="n">
-        <v>1415037.52</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1415037.52</v>
+        <v>15901811.09</v>
       </c>
     </row>
     <row r="61">
@@ -2580,34 +2356,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2041</v>
+        <v>2251</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2901561.62</v>
+        <v>14883843.71</v>
       </c>
       <c r="F61" t="n">
-        <v>2865088.76</v>
+        <v>12754454.71</v>
       </c>
       <c r="G61" t="n">
-        <v>2860275.95</v>
+        <v>10951834.76</v>
       </c>
       <c r="H61" t="n">
-        <v>3394.97</v>
+        <v>1502850.88</v>
       </c>
       <c r="I61" t="n">
-        <v>24471.67</v>
-      </c>
-      <c r="J61" t="n">
-        <v>27866.64</v>
+        <v>1415037.52</v>
       </c>
     </row>
     <row r="62">
@@ -2616,34 +2389,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>18048368.2</v>
+        <v>161962.33</v>
       </c>
       <c r="F62" t="n">
-        <v>17928588.51</v>
+        <v>125489.47</v>
       </c>
       <c r="G62" t="n">
-        <v>17774694.27</v>
+        <v>118482.07</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>25301.47</v>
       </c>
       <c r="I62" t="n">
-        <v>57114.59</v>
-      </c>
-      <c r="J62" t="n">
-        <v>57114.59</v>
+        <v>27866.64</v>
       </c>
     </row>
     <row r="63">
@@ -2652,34 +2422,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>MG INVESTE</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1915</v>
+        <v>4621</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>20043002.56</v>
-      </c>
-      <c r="F63" t="n">
-        <v>20043002.56</v>
-      </c>
-      <c r="G63" t="n">
-        <v>20043002.56</v>
-      </c>
+          <t>FUNDO DE INVESTIMENTO DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>46.77</v>
-      </c>
-      <c r="J63" t="n">
-        <v>46.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2688,34 +2449,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1511</v>
+        <v>1101</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3138279917.06</v>
+        <v>1962170.85</v>
       </c>
       <c r="F64" t="n">
-        <v>3076106533.57</v>
+        <v>1842391.16</v>
       </c>
       <c r="G64" t="n">
-        <v>3055981056.68</v>
+        <v>1687424.71</v>
       </c>
       <c r="H64" t="n">
-        <v>18355346.55</v>
+        <v>59648.14</v>
       </c>
       <c r="I64" t="n">
-        <v>41103215.43</v>
-      </c>
-      <c r="J64" t="n">
-        <v>59458561.98</v>
+        <v>57114.59</v>
       </c>
     </row>
     <row r="65">
@@ -2724,34 +2482,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PGJ</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1091</v>
+        <v>1915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTICA</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>4236732028.37</v>
-      </c>
-      <c r="F65" t="n">
-        <v>4141114287.8</v>
-      </c>
-      <c r="G65" t="n">
-        <v>4100009275.29</v>
-      </c>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>5441376.69</v>
+        <v>46.77</v>
       </c>
       <c r="I65" t="n">
-        <v>90708170.09999999</v>
-      </c>
-      <c r="J65" t="n">
-        <v>96149546.79000001</v>
+        <v>46.77</v>
       </c>
     </row>
     <row r="66">
@@ -2760,34 +2509,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1251</v>
+        <v>1511</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>17184629357.54</v>
+        <v>291434748.82</v>
       </c>
       <c r="F66" t="n">
-        <v>16913388822.07</v>
+        <v>230281934.94</v>
       </c>
       <c r="G66" t="n">
-        <v>16881355805.92</v>
+        <v>210474698.43</v>
       </c>
       <c r="H66" t="n">
-        <v>22568008.23</v>
+        <v>42618737.24</v>
       </c>
       <c r="I66" t="n">
-        <v>179457677.69</v>
-      </c>
-      <c r="J66" t="n">
-        <v>202025685.92</v>
+        <v>59458561.98</v>
       </c>
     </row>
     <row r="67">
@@ -2796,34 +2542,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1721</v>
+        <v>1091</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10652572.94</v>
+        <v>373360990.04</v>
       </c>
       <c r="F67" t="n">
-        <v>10295525.12</v>
+        <v>288800424.93</v>
       </c>
       <c r="G67" t="n">
-        <v>9939287.65</v>
+        <v>246765253.55</v>
       </c>
       <c r="H67" t="n">
-        <v>10152.64</v>
+        <v>96154922.41</v>
       </c>
       <c r="I67" t="n">
-        <v>276281.69</v>
-      </c>
-      <c r="J67" t="n">
-        <v>286434.33</v>
+        <v>96149546.79000001</v>
       </c>
     </row>
     <row r="68">
@@ -2832,34 +2575,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1231</v>
+        <v>1251</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>319941879.07</v>
+        <v>602215326.59</v>
       </c>
       <c r="F68" t="n">
-        <v>286029024.67</v>
+        <v>334228626.99</v>
       </c>
       <c r="G68" t="n">
-        <v>275453889.56</v>
+        <v>302216104.26</v>
       </c>
       <c r="H68" t="n">
-        <v>4468309.21</v>
+        <v>184962081.37</v>
       </c>
       <c r="I68" t="n">
-        <v>18499399.92</v>
-      </c>
-      <c r="J68" t="n">
-        <v>22967709.13</v>
+        <v>202025685.92</v>
       </c>
     </row>
     <row r="69">
@@ -2868,34 +2608,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1631</v>
+        <v>1721</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>12493555.88</v>
+        <v>2536988.16</v>
       </c>
       <c r="F69" t="n">
-        <v>12400512.79</v>
+        <v>2273562.28</v>
       </c>
       <c r="G69" t="n">
-        <v>12257285.88</v>
+        <v>1921255.95</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>281652.2</v>
       </c>
       <c r="I69" t="n">
-        <v>138983.68</v>
-      </c>
-      <c r="J69" t="n">
-        <v>138983.68</v>
+        <v>286434.33</v>
       </c>
     </row>
     <row r="70">
@@ -2904,34 +2641,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1711</v>
+        <v>1231</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>181181663.88</v>
+        <v>125148860.72</v>
       </c>
       <c r="F70" t="n">
-        <v>101620737.74</v>
+        <v>102321590.84</v>
       </c>
       <c r="G70" t="n">
-        <v>97019401.54000001</v>
+        <v>98646414.09999999</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>18854223.87</v>
       </c>
       <c r="I70" t="n">
-        <v>76618911.3</v>
-      </c>
-      <c r="J70" t="n">
-        <v>76618911.3</v>
+        <v>22967709.13</v>
       </c>
     </row>
     <row r="71">
@@ -2940,34 +2674,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1271</v>
+        <v>1631</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>261449910.33</v>
+        <v>1258886.8</v>
       </c>
       <c r="F71" t="n">
-        <v>260070135.18</v>
+        <v>1220837.34</v>
       </c>
       <c r="G71" t="n">
-        <v>257629551.13</v>
+        <v>1034678.49</v>
       </c>
       <c r="H71" t="n">
-        <v>2520</v>
+        <v>143395.07</v>
       </c>
       <c r="I71" t="n">
-        <v>2485549.72</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2488069.72</v>
+        <v>138983.68</v>
       </c>
     </row>
     <row r="72">
@@ -2976,34 +2707,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1221</v>
+        <v>1711</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>425928118.33</v>
+        <v>167877885.35</v>
       </c>
       <c r="F72" t="n">
-        <v>106813200.9</v>
+        <v>88316959.20999999</v>
       </c>
       <c r="G72" t="n">
-        <v>104972627.41</v>
+        <v>83757957.26000001</v>
       </c>
       <c r="H72" t="n">
-        <v>3819.55</v>
+        <v>80368832.76000001</v>
       </c>
       <c r="I72" t="n">
-        <v>10240167.34</v>
-      </c>
-      <c r="J72" t="n">
-        <v>10243986.89</v>
+        <v>76618911.3</v>
       </c>
     </row>
     <row r="73">
@@ -3012,34 +2740,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1481</v>
+        <v>1271</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>338412512.01</v>
+        <v>31225463.65</v>
       </c>
       <c r="F73" t="n">
-        <v>284330922.14</v>
+        <v>29951004.32</v>
       </c>
       <c r="G73" t="n">
-        <v>273376533.99</v>
+        <v>27110347.25</v>
       </c>
       <c r="H73" t="n">
-        <v>6492833.43</v>
+        <v>2511400.79</v>
       </c>
       <c r="I73" t="n">
-        <v>13954481.02</v>
-      </c>
-      <c r="J73" t="n">
-        <v>20447314.45</v>
+        <v>2488069.72</v>
       </c>
     </row>
     <row r="74">
@@ -3048,34 +2773,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>20024070516.28</v>
+        <v>332794381.23</v>
       </c>
       <c r="F74" t="n">
-        <v>19817333122</v>
+        <v>15826635.76</v>
       </c>
       <c r="G74" t="n">
-        <v>19583419698.99</v>
+        <v>13970714.82</v>
       </c>
       <c r="H74" t="n">
-        <v>102690852.14</v>
+        <v>10406884.06</v>
       </c>
       <c r="I74" t="n">
-        <v>437921985.25</v>
-      </c>
-      <c r="J74" t="n">
-        <v>540612837.39</v>
+        <v>10243986.89</v>
       </c>
     </row>
     <row r="75">
@@ -3084,34 +2806,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1191</v>
+        <v>1481</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1886784188.81</v>
+        <v>76364473.64</v>
       </c>
       <c r="F75" t="n">
-        <v>1792612515.59</v>
+        <v>25375821.97</v>
       </c>
       <c r="G75" t="n">
-        <v>1767643635.43</v>
+        <v>23154513.43</v>
       </c>
       <c r="H75" t="n">
-        <v>5956448.89</v>
+        <v>14551272.77</v>
       </c>
       <c r="I75" t="n">
-        <v>38130787.08</v>
-      </c>
-      <c r="J75" t="n">
-        <v>44087235.97</v>
+        <v>20447314.45</v>
       </c>
     </row>
     <row r="76">
@@ -3120,34 +2839,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1491</v>
+        <v>1261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>971196665.48</v>
+        <v>1647660426.2</v>
       </c>
       <c r="F76" t="n">
-        <v>965761230.4299999</v>
+        <v>1460985023.78</v>
       </c>
       <c r="G76" t="n">
-        <v>950181400.99</v>
+        <v>1357356293.22</v>
       </c>
       <c r="H76" t="n">
-        <v>1028658.15</v>
+        <v>447641263.11</v>
       </c>
       <c r="I76" t="n">
-        <v>17535020.6</v>
-      </c>
-      <c r="J76" t="n">
-        <v>18563678.75</v>
+        <v>540612837.39</v>
       </c>
     </row>
     <row r="77">
@@ -3156,34 +2872,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1301</v>
+        <v>1191</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>480636059.58</v>
+        <v>272121296.31</v>
       </c>
       <c r="F77" t="n">
-        <v>393222333.81</v>
+        <v>182907889.63</v>
       </c>
       <c r="G77" t="n">
-        <v>363896390.26</v>
+        <v>163991369.41</v>
       </c>
       <c r="H77" t="n">
-        <v>11727528.06</v>
+        <v>40721854.18</v>
       </c>
       <c r="I77" t="n">
-        <v>201174882.85</v>
-      </c>
-      <c r="J77" t="n">
-        <v>212902410.91</v>
+        <v>44087235.97</v>
       </c>
     </row>
     <row r="78">
@@ -3192,34 +2905,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1451</v>
+        <v>1491</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4556477829.69</v>
+        <v>43335682.08</v>
       </c>
       <c r="F78" t="n">
-        <v>4357599952.24</v>
+        <v>37911528.7</v>
       </c>
       <c r="G78" t="n">
-        <v>4322020545.17</v>
+        <v>29811965.03</v>
       </c>
       <c r="H78" t="n">
-        <v>4833097.2</v>
+        <v>20217485.8</v>
       </c>
       <c r="I78" t="n">
-        <v>108147895.72</v>
-      </c>
-      <c r="J78" t="n">
-        <v>112980992.92</v>
+        <v>18563678.75</v>
       </c>
     </row>
     <row r="79">
@@ -3228,34 +2938,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185286819.99</v>
+        <v>159660221.46</v>
       </c>
       <c r="F79" t="n">
-        <v>178437283.68</v>
+        <v>72388716</v>
       </c>
       <c r="G79" t="n">
-        <v>172648640.16</v>
+        <v>68042026.41</v>
       </c>
       <c r="H79" t="n">
-        <v>271467.65</v>
+        <v>202731195.92</v>
       </c>
       <c r="I79" t="n">
-        <v>5465504.58</v>
-      </c>
-      <c r="J79" t="n">
-        <v>5736972.23</v>
+        <v>212902410.91</v>
       </c>
     </row>
     <row r="80">
@@ -3264,34 +2971,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>940771355.51</v>
+        <v>859917961.11</v>
       </c>
       <c r="F80" t="n">
-        <v>840171011.05</v>
+        <v>675481277.9400001</v>
       </c>
       <c r="G80" t="n">
-        <v>779489331.71</v>
+        <v>645008694.01</v>
       </c>
       <c r="H80" t="n">
-        <v>9145522.6</v>
+        <v>115883928.33</v>
       </c>
       <c r="I80" t="n">
-        <v>62616118.7</v>
-      </c>
-      <c r="J80" t="n">
-        <v>71761641.3</v>
+        <v>112980992.92</v>
       </c>
     </row>
     <row r="81">
@@ -3300,34 +3004,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TCEMG</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1021</v>
+        <v>1371</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1497702565.35</v>
+        <v>30627879.2</v>
       </c>
       <c r="F81" t="n">
-        <v>1459808527.61</v>
+        <v>24704490.71</v>
       </c>
       <c r="G81" t="n">
-        <v>1447340682.34</v>
+        <v>22673198.22</v>
       </c>
       <c r="H81" t="n">
-        <v>33256.58</v>
+        <v>5668995</v>
       </c>
       <c r="I81" t="n">
-        <v>28511863.55</v>
-      </c>
-      <c r="J81" t="n">
-        <v>28545120.13</v>
+        <v>5736972.23</v>
       </c>
     </row>
     <row r="82">
@@ -3336,29 +3037,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TJMG</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1031</v>
+        <v>1501</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>10945290220.95</v>
+        <v>462075650.68</v>
       </c>
       <c r="F82" t="n">
-        <v>10945290220.95</v>
+        <v>370898728.94</v>
       </c>
       <c r="G82" t="n">
-        <v>10946228265.22</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+        <v>327404904.65</v>
+      </c>
+      <c r="H82" t="n">
+        <v>67080853.65</v>
+      </c>
+      <c r="I82" t="n">
+        <v>71761641.3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3366,34 +3070,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TJMMG</t>
+          <t>TCEMG</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1051</v>
+        <v>1021</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>164960722.27</v>
+        <v>129302564.54</v>
       </c>
       <c r="F83" t="n">
-        <v>159274638.21</v>
+        <v>91754036.39</v>
       </c>
       <c r="G83" t="n">
-        <v>157731413.39</v>
+        <v>77297843.15000001</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>33277251.8</v>
       </c>
       <c r="I83" t="n">
-        <v>6499456.92</v>
-      </c>
-      <c r="J83" t="n">
-        <v>6499456.92</v>
+        <v>28545120.13</v>
       </c>
     </row>
     <row r="84">
@@ -3402,34 +3103,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>TJMMG</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2211</v>
+        <v>1051</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>16376327.77</v>
+        <v>18735731.76</v>
       </c>
       <c r="F84" t="n">
-        <v>15665660.91</v>
+        <v>13076787.92</v>
       </c>
       <c r="G84" t="n">
-        <v>14963532.88</v>
+        <v>11529840.23</v>
       </c>
       <c r="H84" t="n">
-        <v>84375.35000000001</v>
+        <v>6895032.89</v>
       </c>
       <c r="I84" t="n">
-        <v>903154.46</v>
-      </c>
-      <c r="J84" t="n">
-        <v>987529.8100000001</v>
+        <v>6499456.92</v>
       </c>
     </row>
     <row r="85">
@@ -3438,34 +3136,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2351</v>
+        <v>2211</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>431560939.48</v>
+        <v>7073363.83</v>
       </c>
       <c r="F85" t="n">
-        <v>399364373.03</v>
+        <v>6415719.38</v>
       </c>
       <c r="G85" t="n">
-        <v>391027226.76</v>
+        <v>5724333.06</v>
       </c>
       <c r="H85" t="n">
-        <v>1690845.8</v>
+        <v>964592.52</v>
       </c>
       <c r="I85" t="n">
-        <v>7591910.97</v>
-      </c>
-      <c r="J85" t="n">
-        <v>9282756.77</v>
+        <v>987529.8100000001</v>
       </c>
     </row>
     <row r="86">
@@ -3474,34 +3169,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>UEMG</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2311</v>
+        <v>2351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>533150763.61</v>
+        <v>102730235.3</v>
       </c>
       <c r="F86" t="n">
-        <v>503448723.24</v>
+        <v>72858869.34</v>
       </c>
       <c r="G86" t="n">
-        <v>492058770.59</v>
+        <v>65773942.81</v>
       </c>
       <c r="H86" t="n">
-        <v>274974.01</v>
+        <v>8096430.92</v>
       </c>
       <c r="I86" t="n">
-        <v>39010212.22</v>
-      </c>
-      <c r="J86" t="n">
-        <v>39285186.23</v>
+        <v>9282756.77</v>
       </c>
     </row>
     <row r="87">
@@ -3510,33 +3202,63 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>85401973.18000001</v>
+      </c>
+      <c r="F87" t="n">
+        <v>63164899.02</v>
+      </c>
+      <c r="G87" t="n">
+        <v>57076892.02</v>
+      </c>
+      <c r="H87" t="n">
+        <v>43051446.14</v>
+      </c>
+      <c r="I87" t="n">
+        <v>39285186.23</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C88" t="n">
         <v>2281</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>7417117.22</v>
-      </c>
-      <c r="F87" t="n">
-        <v>6859782.46</v>
-      </c>
-      <c r="G87" t="n">
-        <v>6435691.91</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>231057.02</v>
-      </c>
-      <c r="J87" t="n">
+      <c r="E88" t="n">
+        <v>3674762.92</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3127428.16</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2767627.66</v>
+      </c>
+      <c r="H88" t="n">
+        <v>261911.27</v>
+      </c>
+      <c r="I88" t="n">
         <v>231057.02</v>
       </c>
     </row>
